--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -943,7 +943,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -953,38 +953,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>B-</t>
+          <t>CCC-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PCI (36-month, non-financing) after ECF $3.0B completed 27-Jul-26</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>14</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L9" t="n">
-        <v>12</v>
-      </c>
-      <c r="M9" t="n">
-        <v>5.2</v>
+          <t>None (technical surveillance only)</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>70</v>
+      </c>
+      <c r="U9" t="n">
+        <v>17.5</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -993,31 +979,31 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>reports/ghana-sovereign-credit.md</t>
+          <t>reports/gabon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Caa1</t>
@@ -1025,20 +1011,23 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>None (Article IV / Post-Financing Assessment)</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>-6.8</v>
+          <t>PCI (36-month, non-financing) after ECF $3.0B completed 27-Jul-26</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>80.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.506</v>
+        <v>5.2</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1047,14 +1036,14 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>reports/iraq-sovereign-credit.md</t>
+          <t>reports/ghana-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1064,44 +1053,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ba3</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EFF (4-year) + RSF</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>6</v>
+          <t>None (Article IV / Post-Financing Assessment)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>-6.8</v>
       </c>
       <c r="L11" t="n">
-        <v>28.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="P11" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-2.8</v>
+        <v>9.6</v>
       </c>
       <c r="X11" t="n">
-        <v>3.95</v>
+        <v>0.506</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1110,61 +1090,61 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>reports/jordan-sovereign-credit.md</t>
+          <t>reports/iraq-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>None (previous EFF/ECF/RSF expired Apr-25; successor under discussion)</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>6.8</v>
+          <t>EFF (4-year) + RSF</t>
+        </is>
       </c>
       <c r="I12" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>14.702</v>
+        <v>28.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>68.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>33</v>
+        <v>-5.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.95</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1173,58 +1153,61 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>reports/kenya-sovereign-credit.md</t>
+          <t>reports/jordan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ba1</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FCL (2-year, precautionary)</t>
-        </is>
+          <t>None (previous EFF/ECF/RSF expired Apr-25; successor under discussion)</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>6.8</v>
       </c>
       <c r="I13" t="n">
-        <v>2.25</v>
+        <v>8.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.95</v>
       </c>
       <c r="L13" t="n">
-        <v>55.65</v>
-      </c>
-      <c r="M13" t="n">
-        <v>5.5</v>
+        <v>14.702</v>
       </c>
       <c r="P13" t="n">
-        <v>66.5</v>
+        <v>68.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3</v>
+        <v>-6.4</v>
       </c>
       <c r="S13" t="n">
-        <v>11.5</v>
+        <v>33</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1233,58 +1216,58 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>reports/morocco-sovereign-credit.md</t>
+          <t>reports/kenya-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Ba1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>15.39</v>
+          <t>FCL (2-year, precautionary)</t>
+        </is>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
-      </c>
-      <c r="J14" t="n">
-        <v>7.61</v>
+        <v>2.25</v>
       </c>
       <c r="L14" t="n">
-        <v>54.98</v>
+        <v>55.65</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.5</v>
       </c>
       <c r="P14" t="n">
-        <v>32.3</v>
+        <v>66.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-3</v>
       </c>
       <c r="S14" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1293,34 +1276,34 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>reports/nigeria-sovereign-credit.md</t>
+          <t>reports/morocco-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Baa3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1328,20 +1311,23 @@
           <t>None (Article IV)</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>2.1</v>
+      <c r="H15" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="I15" t="n">
+        <v>23</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7.61</v>
       </c>
       <c r="L15" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5</v>
+        <v>54.98</v>
       </c>
       <c r="P15" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.65</v>
+        <v>32.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>55</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -1350,47 +1336,55 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>reports/oman-sovereign-credit.md</t>
+          <t>reports/nigeria-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Caa2</t>
+          <t>Baa3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.8</v>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>132</v>
+        <v>34.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.65</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -1399,58 +1393,47 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>reports/senegal-sovereign-credit.md</t>
+          <t>reports/oman-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BB+</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PCI (36-month, non-financing)</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>3.3</v>
+          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
+        </is>
       </c>
       <c r="H17" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-4.1</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>43.3</v>
+        <v>132</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -1459,29 +1442,29 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>reports/serbia-sovereign-credit.md</t>
+          <t>reports/senegal-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1491,29 +1474,26 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
+          <t>PCI (36-month, non-financing)</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="I18" t="n">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="J18" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-4.5</v>
+        <v>-4.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>43.3</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -1522,34 +1502,34 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>reports/south-africa-sovereign-credit.md</t>
+          <t>reports/serbia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ba3</t>
+          <t>Ba2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1558,31 +1538,25 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>29.73</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>37</v>
+        <v>7.25</v>
       </c>
       <c r="J19" t="n">
-        <v>7.27</v>
+        <v>2.85</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.7</v>
+        <v>-1.6</v>
       </c>
       <c r="L19" t="n">
-        <v>61.56</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O19" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="P19" t="n">
-        <v>29.5</v>
+        <v>63.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.2</v>
+        <v>-4.5</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -1591,14 +1565,14 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>reports/turkey-sovereign-credit.md</t>
+          <t>reports/south-africa-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1608,41 +1582,50 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CCC+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EFF (4-year)</t>
+          <t>None (Article IV)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>8.1</v>
+        <v>29.73</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J20" t="n">
-        <v>7.9</v>
+        <v>7.27</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-2.7</v>
       </c>
       <c r="L20" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5.6</v>
+        <v>61.56</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O20" t="n">
+        <v>31.8</v>
       </c>
       <c r="P20" t="n">
-        <v>98.40000000000001</v>
+        <v>29.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-5.2</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -1651,71 +1634,131 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+          <t>reports/turkey-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CCC+</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>EFF (4-year)</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>16</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>reports/ukraine-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>CIS</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Ba2</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>None (Article IV)</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>6.8</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>6.2</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>14</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>7.8</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>72.13</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>12</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>27</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>-2.1</v>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>reports/uzbekistan-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB22"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -830,41 +830,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EFF/ECF ($3.5B) and RSF ($1.3B) completed Jun-26</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
+          <t>Post-Financing Assessment (PFA); ECF/EFF/RSF completed Jul-25</t>
+        </is>
       </c>
       <c r="H7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>30</v>
       </c>
       <c r="P7" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-3.8</v>
+        <v>43</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="n">
+        <v>12</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -873,61 +870,58 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>reports/cote-d-ivoire-sovereign-credit.md</t>
+          <t>reports/cameroon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Ba2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EFF</t>
-        </is>
+          <t>EFF/ECF ($3.5B) and RSF ($1.3B) completed Jun-26</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>12.7</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7.5</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>50</v>
+        <v>55.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-3.8</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -936,41 +930,61 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>reports/egypt-sovereign-credit.md</t>
+          <t>reports/cote-d-ivoire-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CCC-</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caa2</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>None (technical surveillance only)</t>
-        </is>
+          <t>EFF</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>19</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7.5</v>
       </c>
       <c r="P9" t="n">
-        <v>70</v>
-      </c>
-      <c r="U9" t="n">
-        <v>17.5</v>
+        <v>79.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -979,14 +993,14 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>reports/gabon-sovereign-credit.md</t>
+          <t>reports/egypt-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -996,38 +1010,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>B-</t>
+          <t>CCC-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PCI (36-month, non-financing) after ECF $3.0B completed 27-Jul-26</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>14</v>
-      </c>
-      <c r="J10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L10" t="n">
-        <v>12</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5.2</v>
+          <t>None (technical surveillance only)</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>70</v>
+      </c>
+      <c r="U10" t="n">
+        <v>17.5</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1036,31 +1036,31 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>reports/ghana-sovereign-credit.md</t>
+          <t>reports/gabon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Caa1</t>
@@ -1068,20 +1068,23 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>None (Article IV / Post-Financing Assessment)</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>-6.8</v>
+          <t>PCI (36-month, non-financing) after ECF $3.0B completed 27-Jul-26</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>80.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="M11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.506</v>
+        <v>5.2</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1090,14 +1093,14 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>reports/iraq-sovereign-credit.md</t>
+          <t>reports/ghana-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1107,44 +1110,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ba3</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EFF (4-year) + RSF</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>6</v>
+          <t>None (Article IV / Post-Financing Assessment)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>-6.8</v>
       </c>
       <c r="L12" t="n">
-        <v>28.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="P12" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-2.8</v>
+        <v>9.6</v>
       </c>
       <c r="X12" t="n">
-        <v>3.95</v>
+        <v>0.506</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1153,61 +1147,61 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>reports/jordan-sovereign-credit.md</t>
+          <t>reports/iraq-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>None (previous EFF/ECF/RSF expired Apr-25; successor under discussion)</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>6.8</v>
+          <t>EFF (4-year) + RSF</t>
+        </is>
       </c>
       <c r="I13" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>14.702</v>
+        <v>28.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>68.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>33</v>
+        <v>-5.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.95</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1216,58 +1210,61 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>reports/kenya-sovereign-credit.md</t>
+          <t>reports/jordan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ba1</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCL (2-year, precautionary)</t>
-        </is>
+          <t>None (previous EFF/ECF/RSF expired Apr-25; successor under discussion)</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>6.8</v>
       </c>
       <c r="I14" t="n">
-        <v>2.25</v>
+        <v>8.75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.95</v>
       </c>
       <c r="L14" t="n">
-        <v>55.65</v>
-      </c>
-      <c r="M14" t="n">
-        <v>5.5</v>
+        <v>14.702</v>
       </c>
       <c r="P14" t="n">
-        <v>66.5</v>
+        <v>68.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3</v>
+        <v>-6.4</v>
       </c>
       <c r="S14" t="n">
-        <v>11.5</v>
+        <v>33</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1276,58 +1273,58 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>reports/morocco-sovereign-credit.md</t>
+          <t>reports/kenya-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Ba1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>15.39</v>
+          <t>FCL (2-year, precautionary)</t>
+        </is>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
-      </c>
-      <c r="J15" t="n">
-        <v>7.61</v>
+        <v>2.25</v>
       </c>
       <c r="L15" t="n">
-        <v>54.98</v>
+        <v>55.65</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.5</v>
       </c>
       <c r="P15" t="n">
-        <v>32.3</v>
+        <v>66.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-3</v>
       </c>
       <c r="S15" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -1336,34 +1333,34 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>reports/nigeria-sovereign-credit.md</t>
+          <t>reports/morocco-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Baa3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1371,20 +1368,23 @@
           <t>None (Article IV)</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>2.1</v>
+      <c r="H16" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="I16" t="n">
+        <v>23</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7.61</v>
       </c>
       <c r="L16" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="M16" t="n">
-        <v>5</v>
+        <v>54.98</v>
       </c>
       <c r="P16" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.65</v>
+        <v>32.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>55</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -1393,47 +1393,55 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>reports/oman-sovereign-credit.md</t>
+          <t>reports/nigeria-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caa2</t>
+          <t>Baa3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.8</v>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>132</v>
+        <v>34.7</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.65</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -1442,58 +1450,47 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>reports/senegal-sovereign-credit.md</t>
+          <t>reports/oman-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>BB+</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PCI (36-month, non-financing)</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>3.3</v>
+          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
+        </is>
       </c>
       <c r="H18" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-4.1</v>
+        <v>1.8</v>
       </c>
       <c r="P18" t="n">
-        <v>43.3</v>
+        <v>132</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -1502,29 +1499,29 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>reports/serbia-sovereign-credit.md</t>
+          <t>reports/senegal-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1534,29 +1531,26 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
+          <t>PCI (36-month, non-financing)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="I19" t="n">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="J19" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="L19" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-4.5</v>
+        <v>-4.1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>43.3</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -1565,34 +1559,34 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>reports/south-africa-sovereign-credit.md</t>
+          <t>reports/serbia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ba3</t>
+          <t>Ba2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1601,31 +1595,25 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>29.73</v>
+        <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>37</v>
+        <v>7.25</v>
       </c>
       <c r="J20" t="n">
-        <v>7.27</v>
+        <v>2.85</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.7</v>
+        <v>-1.6</v>
       </c>
       <c r="L20" t="n">
-        <v>61.56</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O20" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>29.5</v>
+        <v>63.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.2</v>
+        <v>-4.5</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -1634,14 +1622,14 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>reports/turkey-sovereign-credit.md</t>
+          <t>reports/south-africa-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1651,41 +1639,50 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CCC+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EFF (4-year)</t>
+          <t>None (Article IV)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>8.1</v>
+        <v>29.73</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J21" t="n">
-        <v>7.9</v>
+        <v>7.27</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-2.7</v>
       </c>
       <c r="L21" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5.6</v>
+        <v>61.56</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O21" t="n">
+        <v>31.8</v>
       </c>
       <c r="P21" t="n">
-        <v>98.40000000000001</v>
+        <v>29.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-5.2</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -1694,71 +1691,131 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+          <t>reports/turkey-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CCC+</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>EFF (4-year)</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>16</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>reports/ukraine-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>CIS</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Ba2</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>None (Article IV)</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>6.8</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>6.2</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>14</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>7.8</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>72.13</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>12</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>27</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>-2.1</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>reports/uzbekistan-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1821,6 +1821,69 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CCC+</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Caa2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Concluded 38-month US$1.3bn ECF in Jan-26; negotiating successor program</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>91</v>
+      </c>
+      <c r="S24" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>reports/zambia-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1629,61 +1629,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ba3</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>Frozen USD 1.9bn EFF agreed at staff level in Oct-22; no active Executive Board approval</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>29.73</v>
+        <v>5.6</v>
       </c>
       <c r="I21" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="L21" t="n">
-        <v>61.56</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O21" t="n">
-        <v>31.8</v>
+        <v>1.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>29.5</v>
+        <v>82</v>
       </c>
       <c r="Q21" t="n">
         <v>-5.2</v>
       </c>
+      <c r="X21" t="n">
+        <v>0.15</v>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>08-Oct-26</t>
@@ -1691,14 +1680,14 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>reports/turkey-sovereign-credit.md</t>
+          <t>reports/tunisia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1708,41 +1697,50 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CCC+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>EFF (4-year)</t>
+          <t>None (Article IV)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>8.1</v>
+        <v>29.73</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J22" t="n">
-        <v>7.9</v>
+        <v>7.27</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-2.7</v>
       </c>
       <c r="L22" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>5.6</v>
+        <v>61.56</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O22" t="n">
+        <v>31.8</v>
       </c>
       <c r="P22" t="n">
-        <v>98.40000000000001</v>
+        <v>29.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-5.2</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -1751,64 +1749,58 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+          <t>reports/turkey-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CIS</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>CCC+</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>6.8</v>
+          <t>EFF (4-year)</t>
+        </is>
       </c>
       <c r="H23" t="n">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="I23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="L23" t="n">
-        <v>72.13</v>
+        <v>47.1</v>
       </c>
       <c r="M23" t="n">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="P23" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-2.1</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -1817,68 +1809,134 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>reports/uzbekistan-sovereign-credit.md</t>
+          <t>reports/ukraine-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CIS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>14</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="M24" t="n">
+        <v>12</v>
+      </c>
+      <c r="P24" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>reports/uzbekistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>CCC+</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Caa2</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Concluded 38-month US$1.3bn ECF in Jan-26; negotiating successor program</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="H25" t="n">
         <v>6.1</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>10.75</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>4.65</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>5.8</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>4.2</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>91</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>35</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>reports/zambia-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB25"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -820,48 +820,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Post-Financing Assessment (PFA); ECF/EFF/RSF completed Jul-25</t>
-        </is>
+          <t>Blended 42-month EFF/ECF ($638m) and RSF ($200m) completed 25-Feb-26</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>7.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>30</v>
+        <v>1.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-5.5</v>
       </c>
       <c r="P7" t="n">
-        <v>43</v>
+        <v>54</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.6</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T7" t="n">
-        <v>12</v>
+        <v>14.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.85</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -870,14 +882,14 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>reports/cameroon-sovereign-credit.md</t>
+          <t>reports/benin-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -887,41 +899,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EFF/ECF ($3.5B) and RSF ($1.3B) completed Jun-26</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>6</v>
+          <t>Post-Financing Assessment (PFA); ECF/EFF/RSF completed Jul-25</t>
+        </is>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>30</v>
       </c>
       <c r="P8" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-3.8</v>
+        <v>43</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -930,61 +939,58 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>reports/cote-d-ivoire-sovereign-credit.md</t>
+          <t>reports/cameroon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Ba2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EFF</t>
-        </is>
+          <t>EFF/ECF ($3.5B) and RSF ($1.3B) completed Jun-26</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>12.7</v>
+        <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>7.5</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>50</v>
+        <v>55.1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-3.8</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -993,41 +999,61 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>reports/egypt-sovereign-credit.md</t>
+          <t>reports/cote-d-ivoire-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CCC-</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caa2</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>None (technical surveillance only)</t>
-        </is>
+          <t>EFF</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7.5</v>
       </c>
       <c r="P10" t="n">
-        <v>70</v>
-      </c>
-      <c r="U10" t="n">
-        <v>17.5</v>
+        <v>79.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1036,14 +1062,14 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>reports/gabon-sovereign-credit.md</t>
+          <t>reports/egypt-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1053,38 +1079,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>B-</t>
+          <t>CCC-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PCI (36-month, non-financing) after ECF $3.0B completed 27-Jul-26</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L11" t="n">
-        <v>12</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5.2</v>
+          <t>None (technical surveillance only)</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>70</v>
+      </c>
+      <c r="U11" t="n">
+        <v>17.5</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1093,31 +1105,31 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>reports/ghana-sovereign-credit.md</t>
+          <t>reports/gabon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Caa1</t>
@@ -1125,20 +1137,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>None (Article IV / Post-Financing Assessment)</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>-6.8</v>
+          <t>PCI (36-month, non-financing) after ECF $3.0B completed 27-Jul-26</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>80.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.506</v>
+        <v>5.2</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1147,14 +1162,14 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>reports/iraq-sovereign-credit.md</t>
+          <t>reports/ghana-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1164,44 +1179,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ba3</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EFF (4-year) + RSF</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6</v>
+          <t>None (Article IV / Post-Financing Assessment)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>-6.8</v>
       </c>
       <c r="L13" t="n">
-        <v>28.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="P13" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-2.8</v>
+        <v>9.6</v>
       </c>
       <c r="X13" t="n">
-        <v>3.95</v>
+        <v>0.506</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1210,61 +1216,61 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>reports/jordan-sovereign-credit.md</t>
+          <t>reports/iraq-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>None (previous EFF/ECF/RSF expired Apr-25; successor under discussion)</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>6.8</v>
+          <t>EFF (4-year) + RSF</t>
+        </is>
       </c>
       <c r="I14" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>14.702</v>
+        <v>28.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>68.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>33</v>
+        <v>-5.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.95</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1273,58 +1279,61 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>reports/kenya-sovereign-credit.md</t>
+          <t>reports/jordan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ba1</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FCL (2-year, precautionary)</t>
-        </is>
+          <t>None (previous EFF/ECF/RSF expired Apr-25; successor under discussion)</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>6.8</v>
       </c>
       <c r="I15" t="n">
-        <v>2.25</v>
+        <v>8.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.95</v>
       </c>
       <c r="L15" t="n">
-        <v>55.65</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.5</v>
+        <v>14.702</v>
       </c>
       <c r="P15" t="n">
-        <v>66.5</v>
+        <v>68.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3</v>
+        <v>-6.4</v>
       </c>
       <c r="S15" t="n">
-        <v>11.5</v>
+        <v>33</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -1333,58 +1342,58 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>reports/morocco-sovereign-credit.md</t>
+          <t>reports/kenya-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Ba1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>15.39</v>
+          <t>FCL (2-year, precautionary)</t>
+        </is>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
-      </c>
-      <c r="J16" t="n">
-        <v>7.61</v>
+        <v>2.25</v>
       </c>
       <c r="L16" t="n">
-        <v>54.98</v>
+        <v>55.65</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5.5</v>
       </c>
       <c r="P16" t="n">
-        <v>32.3</v>
+        <v>66.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-3</v>
       </c>
       <c r="S16" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -1393,34 +1402,34 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>reports/nigeria-sovereign-credit.md</t>
+          <t>reports/morocco-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Baa3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1428,20 +1437,23 @@
           <t>None (Article IV)</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>2.1</v>
+      <c r="H17" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="I17" t="n">
+        <v>23</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.61</v>
       </c>
       <c r="L17" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5</v>
+        <v>54.98</v>
       </c>
       <c r="P17" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.65</v>
+        <v>32.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>55</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -1450,47 +1462,55 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>reports/oman-sovereign-credit.md</t>
+          <t>reports/nigeria-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Caa2</t>
+          <t>Baa3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.8</v>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>132</v>
+        <v>34.7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.65</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -1499,58 +1519,47 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>reports/senegal-sovereign-credit.md</t>
+          <t>reports/oman-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>BB+</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PCI (36-month, non-financing)</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>3.3</v>
+          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
+        </is>
       </c>
       <c r="H19" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="I19" t="n">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-4.1</v>
+        <v>1.8</v>
       </c>
       <c r="P19" t="n">
-        <v>43.3</v>
+        <v>132</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -1559,29 +1568,29 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>reports/serbia-sovereign-credit.md</t>
+          <t>reports/senegal-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1591,29 +1600,26 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
+          <t>PCI (36-month, non-financing)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="I20" t="n">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="J20" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="L20" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-4.5</v>
+        <v>-4.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>43.3</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -1622,56 +1628,61 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>reports/south-africa-sovereign-credit.md</t>
+          <t>reports/serbia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BB</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Ba2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Frozen USD 1.9bn EFF agreed at staff level in Oct-22; no active Executive Board approval</t>
+          <t>None (Article IV)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L21" t="n">
+        <v>63.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>82</v>
+        <v>5.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.15</v>
+        <v>-4.5</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -1680,68 +1691,57 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>reports/tunisia-sovereign-credit.md</t>
+          <t>reports/south-africa-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ba3</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>Frozen USD 1.9bn EFF agreed at staff level in Oct-22; no active Executive Board approval</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>29.73</v>
+        <v>5.6</v>
       </c>
       <c r="I22" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="L22" t="n">
-        <v>61.56</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O22" t="n">
-        <v>31.8</v>
+        <v>1.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>29.5</v>
+        <v>82</v>
       </c>
       <c r="Q22" t="n">
         <v>-5.2</v>
       </c>
+      <c r="X22" t="n">
+        <v>0.15</v>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>08-Oct-26</t>
@@ -1749,14 +1749,14 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>reports/turkey-sovereign-credit.md</t>
+          <t>reports/tunisia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1766,41 +1766,50 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CCC+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>EFF (4-year)</t>
+          <t>None (Article IV)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>8.1</v>
+        <v>29.73</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J23" t="n">
-        <v>7.9</v>
+        <v>7.27</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-2.7</v>
       </c>
       <c r="L23" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>5.6</v>
+        <v>61.56</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O23" t="n">
+        <v>31.8</v>
       </c>
       <c r="P23" t="n">
-        <v>98.40000000000001</v>
+        <v>29.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-5.2</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -1809,64 +1818,58 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+          <t>reports/turkey-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CIS</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>CCC+</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>6.8</v>
+          <t>EFF (4-year)</t>
+        </is>
       </c>
       <c r="H24" t="n">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="L24" t="n">
-        <v>72.13</v>
+        <v>47.1</v>
       </c>
       <c r="M24" t="n">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="P24" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-2.1</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -1875,68 +1878,134 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>reports/uzbekistan-sovereign-credit.md</t>
+          <t>reports/ukraine-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CIS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>14</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="M25" t="n">
+        <v>12</v>
+      </c>
+      <c r="P25" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>reports/uzbekistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>CCC+</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Caa2</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Concluded 38-month US$1.3bn ECF in Jan-26; negotiating successor program</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>6.1</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>10.75</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>4.65</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>5.8</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>4.2</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>91</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>35</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>reports/zambia-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1526,40 +1526,66 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Caa2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
-        </is>
+          <t>38-month ECF ($35.7m SDR 26.43m review)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>7.8</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2</v>
+        <v>15.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>8.75</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8</v>
+        <v>-6.95</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>63</v>
       </c>
       <c r="P19" t="n">
-        <v>132</v>
+        <v>77.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.62</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -1568,58 +1594,47 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>reports/senegal-sovereign-credit.md</t>
+          <t>reports/rwanda-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BB+</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PCI (36-month, non-financing)</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>3.3</v>
+          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
+        </is>
       </c>
       <c r="H20" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="I20" t="n">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-4.1</v>
+        <v>1.8</v>
       </c>
       <c r="P20" t="n">
-        <v>43.3</v>
+        <v>132</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -1628,29 +1643,29 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>reports/serbia-sovereign-credit.md</t>
+          <t>reports/senegal-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1660,29 +1675,26 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
+          <t>PCI (36-month, non-financing)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>3.3</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="I21" t="n">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="J21" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="L21" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-4.5</v>
+        <v>-4.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>43.3</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -1691,56 +1703,61 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>reports/south-africa-sovereign-credit.md</t>
+          <t>reports/serbia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BB</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Ba2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Frozen USD 1.9bn EFF agreed at staff level in Oct-22; no active Executive Board approval</t>
+          <t>None (Article IV)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>63.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>82</v>
+        <v>5.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.15</v>
+        <v>-4.5</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -1749,68 +1766,57 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>reports/tunisia-sovereign-credit.md</t>
+          <t>reports/south-africa-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ba3</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>Frozen USD 1.9bn EFF agreed at staff level in Oct-22; no active Executive Board approval</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>29.73</v>
+        <v>5.6</v>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="L23" t="n">
-        <v>61.56</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O23" t="n">
-        <v>31.8</v>
+        <v>1.4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>29.5</v>
+        <v>82</v>
       </c>
       <c r="Q23" t="n">
         <v>-5.2</v>
       </c>
+      <c r="X23" t="n">
+        <v>0.15</v>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>08-Oct-26</t>
@@ -1818,14 +1824,14 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>reports/turkey-sovereign-credit.md</t>
+          <t>reports/tunisia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1835,41 +1841,50 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CCC+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EFF (4-year)</t>
+          <t>None (Article IV)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>8.1</v>
+        <v>29.73</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J24" t="n">
-        <v>7.9</v>
+        <v>7.27</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-2.7</v>
       </c>
       <c r="L24" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>5.6</v>
+        <v>61.56</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O24" t="n">
+        <v>31.8</v>
       </c>
       <c r="P24" t="n">
-        <v>98.40000000000001</v>
+        <v>29.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-5.2</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -1878,64 +1893,58 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+          <t>reports/turkey-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CIS</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>CCC+</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>6.8</v>
+          <t>EFF (4-year)</t>
+        </is>
       </c>
       <c r="H25" t="n">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="I25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="L25" t="n">
-        <v>72.13</v>
+        <v>47.1</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="P25" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-2.1</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -1944,68 +1953,134 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>reports/uzbekistan-sovereign-credit.md</t>
+          <t>reports/ukraine-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CIS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>14</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="M26" t="n">
+        <v>12</v>
+      </c>
+      <c r="P26" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>reports/uzbekistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>CCC+</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Caa2</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Concluded 38-month US$1.3bn ECF in Jan-26; negotiating successor program</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="H27" t="n">
         <v>6.1</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>10.75</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>4.65</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>5.8</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>4.2</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P27" t="n">
         <v>91</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>35</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>reports/zambia-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -575,56 +575,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Africa</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>B3</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5.97</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="L3" t="n">
-        <v>14.9</v>
+        <v>8.602</v>
       </c>
       <c r="M3" t="n">
-        <v>6.8</v>
+        <v>7.208</v>
       </c>
       <c r="P3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>13.06</v>
+        <v>51.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -633,64 +604,66 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>reports/angola-sovereign-credit.md</t>
+          <t>reports/albania-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CIS</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ba3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Precautionary SBA (3-year)</t>
-        </is>
-      </c>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>6.75</v>
+        <v>14.75</v>
       </c>
       <c r="J4" t="n">
-        <v>2.45</v>
+        <v>5.97</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>14.9</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>6.8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>49.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4</v>
+        <v>-2.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>13.06</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -699,14 +672,14 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>reports/armenia-sovereign-credit.md</t>
+          <t>reports/angola-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,44 +689,50 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Baa3</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>Precautionary SBA (3-year)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.2</v>
+        <v>5.25</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="L5" t="n">
         <v>6.5</v>
       </c>
-      <c r="K5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>15.36</v>
-      </c>
-      <c r="O5" t="n">
-        <v>8.300000000000001</v>
+      <c r="M5" t="n">
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.39</v>
+        <v>50.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-3.4</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -762,34 +741,34 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>reports/azerbaijan-sovereign-credit.md</t>
+          <t>reports/armenia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>CIS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Baa3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -797,14 +776,32 @@
           <t>None (Article IV)</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>15.36</v>
+      </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>4.954</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>134</v>
+        <v>18.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>-11</v>
+        <v>1.8</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.39</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -813,67 +810,58 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>reports/bahrain-sovereign-credit.md</t>
+          <t>reports/azerbaijan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ba3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blended 42-month EFF/ECF ($638m) and RSF ($200m) completed 25-Feb-26</t>
+          <t>None (Article IV)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.5</v>
+        <v>3.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>14</v>
-      </c>
-      <c r="T7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.85</v>
+        <v>-11</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -882,55 +870,67 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>reports/benin-sovereign-credit.md</t>
+          <t>reports/bahrain-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Post-Financing Assessment (PFA); ECF/EFF/RSF completed Jul-25</t>
-        </is>
+          <t>Blended 42-month EFF/ECF ($638m) and RSF ($200m) completed 25-Feb-26</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>7.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>30</v>
+        <v>1.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-5.5</v>
       </c>
       <c r="P8" t="n">
-        <v>43</v>
+        <v>54</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.6</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T8" t="n">
-        <v>12</v>
+        <v>14.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.85</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -939,14 +939,14 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>reports/cameroon-sovereign-credit.md</t>
+          <t>reports/benin-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,41 +956,53 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EFF/ECF ($3.5B) and RSF ($1.3B) completed Jun-26</t>
+          <t>Post-Financing Assessment (PFA); ECF/EFF/RSF completed Jul-25</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.062</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.275</v>
+      </c>
+      <c r="O9" t="n">
+        <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>55.1</v>
+        <v>43</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.8</v>
+        <v>-1.7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="n">
+        <v>12</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -999,61 +1011,61 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>reports/cote-d-ivoire-sovereign-credit.md</t>
+          <t>reports/cameroon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Ba2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EFF</t>
-        </is>
+          <t>EFF/ECF ($3.5B) and RSF ($1.3B) completed Jun-26</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>12.7</v>
+        <v>1.2</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>7.5</v>
+        <v>1.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.1</v>
       </c>
       <c r="P10" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>50</v>
+        <v>55.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-3.8</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1062,41 +1074,73 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>reports/egypt-sovereign-credit.md</t>
+          <t>reports/cote-d-ivoire-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CCC-</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Caa2</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>None (technical surveillance only)</t>
-        </is>
+          <t>EFF</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>19</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>48.875</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7.5</v>
       </c>
       <c r="P11" t="n">
-        <v>70</v>
-      </c>
-      <c r="U11" t="n">
-        <v>17.5</v>
+        <v>79.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1105,55 +1149,34 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>reports/gabon-sovereign-credit.md</t>
+          <t>reports/egypt-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Africa</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>PCI (36-month, non-financing) after ECF $3.0B completed 27-Jul-26</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J12" t="n">
-        <v>8.800000000000001</v>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-2.4</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>3.784</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>1.781</v>
+      </c>
+      <c r="P12" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1.8</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1162,52 +1185,56 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>reports/ghana-sovereign-credit.md</t>
+          <t>reports/ethiopia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>B-</t>
+          <t>CCC-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>None (Article IV / Post-Financing Assessment)</t>
+          <t>None (technical surveillance only)</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-6.8</v>
+        <v>2.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>80.59999999999999</v>
+        <v>0.639</v>
       </c>
       <c r="M13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.506</v>
+        <v>4.247</v>
+      </c>
+      <c r="P13" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-10</v>
+      </c>
+      <c r="U13" t="n">
+        <v>17.5</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1216,61 +1243,34 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>reports/iraq-sovereign-credit.md</t>
+          <t>reports/gabon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Middle East</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Ba3</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>EFF (4-year) + RSF</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-5</v>
       </c>
       <c r="L14" t="n">
-        <v>28.5</v>
+        <v>6.157</v>
       </c>
       <c r="M14" t="n">
-        <v>9.199999999999999</v>
+        <v>3.017</v>
       </c>
       <c r="P14" t="n">
-        <v>83.59999999999999</v>
+        <v>35.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.95</v>
+        <v>-2.3</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>reports/jordan-sovereign-credit.md</t>
+          <t>reports/georgia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1296,44 +1296,50 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>None (previous EFF/ECF/RSF expired Apr-25; successor under discussion)</t>
-        </is>
+          <t>PCI (36-month, non-financing) after ECF $3.0B completed 27-Jul-26</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>4.8</v>
       </c>
       <c r="H15" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>8.75</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
-        <v>1.95</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10.1</v>
       </c>
       <c r="L15" t="n">
-        <v>14.702</v>
+        <v>12</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.2</v>
       </c>
       <c r="P15" t="n">
-        <v>68.5</v>
+        <v>53</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>33</v>
+        <v>-2.3</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -1342,14 +1348,14 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>reports/kenya-sovereign-credit.md</t>
+          <t>reports/ghana-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1359,41 +1365,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ba1</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FCL (2-year, precautionary)</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.25</v>
+          <t>None (Article IV / Post-Financing Assessment)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-5.3</v>
       </c>
       <c r="L16" t="n">
-        <v>55.65</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="P16" t="n">
-        <v>66.5</v>
+        <v>61.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>11.5</v>
+        <v>-7.9</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.506</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -1402,58 +1411,67 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>reports/morocco-sovereign-credit.md</t>
+          <t>reports/iraq-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>15.39</v>
+          <t>EFF (4-year) + RSF</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2.7</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
-      </c>
-      <c r="J17" t="n">
-        <v>7.61</v>
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-6.2</v>
       </c>
       <c r="L17" t="n">
-        <v>54.98</v>
+        <v>28.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>55</v>
+        <v>83.59999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.95</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -1462,55 +1480,70 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>reports/nigeria-sovereign-credit.md</t>
+          <t>reports/jordan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Baa3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>None (previous EFF/ECF/RSF expired Apr-25; successor under discussion)</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>18.38</v>
+        <v>14.702</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>4.632</v>
       </c>
       <c r="P18" t="n">
-        <v>34.7</v>
+        <v>68.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.65</v>
+        <v>-6.4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>33</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -1519,73 +1552,34 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>reports/oman-sovereign-credit.md</t>
+          <t>reports/kenya-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rwanda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>38-month ECF ($35.7m SDR 26.43m review)</t>
-        </is>
-      </c>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H19" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="I19" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-6.95</v>
+        <v>2.8</v>
       </c>
       <c r="K19" t="n">
-        <v>-15</v>
+        <v>-19.4</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>2.196</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>63</v>
+        <v>3.947</v>
       </c>
       <c r="P19" t="n">
-        <v>77.5</v>
+        <v>62.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.62</v>
+        <v>-4</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -1594,47 +1588,64 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>reports/rwanda-sovereign-credit.md</t>
+          <t>reports/montenegro-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Caa2</t>
+          <t>Ba1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1.2</v>
+          <t>FCL (2-year, precautionary)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>4.9</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.5</v>
       </c>
       <c r="P20" t="n">
-        <v>132</v>
+        <v>66.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>11.5</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -1643,58 +1654,34 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>reports/senegal-sovereign-credit.md</t>
+          <t>reports/morocco-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Serbia</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>BB+</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>BBB-</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Ba2</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>PCI (36-month, non-financing)</t>
-        </is>
-      </c>
+          <t>Mozambique</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.55</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.1</v>
+        <v>-43</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.843</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.44</v>
       </c>
       <c r="P21" t="n">
-        <v>43.3</v>
+        <v>106.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-6.5</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -1703,61 +1690,34 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>reports/serbia-sovereign-credit.md</t>
+          <t>reports/mozambique-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Africa</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Ba2</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.85</v>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>2.4</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.6</v>
+        <v>-15.7</v>
       </c>
       <c r="L22" t="n">
-        <v>63.5</v>
+        <v>3.105</v>
       </c>
       <c r="M22" t="n">
-        <v>5.8</v>
+        <v>3.958</v>
+      </c>
+      <c r="P22" t="n">
+        <v>70.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5</v>
+        <v>-6.1</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -1766,56 +1726,70 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>reports/south-africa-sovereign-credit.md</t>
+          <t>reports/namibia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Frozen USD 1.9bn EFF agreed at staff level in Oct-22; no active Executive Board approval</t>
-        </is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>4.1</v>
       </c>
       <c r="H23" t="n">
-        <v>5.6</v>
+        <v>15.39</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4</v>
+        <v>7.61</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>54.98</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>7.118</v>
       </c>
       <c r="P23" t="n">
-        <v>82</v>
+        <v>32.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.15</v>
+        <v>-4.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>55</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -1824,67 +1798,34 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>reports/tunisia-sovereign-credit.md</t>
+          <t>reports/nigeria-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Ba3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>29.73</v>
-      </c>
-      <c r="I24" t="n">
-        <v>37</v>
-      </c>
-      <c r="J24" t="n">
-        <v>7.27</v>
+          <t>North Macedonia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>3.1</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.7</v>
+        <v>-5</v>
       </c>
       <c r="L24" t="n">
-        <v>61.56</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O24" t="n">
-        <v>31.8</v>
+        <v>5.804</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4.566</v>
       </c>
       <c r="P24" t="n">
-        <v>29.5</v>
+        <v>53.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.2</v>
+        <v>-4.2</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -1893,58 +1834,58 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>reports/turkey-sovereign-credit.md</t>
+          <t>reports/north-macedonia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CCC+</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Baa3</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EFF (4-year)</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>16</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7.9</v>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7.5</v>
       </c>
       <c r="L25" t="n">
-        <v>47.1</v>
+        <v>18.38</v>
       </c>
       <c r="M25" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
-        <v>98.40000000000001</v>
+        <v>34.7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.65</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -1953,64 +1894,34 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+          <t>reports/oman-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CIS</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Ba2</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>14</v>
-      </c>
-      <c r="J26" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.4</v>
       </c>
       <c r="L26" t="n">
-        <v>72.13</v>
+        <v>26.456</v>
       </c>
       <c r="M26" t="n">
-        <v>12</v>
+        <v>3.755</v>
       </c>
       <c r="P26" t="n">
-        <v>27</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.1</v>
+        <v>-3.2</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -2019,68 +1930,664 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>reports/uzbekistan-sovereign-credit.md</t>
+          <t>reports/pakistan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>38-month ECF ($35.7m SDR 26.43m review)</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-6.95</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>63</v>
+      </c>
+      <c r="P27" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>reports/rwanda-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Caa2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>reports/senegal-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BB+</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PCI (36-month, non-financing)</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>34.151</v>
+      </c>
+      <c r="M29" t="n">
+        <v>6.161</v>
+      </c>
+      <c r="P29" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>reports/serbia-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>reports/south-africa-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="M31" t="n">
+        <v>5.749</v>
+      </c>
+      <c r="P31" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>reports/tajikistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Middle East</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Caa1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Frozen USD 1.9bn EFF agreed at staff level in Oct-22; no active Executive Board approval</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>9.343999999999999</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>reports/tunisia-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BB-</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BB-</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ba3</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="I33" t="n">
+        <v>37</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L33" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="M33" t="n">
+        <v>5.128</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O33" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="P33" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>reports/turkey-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CCC+</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>EFF (4-year)</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>16</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P34" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>reports/ukraine-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CIS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>14</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="M35" t="n">
+        <v>12</v>
+      </c>
+      <c r="P35" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>reports/uzbekistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>CCC+</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Caa2</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Concluded 38-month US$1.3bn ECF in Jan-26; negotiating successor program</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="G36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H36" t="n">
         <v>6.1</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I36" t="n">
         <v>10.75</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J36" t="n">
         <v>4.65</v>
       </c>
-      <c r="L27" t="n">
+      <c r="K36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L36" t="n">
         <v>5.8</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M36" t="n">
         <v>4.2</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P36" t="n">
         <v>91</v>
       </c>
-      <c r="S27" t="n">
+      <c r="Q36" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="S36" t="n">
         <v>35</v>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
         <is>
           <t>reports/zambia-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -1808,24 +1808,49 @@
           <t>North Macedonia</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BB+</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BB-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PLL concluded Nov-24</t>
+        </is>
+      </c>
       <c r="G24" t="n">
         <v>3.1</v>
       </c>
+      <c r="I24" t="n">
+        <v>4.25</v>
+      </c>
       <c r="K24" t="n">
         <v>-5</v>
       </c>
       <c r="L24" t="n">
-        <v>5.804</v>
+        <v>5.51</v>
       </c>
       <c r="M24" t="n">
-        <v>4.566</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>53.1</v>
+        <v>55.2</v>
       </c>
       <c r="Q24" t="n">
         <v>-4.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.16</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -548,25 +548,40 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>REER z-score (10y) (sd)</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>Reserves, 12m change (%)</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>Terms of trade, 12m change (%)</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
           <t>Eurobonds outstanding (USD bn)</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>10y spread (bp)</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>5y CDS (bp)</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>As of</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AE2" s="1" t="inlineStr">
         <is>
           <t>Report</t>
         </is>
@@ -576,20 +591,37 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>Albania</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Europe (Western Balkans)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>3.4</v>
       </c>
+      <c r="H3" t="n">
+        <v>3.3508</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.85</v>
+      </c>
       <c r="K3" t="n">
         <v>-2.8</v>
       </c>
       <c r="L3" t="n">
-        <v>8.602</v>
+        <v>9.347</v>
       </c>
       <c r="M3" t="n">
-        <v>7.208</v>
+        <v>7.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>39.7</v>
       </c>
       <c r="P3" t="n">
         <v>51.5</v>
@@ -597,12 +629,18 @@
       <c r="Q3" t="n">
         <v>-2</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="Y3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>reports/albania-sovereign-credit.md</t>
         </is>
@@ -616,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -662,15 +700,21 @@
       <c r="Q4" t="n">
         <v>-2.4</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA4" t="n">
         <v>13.06</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>reports/angola-sovereign-credit.md</t>
         </is>
@@ -684,7 +728,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CIS</t>
+          <t>Caucasus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -704,7 +748,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Precautionary SBA (3-year)</t>
+          <t>Stand-By Arrangement (3-year, precautionary)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -734,12 +778,21 @@
       <c r="Q5" t="n">
         <v>-3.4</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="X5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>reports/armenia-sovereign-credit.md</t>
         </is>
@@ -753,7 +806,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIS</t>
+          <t>CEEMEA (South Caucasus)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -773,15 +826,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>None (Article IV surveillance only)</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1.2</v>
       </c>
+      <c r="H6" t="n">
+        <v>3.5</v>
+      </c>
       <c r="I6" t="n">
         <v>6.5</v>
       </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
       <c r="K6" t="n">
         <v>10.5</v>
       </c>
@@ -800,15 +859,21 @@
       <c r="Q6" t="n">
         <v>1.8</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AA6" t="n">
         <v>1.39</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>reports/azerbaijan-sovereign-credit.md</t>
         </is>
@@ -822,7 +887,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>MENA / GCC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -840,35 +905,46 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>-0.5</v>
       </c>
+      <c r="H7" t="n">
+        <v>2.9329</v>
+      </c>
       <c r="K7" t="n">
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>5.27</v>
+        <v>6.671</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q7" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
+        <v>10.8</v>
+      </c>
+      <c r="S7" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>reports/bahrain-sovereign-credit.md</t>
         </is>
@@ -882,7 +958,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Sub-Saharan Africa (WAEMU)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -902,11 +978,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blended 42-month EFF/ECF ($638m) and RSF ($200m) completed 25-Feb-26</t>
+          <t>EFF/ECF/RSF (42-month blended) completed</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -929,15 +1005,18 @@
       <c r="T8" t="n">
         <v>14.5</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.85</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>reports/benin-sovereign-credit.md</t>
         </is>
@@ -946,352 +1025,378 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Africa</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Post-Financing Assessment (PFA); ECF/EFF/RSF completed Jul-25</t>
-        </is>
-      </c>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>4.2234</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.529999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.1</v>
+        <v>-2.7</v>
       </c>
       <c r="L9" t="n">
-        <v>5.062</v>
+        <v>372.615</v>
       </c>
       <c r="M9" t="n">
-        <v>5.275</v>
-      </c>
-      <c r="O9" t="n">
-        <v>30</v>
+        <v>8.420999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>43</v>
+        <v>96.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="S9" t="n">
-        <v>20</v>
-      </c>
-      <c r="T9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>reports/cameroon-sovereign-credit.md</t>
+        <v>-7.7</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>reports/brazil-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Sub-Saharan Africa (CEMAC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EFF/ECF ($3.5B) and RSF ($1.3B) completed Jun-26</t>
+          <t>None active; ECF/EFF/RSF arrangements completed Jul-25, now annual Post-Financing Assessment</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1</v>
+        <v>-5.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.275</v>
+      </c>
+      <c r="O10" t="n">
+        <v>30</v>
       </c>
       <c r="P10" t="n">
-        <v>55.1</v>
+        <v>43</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>reports/cote-d-ivoire-sovereign-credit.md</t>
+        <v>-1.7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="n">
+        <v>12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>reports/cameroon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Middle East</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>EFF</t>
-        </is>
-      </c>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>12.7</v>
+        <v>4.1322</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>6.3</v>
+        <v>0.37</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.2</v>
+        <v>-0.8</v>
       </c>
       <c r="L11" t="n">
-        <v>48.875</v>
+        <v>51.858</v>
       </c>
       <c r="M11" t="n">
-        <v>7.5</v>
+        <v>4.217</v>
       </c>
       <c r="P11" t="n">
-        <v>79.7</v>
+        <v>42.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>-12.1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>reports/egypt-sovereign-credit.md</t>
+        <v>-2.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>reports/chile-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>9.199999999999999</v>
+        <v>2.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.2417</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.76</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="L12" t="n">
-        <v>3.784</v>
+        <v>66.304</v>
       </c>
       <c r="M12" t="n">
-        <v>1.781</v>
+        <v>7.268</v>
       </c>
       <c r="P12" t="n">
-        <v>40.4</v>
+        <v>60.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>reports/ethiopia-sovereign-credit.md</t>
+        <v>-5.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>reports/colombia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Sub-Saharan Africa (WAEMU)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CCC-</t>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Caa2</t>
+          <t>Ba2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>None (technical surveillance only)</t>
+          <t>EFF/ECF (40-month, US$3.5B) and RSF (US$1.3B); final reviews completed Jun-26</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2.7</v>
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.8</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4.247</v>
+        <v>-1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>70</v>
+        <v>55.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10</v>
-      </c>
-      <c r="U13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>reports/gabon-sovereign-credit.md</t>
+        <v>-3.8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>reports/cote-d-ivoire-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.922</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.83</v>
       </c>
       <c r="K14" t="n">
-        <v>-5</v>
+        <v>-1.5</v>
       </c>
       <c r="L14" t="n">
-        <v>6.157</v>
+        <v>184.565</v>
       </c>
       <c r="M14" t="n">
-        <v>3.017</v>
+        <v>7.644</v>
       </c>
       <c r="P14" t="n">
-        <v>35.1</v>
+        <v>46.4</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.3</v>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>reports/georgia-sovereign-credit.md</t>
+      <c r="X14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>reports/czech-republic-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1301,7 +1406,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1311,511 +1416,589 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PCI (36-month, non-financing) after ECF $3.0B completed 27-Jul-26</t>
+          <t>EFF (with RSF)</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>12.7</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>8.800000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="K15" t="n">
-        <v>10.1</v>
+        <v>-4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>53.559</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="P15" t="n">
-        <v>53</v>
+        <v>79.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>reports/ghana-sovereign-credit.md</t>
+        <v>-12.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>reports/egypt-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>RD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>Caa3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>None (Article IV / Post-Financing Assessment)</t>
+          <t>Extended Credit Facility (48-month)</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-6.8</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13.4</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.3</v>
+        <v>-2.4</v>
       </c>
       <c r="L16" t="n">
-        <v>80.59999999999999</v>
+        <v>3.784</v>
       </c>
       <c r="M16" t="n">
-        <v>9.6</v>
+        <v>1.781</v>
       </c>
       <c r="P16" t="n">
-        <v>61.7</v>
+        <v>40.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>reports/iraq-sovereign-credit.md</t>
+        <v>-1.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>reports/ethiopia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Sub-Saharan Africa (CEMAC)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>BB-</t>
+          <t>CCC-</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ba3</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EFF (4-year) + RSF</t>
+          <t>None (2021 EFF expired; technical surveillance mission 14-25 Sep-26, no SLA)</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>2.7</v>
       </c>
-      <c r="I17" t="n">
-        <v>6</v>
+      <c r="H17" t="n">
+        <v>1.597</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.2</v>
+        <v>-4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>28.5</v>
+        <v>0.673</v>
       </c>
       <c r="M17" t="n">
-        <v>9.199999999999999</v>
+        <v>4.247</v>
       </c>
       <c r="P17" t="n">
-        <v>83.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-2.8</v>
+        <v>-10</v>
+      </c>
+      <c r="U17" t="n">
+        <v>17.5</v>
       </c>
       <c r="X17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>reports/jordan-sovereign-credit.md</t>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-51.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>reports/gabon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Africa</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>None (previous EFF/ECF/RSF expired Apr-25; successor under discussion)</t>
-        </is>
-      </c>
+          <t>Caucasus</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="H18" t="n">
-        <v>6.8</v>
+        <v>5.6478</v>
       </c>
       <c r="I18" t="n">
-        <v>8.75</v>
+        <v>8.25</v>
       </c>
       <c r="J18" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.1</v>
+        <v>-5</v>
       </c>
       <c r="L18" t="n">
-        <v>14.702</v>
+        <v>8.138999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>4.632</v>
+        <v>3.017</v>
       </c>
       <c r="P18" t="n">
-        <v>68.5</v>
+        <v>35.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>33</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>reports/kenya-sovereign-credit.md</t>
+        <v>-2.3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>reports/georgia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Montenegro</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Caa1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>36-month non-financing Policy Coordination Instrument (PCI), following completion of the US$3.0B ECF</t>
+        </is>
+      </c>
       <c r="G19" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>14</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-19.4</v>
+        <v>10.1</v>
       </c>
       <c r="L19" t="n">
-        <v>2.196</v>
+        <v>12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.947</v>
+        <v>5.2</v>
       </c>
       <c r="P19" t="n">
-        <v>62.4</v>
+        <v>53</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>reports/montenegro-sovereign-credit.md</t>
+        <v>-2.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>reports/ghana-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Middle East</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BB+</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>BBB-</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Ba1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>FCL (2-year, precautionary)</t>
-        </is>
-      </c>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.2826</v>
       </c>
       <c r="I20" t="n">
-        <v>2.25</v>
+        <v>5.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.22</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.1</v>
+        <v>-0.4</v>
       </c>
       <c r="L20" t="n">
-        <v>55.65</v>
+        <v>73.621</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>3.495</v>
       </c>
       <c r="P20" t="n">
-        <v>66.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>reports/morocco-sovereign-credit.md</t>
+        <v>-5.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>reports/hungary-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.4412</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-43</v>
+        <v>-2</v>
       </c>
       <c r="L21" t="n">
-        <v>3.843</v>
+        <v>751.764</v>
       </c>
       <c r="M21" t="n">
-        <v>3.44</v>
+        <v>7.851</v>
       </c>
       <c r="P21" t="n">
-        <v>106.1</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>reports/mozambique-sovereign-credit.md</t>
+        <v>-7.4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>reports/india-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>2.4</v>
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.8821</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.87</v>
       </c>
       <c r="K22" t="n">
-        <v>-15.7</v>
+        <v>-1.1</v>
       </c>
       <c r="L22" t="n">
-        <v>3.105</v>
+        <v>146.492</v>
       </c>
       <c r="M22" t="n">
-        <v>3.958</v>
+        <v>5.514</v>
       </c>
       <c r="P22" t="n">
-        <v>70.5</v>
+        <v>41.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>reports/namibia-sovereign-credit.md</t>
+        <v>-2.9</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>reports/indonesia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>None active (Article IV surveillance and Post-Financing Assessment only; last SBA expired 2018)</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4.1</v>
+        <v>-6.8</v>
       </c>
       <c r="H23" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="I23" t="n">
-        <v>23</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7.61</v>
+        <v>3.0928</v>
       </c>
       <c r="K23" t="n">
-        <v>5.8</v>
+        <v>-5.3</v>
       </c>
       <c r="L23" t="n">
-        <v>54.98</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>7.118</v>
+        <v>9.6</v>
       </c>
       <c r="P23" t="n">
-        <v>32.3</v>
+        <v>53.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>reports/nigeria-sovereign-credit.md</t>
+        <v>-4.2</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.50625</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>reports/iraq-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1823,284 +2006,307 @@
           <t>BB-</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ba3</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PLL concluded Nov-24</t>
+          <t>4-year Extended Fund Facility (SDR 926.37m) plus RSF</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.7011</v>
       </c>
       <c r="I24" t="n">
-        <v>4.25</v>
+        <v>6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>-5</v>
+        <v>-6.2</v>
       </c>
       <c r="L24" t="n">
-        <v>5.51</v>
+        <v>28.5</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>55.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>reports/north-macedonia-sovereign-credit.md</t>
+        <v>-5.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>reports/jordan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Baa3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.95</v>
       </c>
       <c r="K25" t="n">
-        <v>7.5</v>
+        <v>-4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>18.38</v>
+        <v>14.702</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>4.632</v>
       </c>
       <c r="P25" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y25" t="n">
         <v>34.7</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>reports/oman-sovereign-credit.md</t>
+      <c r="Z25" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>reports/kenya-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.7817</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.97</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4</v>
+        <v>1.4</v>
       </c>
       <c r="L26" t="n">
-        <v>26.456</v>
+        <v>131.981</v>
       </c>
       <c r="M26" t="n">
-        <v>3.755</v>
+        <v>4.276</v>
       </c>
       <c r="P26" t="n">
-        <v>70.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>reports/pakistan-sovereign-credit.md</t>
+        <v>-3.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>reports/malaysia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rwanda</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>38-month ECF ($35.7m SDR 26.43m review)</t>
-        </is>
-      </c>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>7.8</v>
+        <v>1.6</v>
       </c>
       <c r="H27" t="n">
-        <v>15.7</v>
+        <v>3.2619</v>
       </c>
       <c r="I27" t="n">
-        <v>8.75</v>
+        <v>6.5</v>
       </c>
       <c r="J27" t="n">
-        <v>-6.95</v>
+        <v>3.24</v>
       </c>
       <c r="K27" t="n">
-        <v>-15</v>
+        <v>-0.4</v>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>265.969</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>63</v>
+        <v>3.73</v>
       </c>
       <c r="P27" t="n">
-        <v>77.5</v>
+        <v>62.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.8</v>
+        <v>-4.4</v>
       </c>
       <c r="X27" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>reports/rwanda-sovereign-credit.md</t>
+        <v>1.8</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>reports/mexico-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Africa</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Caa2</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Staff-level agreement on successor arrangement (replaces suspended $1.8B facility)</t>
-        </is>
-      </c>
+          <t>Western Balkans</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.8</v>
+        <v>3.6043</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.2</v>
+        <v>-19.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.196</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.947</v>
       </c>
       <c r="P28" t="n">
-        <v>132</v>
+        <v>63.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>reports/senegal-sovereign-credit.md</t>
+        <v>-4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>reports/montenegro-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2115,504 +2321,1476 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Ba1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PCI (36-month, non-financing)</t>
+          <t>Flexible Credit Line (2-year, precautionary)</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="H29" t="n">
-        <v>2.2</v>
+        <v>-0.3333</v>
       </c>
       <c r="I29" t="n">
-        <v>5.75</v>
+        <v>2.25</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>2.58</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.1</v>
+        <v>-3.1</v>
       </c>
       <c r="L29" t="n">
-        <v>34.151</v>
+        <v>55.65</v>
       </c>
       <c r="M29" t="n">
-        <v>6.161</v>
+        <v>5.5</v>
       </c>
       <c r="P29" t="n">
-        <v>43.3</v>
+        <v>67.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>reports/serbia-sovereign-credit.md</t>
+        <v>-3.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>reports/morocco-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>CCC (LC: SD)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa3</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>Extended Credit Facility (2022) lapsed Apr-25; successor under discussion</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H30" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="I30" t="n">
-        <v>7.25</v>
+        <v>9.25</v>
       </c>
       <c r="J30" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.6</v>
+        <v>-43</v>
       </c>
       <c r="L30" t="n">
-        <v>63.5</v>
+        <v>3.9</v>
       </c>
       <c r="M30" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="P30" t="n">
-        <v>78.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="Q30" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>reports/south-africa-sovereign-credit.md</t>
+        <v>-6.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>reports/mozambique-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Africa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>2.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.4106</v>
       </c>
       <c r="K31" t="n">
-        <v>6.3</v>
+        <v>-15.7</v>
       </c>
       <c r="L31" t="n">
-        <v>4.31</v>
+        <v>3.252</v>
       </c>
       <c r="M31" t="n">
-        <v>5.749</v>
+        <v>3.958</v>
       </c>
       <c r="P31" t="n">
-        <v>21.9</v>
+        <v>70.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>reports/tajikistan-sovereign-credit.md</t>
+        <v>-6.1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>reports/namibia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Frozen USD 1.9bn EFF agreed at staff level in Oct-22; no active Executive Board approval</t>
-        </is>
-      </c>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="H32" t="n">
-        <v>5.6</v>
+        <v>15.39</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>1.4</v>
+        <v>7.61</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.2</v>
+        <v>5.8</v>
       </c>
       <c r="L32" t="n">
-        <v>9.343999999999999</v>
+        <v>54.98</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P32" t="n">
-        <v>82</v>
+        <v>32.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>-5.2</v>
+        <v>-4.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>55</v>
       </c>
       <c r="X32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>reports/tunisia-sovereign-credit.md</t>
+        <v>-0.51</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>reports/nigeria-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>CEEMEA - Western Balkans</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>BB+</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>BB-</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Ba3</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>PLL concluded Nov-24</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H33" t="n">
-        <v>29.73</v>
+        <v>2.5729</v>
       </c>
       <c r="I33" t="n">
-        <v>37</v>
+        <v>4.25</v>
       </c>
       <c r="J33" t="n">
-        <v>7.27</v>
+        <v>1.68</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.7</v>
+        <v>-5</v>
       </c>
       <c r="L33" t="n">
-        <v>61.56</v>
+        <v>5.51</v>
       </c>
       <c r="M33" t="n">
-        <v>5.128</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O33" t="n">
-        <v>31.8</v>
+        <v>4.2</v>
       </c>
       <c r="P33" t="n">
-        <v>29.5</v>
+        <v>55.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>reports/turkey-sovereign-credit.md</t>
+        <v>-4.2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>reports/north-macedonia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Middle East (GCC)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CCC+</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Baa3</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EFF (4-year)</t>
+          <t>None (Article IV)</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H34" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>16</v>
-      </c>
-      <c r="J34" t="n">
-        <v>7.9</v>
+        <v>3.3771</v>
       </c>
       <c r="K34" t="n">
-        <v>-18.9</v>
+        <v>2.5</v>
       </c>
       <c r="L34" t="n">
-        <v>47.1</v>
+        <v>18.38</v>
       </c>
       <c r="M34" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>98.40000000000001</v>
+        <v>34.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>-18.4</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+        <v>0.6</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>reports/oman-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CIS</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Ba2</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
+          <t>South Asia</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="H35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>14</v>
-      </c>
-      <c r="J35" t="n">
-        <v>7.8</v>
+        <v>10.2591</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.3</v>
+        <v>-0.4</v>
       </c>
       <c r="L35" t="n">
-        <v>72.13</v>
+        <v>27.993</v>
       </c>
       <c r="M35" t="n">
-        <v>12</v>
+        <v>3.755</v>
       </c>
       <c r="P35" t="n">
-        <v>27</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Q35" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>reports/uzbekistan-sovereign-credit.md</t>
+        <v>-3.2</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>reports/pakistan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.0636</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>95.26900000000001</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10.423</v>
+      </c>
+      <c r="P36" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>reports/peru-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6.3629</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>103.316</v>
+      </c>
+      <c r="M37" t="n">
+        <v>7.306</v>
+      </c>
+      <c r="P37" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>reports/philippines-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.2123</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>304.971</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5.861</v>
+      </c>
+      <c r="P38" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>reports/poland-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="L39" t="n">
+        <v>90.04300000000001</v>
+      </c>
+      <c r="M39" t="n">
+        <v>5.528</v>
+      </c>
+      <c r="P39" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>reports/romania-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ECF (38-month, reported)</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-6.95</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4</v>
+      </c>
+      <c r="O40" t="n">
+        <v>63</v>
+      </c>
+      <c r="P40" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>reports/rwanda-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa (WAEMU)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Caa2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Successor financing arrangement (staff-level agreement) replacing suspended EFF/ECF approved Jun-23</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="P41" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>reports/senegal-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Western Balkans / CEEMEA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BB+</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Policy Coordination Instrument (36-month, non-financing, through late 2027)</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="M42" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>reports/serbia-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L43" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="M43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P43" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>reports/south-africa-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Central Asia</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>6</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.0609</v>
+      </c>
+      <c r="K44" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L44" t="n">
+        <v>6.395</v>
+      </c>
+      <c r="M44" t="n">
+        <v>5.749</v>
+      </c>
+      <c r="P44" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>reports/tajikistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.5265</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L45" t="n">
+        <v>283.137</v>
+      </c>
+      <c r="M45" t="n">
+        <v>8.051</v>
+      </c>
+      <c r="P45" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>reports/thailand-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MENA / North Africa</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Caa1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>USD 1.9bn Extended Fund Facility, staff-level agreement Oct-22, never approved by the Executive Board; frozen</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I46" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>9.079000000000001</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3</v>
+      </c>
+      <c r="P46" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>reports/tunisia-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CEEMEA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BB-</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BB-</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ba3</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H47" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="I47" t="n">
+        <v>37</v>
+      </c>
+      <c r="J47" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L47" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="M47" t="n">
+        <v>5.128</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O47" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="P47" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>reports/turkey-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CEEMEA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CCC+</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Extended Fund Facility (EFF), 4-year</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>16</v>
+      </c>
+      <c r="J48" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="L48" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P48" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="X48" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>reports/ukraine-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CIS / Central Asia</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>None active (annual Article IV surveillance and technical assistance only)</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I49" t="n">
+        <v>14</v>
+      </c>
+      <c r="J49" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="L49" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="M49" t="n">
+        <v>12</v>
+      </c>
+      <c r="P49" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>reports/uzbekistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Africa</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>CCC+</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Caa2</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Concluded 38-month US$1.3bn ECF in Jan-26; negotiating successor program</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>38-month ECF concluded Jan-26 (sixth and final review); successor programme under negotiation</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
         <v>4.3</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H50" t="n">
         <v>6.1</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I50" t="n">
         <v>10.75</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J50" t="n">
         <v>4.65</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K50" t="n">
         <v>0.9</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L50" t="n">
         <v>5.8</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M50" t="n">
         <v>4.2</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P50" t="n">
         <v>91</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q50" t="n">
         <v>-4.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S50" t="n">
         <v>35</v>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
+      <c r="X50" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
         <is>
           <t>reports/zambia-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -3528,13 +3528,13 @@
         <v>-2.7</v>
       </c>
       <c r="L47" t="n">
-        <v>61.56</v>
+        <v>174.4</v>
       </c>
       <c r="M47" t="n">
         <v>5.128</v>
       </c>
       <c r="N47" t="n">
-        <v>0.36</v>
+        <v>1.02</v>
       </c>
       <c r="O47" t="n">
         <v>31.8</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -3242,7 +3242,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BB (foreign) / BB+ (local)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3271,7 +3271,7 @@
         <v>-1.6</v>
       </c>
       <c r="L43" t="n">
-        <v>63.5</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>5.8</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE50"/>
+  <dimension ref="A1:AG50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -558,30 +558,40 @@
       </c>
       <c r="Z2" s="1" t="inlineStr">
         <is>
+          <t>Reserves net of 1y drains (USD bn)</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>Current account, last 4Q (USD bn)</t>
+        </is>
+      </c>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
           <t>Terms of trade, 12m change (%)</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Eurobonds outstanding (USD bn)</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>10y spread (bp)</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AE2" s="1" t="inlineStr">
         <is>
           <t>5y CDS (bp)</t>
         </is>
       </c>
-      <c r="AD2" s="1" t="inlineStr">
+      <c r="AF2" s="1" t="inlineStr">
         <is>
           <t>As of</t>
         </is>
       </c>
-      <c r="AE2" s="1" t="inlineStr">
+      <c r="AG2" s="1" t="inlineStr">
         <is>
           <t>Report</t>
         </is>
@@ -633,14 +643,20 @@
         <v>19.3</v>
       </c>
       <c r="Z3" t="n">
+        <v>8.401999999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AB3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>reports/albania-sovereign-credit.md</t>
         </is>
@@ -704,17 +720,23 @@
         <v>4.2</v>
       </c>
       <c r="Z4" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>13.06</v>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>reports/angola-sovereign-credit.md</t>
         </is>
@@ -785,14 +807,20 @@
         <v>53.9</v>
       </c>
       <c r="Z5" t="n">
+        <v>3.708</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="AB5" t="n">
         <v>-1.1</v>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>reports/armenia-sovereign-credit.md</t>
         </is>
@@ -862,18 +890,21 @@
       <c r="Y6" t="n">
         <v>29.7</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AB6" t="n">
         <v>14.4</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>1.39</v>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>reports/azerbaijan-sovereign-credit.md</t>
         </is>
@@ -936,15 +967,18 @@
       <c r="Y7" t="n">
         <v>86.40000000000001</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB7" t="n">
         <v>5.3</v>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>reports/bahrain-sovereign-credit.md</t>
         </is>
@@ -1005,18 +1039,18 @@
       <c r="T8" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>-1.1</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>2.85</v>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>reports/benin-sovereign-credit.md</t>
         </is>
@@ -1063,14 +1097,20 @@
         <v>6.2</v>
       </c>
       <c r="Z9" t="n">
+        <v>373.651</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-59.09</v>
+      </c>
+      <c r="AB9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>reports/brazil-sovereign-credit.md</t>
         </is>
@@ -1143,15 +1183,18 @@
       <c r="Y10" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="AB10" t="n">
         <v>-1.2</v>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>reports/cameroon-sovereign-credit.md</t>
         </is>
@@ -1198,14 +1241,20 @@
         <v>11.8</v>
       </c>
       <c r="Z11" t="n">
+        <v>47.964</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.4</v>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>reports/chile-sovereign-credit.md</t>
         </is>
@@ -1252,14 +1301,20 @@
         <v>6.6</v>
       </c>
       <c r="Z12" t="n">
+        <v>59.708</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-12.91</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2.9</v>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
         <is>
           <t>reports/colombia-sovereign-credit.md</t>
         </is>
@@ -1320,15 +1375,15 @@
       <c r="X13" t="n">
         <v>0.6</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>-7.3</v>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
         <is>
           <t>reports/cote-d-ivoire-sovereign-credit.md</t>
         </is>
@@ -1375,14 +1430,20 @@
         <v>11</v>
       </c>
       <c r="Z14" t="n">
+        <v>171.989</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB14" t="n">
         <v>-1.8</v>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
         <is>
           <t>reports/czech-republic-sovereign-credit.md</t>
         </is>
@@ -1447,7 +1508,7 @@
         <v>-12.1</v>
       </c>
       <c r="R15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -1456,14 +1517,20 @@
         <v>14.7</v>
       </c>
       <c r="Z15" t="n">
+        <v>17.224</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-16.76</v>
+      </c>
+      <c r="AB15" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
         <is>
           <t>reports/egypt-sovereign-credit.md</t>
         </is>
@@ -1527,18 +1594,21 @@
       <c r="Y16" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="AB16" t="n">
         <v>-2.8</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>1</v>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
         <is>
           <t>reports/ethiopia-sovereign-credit.md</t>
         </is>
@@ -1600,15 +1670,15 @@
       <c r="Y17" t="n">
         <v>-51.4</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>22.6</v>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
         <is>
           <t>reports/gabon-sovereign-credit.md</t>
         </is>
@@ -1660,14 +1730,20 @@
         <v>56.4</v>
       </c>
       <c r="Z18" t="n">
+        <v>7.255</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="AB18" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
         <is>
           <t>reports/georgia-sovereign-credit.md</t>
         </is>
@@ -1737,15 +1813,18 @@
       <c r="Y19" t="n">
         <v>11.9</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="AB19" t="n">
         <v>3.3</v>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
         <is>
           <t>reports/ghana-sovereign-credit.md</t>
         </is>
@@ -1792,14 +1871,20 @@
         <v>30.3</v>
       </c>
       <c r="Z20" t="n">
+        <v>66.95</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB20" t="n">
         <v>-1.1</v>
       </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
         <is>
           <t>reports/hungary-sovereign-credit.md</t>
         </is>
@@ -1846,14 +1931,20 @@
         <v>8.1</v>
       </c>
       <c r="Z21" t="n">
+        <v>715.745</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-28.25</v>
+      </c>
+      <c r="AB21" t="n">
         <v>-2.8</v>
       </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
         <is>
           <t>reports/india-sovereign-credit.md</t>
         </is>
@@ -1900,14 +1991,20 @@
         <v>-2.8</v>
       </c>
       <c r="Z22" t="n">
+        <v>75.541</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-14.36</v>
+      </c>
+      <c r="AB22" t="n">
         <v>0.4</v>
       </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
         <is>
           <t>reports/indonesia-sovereign-credit.md</t>
         </is>
@@ -1968,18 +2065,21 @@
       <c r="Y23" t="n">
         <v>-10.9</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AB23" t="n">
         <v>16.7</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>0.50625</v>
       </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
         <is>
           <t>reports/iraq-sovereign-credit.md</t>
         </is>
@@ -2050,17 +2150,23 @@
         <v>23</v>
       </c>
       <c r="Z24" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-3.11</v>
+      </c>
+      <c r="AB24" t="n">
         <v>-6.1</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>3.95</v>
       </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
         <is>
           <t>reports/jordan-sovereign-credit.md</t>
         </is>
@@ -2126,15 +2232,15 @@
       <c r="Y25" t="n">
         <v>34.7</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>-2.9</v>
       </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
         <is>
           <t>reports/kenya-sovereign-credit.md</t>
         </is>
@@ -2181,14 +2287,20 @@
         <v>7.5</v>
       </c>
       <c r="Z26" t="n">
+        <v>97.798</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1</v>
       </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
         <is>
           <t>reports/malaysia-sovereign-credit.md</t>
         </is>
@@ -2235,14 +2347,20 @@
         <v>6.8</v>
       </c>
       <c r="Z27" t="n">
+        <v>250.968</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AB27" t="n">
         <v>0.3</v>
       </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
         <is>
           <t>reports/mexico-sovereign-credit.md</t>
         </is>
@@ -2284,15 +2402,18 @@
       <c r="Y28" t="n">
         <v>26.1</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="AB28" t="n">
         <v>-1.6</v>
       </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
         <is>
           <t>reports/montenegro-sovereign-credit.md</t>
         </is>
@@ -2366,14 +2487,20 @@
         <v>18</v>
       </c>
       <c r="Z29" t="n">
+        <v>50.756</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-5.83</v>
+      </c>
+      <c r="AB29" t="n">
         <v>-3.2</v>
       </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
         <is>
           <t>reports/morocco-sovereign-credit.md</t>
         </is>
@@ -2440,18 +2567,21 @@
       <c r="Y30" t="n">
         <v>4.9</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="AB30" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>0.9</v>
       </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
         <is>
           <t>reports/mozambique-sovereign-credit.md</t>
         </is>
@@ -2493,15 +2623,15 @@
       <c r="Y31" t="n">
         <v>-6.3</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>0.8</v>
       </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
         <is>
           <t>reports/namibia-sovereign-credit.md</t>
         </is>
@@ -2570,18 +2700,18 @@
       <c r="Y32" t="n">
         <v>30.8</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>4.6</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>15.12</v>
       </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
         <is>
           <t>reports/nigeria-sovereign-credit.md</t>
         </is>
@@ -2646,18 +2776,18 @@
       <c r="Y33" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>-2.6</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>2.16</v>
       </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
         <is>
           <t>reports/north-macedonia-sovereign-credit.md</t>
         </is>
@@ -2718,15 +2848,15 @@
       <c r="Y34" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>15.6</v>
       </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
         <is>
           <t>reports/oman-sovereign-credit.md</t>
         </is>
@@ -2771,15 +2901,15 @@
       <c r="Y35" t="n">
         <v>22.8</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>-2.3</v>
       </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
         <is>
           <t>reports/pakistan-sovereign-credit.md</t>
         </is>
@@ -2825,15 +2955,15 @@
       <c r="Y36" t="n">
         <v>16.3</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AB36" t="n">
         <v>2.5</v>
       </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
         <is>
           <t>reports/peru-sovereign-credit.md</t>
         </is>
@@ -2879,15 +3009,15 @@
       <c r="Y37" t="n">
         <v>-2</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
         <v>-1.4</v>
       </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
         <is>
           <t>reports/philippines-sovereign-credit.md</t>
         </is>
@@ -2933,15 +3063,15 @@
       <c r="Y38" t="n">
         <v>16.9</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AB38" t="n">
         <v>-1.1</v>
       </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
         <is>
           <t>reports/poland-sovereign-credit.md</t>
         </is>
@@ -2987,15 +3117,15 @@
       <c r="Y39" t="n">
         <v>2.9</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AB39" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
         <is>
           <t>reports/romania-sovereign-credit.md</t>
         </is>
@@ -3065,18 +3195,18 @@
       <c r="Y40" t="n">
         <v>-16.4</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>-0</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>0.62</v>
       </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
         <is>
           <t>reports/rwanda-sovereign-credit.md</t>
         </is>
@@ -3129,18 +3259,18 @@
       <c r="Q41" t="n">
         <v>-6.7</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AB41" t="n">
         <v>-2.4</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>3.2</v>
       </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
         <is>
           <t>reports/senegal-sovereign-credit.md</t>
         </is>
@@ -3210,15 +3340,15 @@
       <c r="Y42" t="n">
         <v>7</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AB42" t="n">
         <v>-1.4</v>
       </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
         <is>
           <t>reports/serbia-sovereign-credit.md</t>
         </is>
@@ -3291,15 +3421,15 @@
       <c r="Y43" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AB43" t="n">
         <v>-0.9</v>
       </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
         <is>
           <t>reports/south-africa-sovereign-credit.md</t>
         </is>
@@ -3341,15 +3471,15 @@
       <c r="Y44" t="n">
         <v>45.9</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AB44" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
         <is>
           <t>reports/tajikistan-sovereign-credit.md</t>
         </is>
@@ -3395,15 +3525,15 @@
       <c r="Y45" t="n">
         <v>5.9</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AB45" t="n">
         <v>-3.9</v>
       </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
         <is>
           <t>reports/thailand-sovereign-credit.md</t>
         </is>
@@ -3468,18 +3598,18 @@
       <c r="Y46" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AB46" t="n">
         <v>-1.2</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AC46" t="n">
         <v>0.15</v>
       </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
         <is>
           <t>reports/tunisia-sovereign-credit.md</t>
         </is>
@@ -3552,14 +3682,20 @@
         <v>4.7</v>
       </c>
       <c r="Z47" t="n">
+        <v>137.109</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-38.89</v>
+      </c>
+      <c r="AB47" t="n">
         <v>-1</v>
       </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
         <is>
           <t>reports/turkey-sovereign-credit.md</t>
         </is>
@@ -3629,15 +3765,15 @@
       <c r="Y48" t="n">
         <v>5.7</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AB48" t="n">
         <v>-2.3</v>
       </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
         <is>
           <t>reports/ukraine-sovereign-credit.md</t>
         </is>
@@ -3704,12 +3840,12 @@
       <c r="Y49" t="n">
         <v>32</v>
       </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
         <is>
           <t>reports/uzbekistan-sovereign-credit.md</t>
         </is>
@@ -3782,15 +3918,15 @@
       <c r="Y50" t="n">
         <v>25.6</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AB50" t="n">
         <v>5.1</v>
       </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AE50" t="inlineStr">
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
         <is>
           <t>reports/zambia-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2623,6 +2623,12 @@
       <c r="Y31" t="n">
         <v>-6.3</v>
       </c>
+      <c r="Z31" t="n">
+        <v>2.151</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-1.86</v>
+      </c>
       <c r="AB31" t="n">
         <v>0.8</v>
       </c>
@@ -2700,6 +2706,9 @@
       <c r="Y32" t="n">
         <v>30.8</v>
       </c>
+      <c r="AA32" t="n">
+        <v>15.61</v>
+      </c>
       <c r="AB32" t="n">
         <v>4.6</v>
       </c>
@@ -2775,6 +2784,12 @@
       </c>
       <c r="Y33" t="n">
         <v>7.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.474</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-0.99</v>
       </c>
       <c r="AB33" t="n">
         <v>-2.6</v>
@@ -2901,6 +2916,9 @@
       <c r="Y35" t="n">
         <v>22.8</v>
       </c>
+      <c r="AA35" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="AB35" t="n">
         <v>-2.3</v>
       </c>
@@ -2955,6 +2973,12 @@
       <c r="Y36" t="n">
         <v>16.3</v>
       </c>
+      <c r="Z36" t="n">
+        <v>87.288</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>12.01</v>
+      </c>
       <c r="AB36" t="n">
         <v>2.5</v>
       </c>
@@ -3009,6 +3033,12 @@
       <c r="Y37" t="n">
         <v>-2</v>
       </c>
+      <c r="Z37" t="n">
+        <v>93.018</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-22.11</v>
+      </c>
       <c r="AB37" t="n">
         <v>-1.4</v>
       </c>
@@ -3063,6 +3093,12 @@
       <c r="Y38" t="n">
         <v>16.9</v>
       </c>
+      <c r="Z38" t="n">
+        <v>277.21</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-13.87</v>
+      </c>
       <c r="AB38" t="n">
         <v>-1.1</v>
       </c>
@@ -3117,6 +3153,12 @@
       <c r="Y39" t="n">
         <v>2.9</v>
       </c>
+      <c r="Z39" t="n">
+        <v>72.172</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-32.2</v>
+      </c>
       <c r="AB39" t="n">
         <v>-0.5</v>
       </c>
@@ -3195,6 +3237,12 @@
       <c r="Y40" t="n">
         <v>-16.4</v>
       </c>
+      <c r="Z40" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-1.98</v>
+      </c>
       <c r="AB40" t="n">
         <v>-0</v>
       </c>
@@ -3340,6 +3388,12 @@
       <c r="Y42" t="n">
         <v>7</v>
       </c>
+      <c r="Z42" t="n">
+        <v>30.033</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-4.36</v>
+      </c>
       <c r="AB42" t="n">
         <v>-1.4</v>
       </c>
@@ -3420,6 +3474,12 @@
       </c>
       <c r="Y43" t="n">
         <v>7.8</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>74.307</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-1.32</v>
       </c>
       <c r="AB43" t="n">
         <v>-0.9</v>
@@ -3471,6 +3531,9 @@
       <c r="Y44" t="n">
         <v>45.9</v>
       </c>
+      <c r="AA44" t="n">
+        <v>3.48</v>
+      </c>
       <c r="AB44" t="n">
         <v>-0.8</v>
       </c>
@@ -3525,6 +3588,12 @@
       <c r="Y45" t="n">
         <v>5.9</v>
       </c>
+      <c r="Z45" t="n">
+        <v>302.852</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>8.08</v>
+      </c>
       <c r="AB45" t="n">
         <v>-3.9</v>
       </c>
@@ -3597,6 +3666,9 @@
       </c>
       <c r="Y46" t="n">
         <v>6.8</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-1.33</v>
       </c>
       <c r="AB46" t="n">
         <v>-1.2</v>
@@ -3765,6 +3837,12 @@
       <c r="Y48" t="n">
         <v>5.7</v>
       </c>
+      <c r="Z48" t="n">
+        <v>38.646</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-24.81</v>
+      </c>
       <c r="AB48" t="n">
         <v>-2.3</v>
       </c>
@@ -3840,6 +3918,9 @@
       <c r="Y49" t="n">
         <v>32</v>
       </c>
+      <c r="AA49" t="n">
+        <v>-11.23</v>
+      </c>
       <c r="AF49" t="inlineStr">
         <is>
           <t>08-Oct-26</t>
@@ -3917,6 +3998,9 @@
       </c>
       <c r="Y50" t="n">
         <v>25.6</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-0.9</v>
       </c>
       <c r="AB50" t="n">
         <v>5.1</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2691,6 +2691,9 @@
       <c r="M32" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="O32" t="n">
+        <v>14.4</v>
+      </c>
       <c r="P32" t="n">
         <v>32.3</v>
       </c>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -1777,7 +1777,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36-month non-financing Policy Coordination Instrument (PCI), following completion of the US$3.0B ECF</t>
+          <t>36-month non-financing Policy Coordination Instrument (PCI), following the US$3.0B ECF closed 27-Jul-26</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2198,18 +2198,22 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>None; prior EFF/ECF/RSF expired uncompleted Apr-25, successor talks ongoing</t>
+        </is>
+      </c>
       <c r="G25" t="n">
         <v>4.5</v>
       </c>
       <c r="H25" t="n">
-        <v>6.8</v>
+        <v>6.76</v>
       </c>
       <c r="I25" t="n">
         <v>8.75</v>
       </c>
       <c r="J25" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="K25" t="n">
         <v>-4.1</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -1062,6 +1062,11 @@
           <t>Brazil</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>1.9</v>
@@ -1206,6 +1211,11 @@
           <t>Chile</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>2.4</v>
@@ -1266,6 +1276,11 @@
           <t>Colombia</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>2.3</v>
@@ -1395,6 +1410,11 @@
           <t>Czech Republic</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Central Europe</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>2.2</v>
@@ -1836,6 +1856,11 @@
           <t>Hungary</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Central Europe</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>1.7</v>
@@ -1896,6 +1921,11 @@
           <t>India</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>6.5</v>
@@ -1956,6 +1986,11 @@
           <t>Indonesia</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>5</v>
@@ -2256,6 +2291,11 @@
           <t>Malaysia</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>4.7</v>
@@ -2316,6 +2356,11 @@
           <t>Mexico</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>1.6</v>
@@ -2946,6 +2991,11 @@
           <t>Peru</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>2.8</v>
@@ -3006,6 +3056,11 @@
           <t>Philippines</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>4.1</v>
@@ -3066,6 +3121,11 @@
           <t>Poland</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Central Europe</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>3.3</v>
@@ -3126,6 +3186,11 @@
           <t>Romania</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Central Europe</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>0.7</v>
@@ -3559,6 +3624,11 @@
       <c r="A45" t="inlineStr">
         <is>
           <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Asia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa (WAEMU)</t>
+          <t>West Africa (WAEMU)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EFF/ECF (40-month, US$3.5B) and RSF (US$1.3B); final reviews completed Jun-26</t>
+          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B), final reviews completed Jun-26</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -3355,7 +3355,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Successor financing arrangement (staff-level agreement) replacing suspended EFF/ECF approved Jun-23</t>
+          <t>Staff-level agreement on new arrangement replacing suspended $1.8B facility</t>
         </is>
       </c>
       <c r="G41" t="n">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -705,7 +705,7 @@
         <v>2.2</v>
       </c>
       <c r="L4" t="n">
-        <v>14.9</v>
+        <v>15.821</v>
       </c>
       <c r="M4" t="n">
         <v>6.8</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -3878,7 +3878,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (EFF), 4-year</t>
+          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
         </is>
       </c>
       <c r="G48" t="n">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG50"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 08-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 09-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Europe (Western Balkans)</t>
+          <t>CEEMEA (Western Balkans)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -625,7 +625,7 @@
         <v>-2.8</v>
       </c>
       <c r="L3" t="n">
-        <v>9.347</v>
+        <v>8.6</v>
       </c>
       <c r="M3" t="n">
         <v>7.2</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stand-By Arrangement (3-year, precautionary)</t>
+          <t>3-year precautionary Stand-By Arrangement</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -844,7 +844,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>BB+ (unsolicited)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MENA / GCC</t>
+          <t>CEEMEA (GCC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -953,10 +953,10 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.8</v>
+        <v>-11</v>
       </c>
       <c r="S7" t="n">
         <v>27.5</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EFF/ECF/RSF (42-month blended) completed</t>
+          <t>EFF/ECF/RSF (42-month blended) completed; final disbursement USD 118m</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>None active; ECF/EFF/RSF arrangements completed Jul-25, now annual Post-Financing Assessment</t>
+          <t>None; ECF/EFF/RSF completed Jul-25, Post-Financing Assessment</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1159,7 +1159,7 @@
         <v>2.6</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.1</v>
+        <v>-3.75</v>
       </c>
       <c r="L10" t="n">
         <v>5.14</v>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>West Africa (WAEMU)</t>
+          <t>Sub-Saharan Africa (WAEMU)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B), final reviews completed Jun-26</t>
+          <t>EFF/ECF (final sixth review completed) and RSF (fifth review completed)</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1528,7 +1528,7 @@
         <v>-12.1</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Sub-Saharan Africa (East Africa)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CCC-</t>
+          <t>CCC- (LTFC IDR); LTLC CC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>None (2021 EFF expired; technical surveillance mission 14-25 Sep-26, no SLA)</t>
+          <t>None (2021 EFF expired; Sep-26 staff mission was technical surveillance of the mid-2026 debt audit)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36-month non-financing Policy Coordination Instrument (PCI), following the US$3.0B ECF closed 27-Jul-26</t>
+          <t>Policy Coordination Instrument (36-month, non-financing); follows the US$3.0B ECF closed 27-Jul-26</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Middle East (CEEMEA)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>None active (Article IV surveillance and Post-Financing Assessment only; last SBA expired 2018)</t>
+          <t>None (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2092,7 +2092,7 @@
         <v>9.6</v>
       </c>
       <c r="P23" t="n">
-        <v>53.9</v>
+        <v>57</v>
       </c>
       <c r="Q23" t="n">
         <v>-4.2</v>
@@ -2123,156 +2123,114 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MENA</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Ba3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>4-year Extended Fund Facility (SDR 926.37m) plus RSF</t>
-        </is>
-      </c>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.7011</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.2</v>
+        <v>1.9</v>
       </c>
       <c r="L24" t="n">
-        <v>28.5</v>
+        <v>229.487</v>
       </c>
       <c r="M24" t="n">
-        <v>9.199999999999999</v>
+        <v>14.361</v>
       </c>
       <c r="P24" t="n">
-        <v>83.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>21.01</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>-3.11</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.95</v>
+        <v>-5.9</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>reports/jordan-sovereign-credit.md</t>
+          <t>reports/israel-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Ba3</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>None; prior EFF/ECF/RSF expired uncompleted Apr-25, successor talks ongoing</t>
+          <t>Extended Fund Facility (4-year, SDR 926.37m) plus RSF; Fifth EFF Review completed Jun-26</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>6.76</v>
+        <v>2.7011</v>
       </c>
       <c r="I25" t="n">
-        <v>8.75</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.1</v>
+        <v>-6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>14.702</v>
+        <v>28.5</v>
       </c>
       <c r="M25" t="n">
-        <v>4.632</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>68.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>33</v>
+        <v>-5.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-2.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>34.7</v>
+        <v>23</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-3.11</v>
       </c>
       <c r="AB25" t="n">
-        <v>-2.9</v>
+        <v>-6.1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.95</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
@@ -2281,128 +2239,108 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>reports/kenya-sovereign-credit.md</t>
+          <t>reports/jordan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Asia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.7817</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.97</v>
+        <v>4.6</v>
       </c>
       <c r="K26" t="n">
-        <v>1.4</v>
+        <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>131.981</v>
+        <v>66.069</v>
       </c>
       <c r="M26" t="n">
-        <v>4.276</v>
+        <v>7.386</v>
       </c>
       <c r="P26" t="n">
-        <v>69.5</v>
+        <v>24.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>97.798</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1</v>
+        <v>-1.3</v>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>reports/malaysia-sovereign-credit.md</t>
+          <t>reports/kazakhstan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>B3</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2619</v>
+        <v>6.76</v>
       </c>
       <c r="I27" t="n">
-        <v>6.5</v>
+        <v>8.75</v>
       </c>
       <c r="J27" t="n">
-        <v>3.24</v>
+        <v>1.99</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.4</v>
+        <v>-4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>265.969</v>
+        <v>14.702</v>
       </c>
       <c r="M27" t="n">
-        <v>3.73</v>
+        <v>4.632</v>
       </c>
       <c r="P27" t="n">
-        <v>62.7</v>
+        <v>68.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.8</v>
+        <v>-6.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>33</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>250.968</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>-0.7</v>
+        <v>34.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.3</v>
+        <v>-2.9</v>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
@@ -2411,219 +2349,135 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>reports/mexico-sovereign-credit.md</t>
+          <t>reports/kenya-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Montenegro</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Western Balkans</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3.6043</v>
+        <v>-0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>-19.4</v>
+        <v>26</v>
       </c>
       <c r="L28" t="n">
-        <v>2.196</v>
+        <v>51.738</v>
       </c>
       <c r="M28" t="n">
-        <v>3.947</v>
+        <v>8.406000000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>63.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>-1.6</v>
+        <v>27.6</v>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>reports/montenegro-sovereign-credit.md</t>
+          <t>reports/kuwait-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>BB+</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>BBB-</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Ba1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Flexible Credit Line (2-year, precautionary)</t>
-        </is>
-      </c>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-0.3333</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.58</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.1</v>
+        <v>-22.5</v>
       </c>
       <c r="L29" t="n">
-        <v>55.65</v>
+        <v>33.301</v>
       </c>
       <c r="M29" t="n">
-        <v>5.5</v>
+        <v>13.603</v>
       </c>
       <c r="P29" t="n">
-        <v>67.2</v>
+        <v>139.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>50.756</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>-5.83</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>-3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>reports/morocco-sovereign-credit.md</t>
+          <t>reports/lebanon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>CCC (LC: SD)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Caa3</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Extended Credit Facility (2022) lapsed Apr-25; successor under discussion</t>
-        </is>
-      </c>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="H30" t="n">
-        <v>6.5</v>
+        <v>1.7817</v>
       </c>
       <c r="I30" t="n">
-        <v>9.25</v>
+        <v>2.75</v>
       </c>
       <c r="J30" t="n">
-        <v>2.75</v>
+        <v>0.97</v>
       </c>
       <c r="K30" t="n">
-        <v>-43</v>
+        <v>1.4</v>
       </c>
       <c r="L30" t="n">
-        <v>3.9</v>
+        <v>131.981</v>
       </c>
       <c r="M30" t="n">
-        <v>6.5</v>
+        <v>4.276</v>
       </c>
       <c r="P30" t="n">
-        <v>94</v>
+        <v>69.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>-6.5</v>
+        <v>-3.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.9</v>
+        <v>7.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>97.798</v>
       </c>
       <c r="AA30" t="n">
-        <v>-2.95</v>
+        <v>10.37</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
@@ -2632,54 +2486,63 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>reports/mozambique-sovereign-credit.md</t>
+          <t>reports/malaysia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="H31" t="n">
-        <v>4.4106</v>
+        <v>3.2619</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.24</v>
       </c>
       <c r="K31" t="n">
-        <v>-15.7</v>
+        <v>-0.4</v>
       </c>
       <c r="L31" t="n">
-        <v>3.252</v>
+        <v>265.969</v>
       </c>
       <c r="M31" t="n">
-        <v>3.958</v>
+        <v>3.73</v>
       </c>
       <c r="P31" t="n">
-        <v>70.5</v>
+        <v>62.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>-6.1</v>
+        <v>-4.4</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>-6.3</v>
+        <v>6.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.151</v>
+        <v>250.968</v>
       </c>
       <c r="AA31" t="n">
-        <v>-1.86</v>
+        <v>-0.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
@@ -2688,84 +2551,51 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>reports/namibia-sovereign-credit.md</t>
+          <t>reports/mexico-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>B3</t>
+          <t>Western Balkans (CEEMEA)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="H32" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="I32" t="n">
-        <v>23</v>
-      </c>
-      <c r="J32" t="n">
-        <v>7.61</v>
+        <v>3.6043</v>
       </c>
       <c r="K32" t="n">
-        <v>5.8</v>
+        <v>-19.4</v>
       </c>
       <c r="L32" t="n">
-        <v>54.98</v>
+        <v>2.196</v>
       </c>
       <c r="M32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O32" t="n">
-        <v>14.4</v>
+        <v>3.947</v>
       </c>
       <c r="P32" t="n">
-        <v>32.3</v>
+        <v>63.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="S32" t="n">
-        <v>55</v>
-      </c>
-      <c r="X32" t="n">
-        <v>-0.51</v>
+        <v>-4</v>
       </c>
       <c r="Y32" t="n">
-        <v>30.8</v>
+        <v>26.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>15.61</v>
+        <v>-2.07</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>15.12</v>
+        <v>-1.6</v>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
@@ -2774,19 +2604,19 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>reports/nigeria-sovereign-credit.md</t>
+          <t>reports/montenegro-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CEEMEA - Western Balkans</t>
+          <t>North Africa (MENA)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2796,58 +2626,63 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ba1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PLL concluded Nov-24</t>
+          <t>Flexible Credit Line (2-year, precautionary)</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="H33" t="n">
-        <v>2.5729</v>
+        <v>-0.3333</v>
       </c>
       <c r="I33" t="n">
-        <v>4.25</v>
+        <v>2.25</v>
       </c>
       <c r="J33" t="n">
-        <v>1.68</v>
+        <v>2.58</v>
       </c>
       <c r="K33" t="n">
-        <v>-5</v>
+        <v>-3.1</v>
       </c>
       <c r="L33" t="n">
-        <v>5.51</v>
+        <v>55.65</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="P33" t="n">
-        <v>55.2</v>
+        <v>67.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>-4.2</v>
+        <v>-3.5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>11.5</v>
       </c>
       <c r="X33" t="n">
-        <v>1.52</v>
+        <v>-2.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.474</v>
+        <v>50.756</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.99</v>
+        <v>-5.83</v>
       </c>
       <c r="AB33" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.16</v>
+        <v>-3.2</v>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
@@ -2856,67 +2691,79 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>reports/north-macedonia-sovereign-credit.md</t>
+          <t>reports/morocco-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Middle East (GCC)</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>CCC (LTFC) / SD (LC)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Baa3</t>
+          <t>Caa3</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>2022 Extended Credit Facility (SDR 340.8m) lapsed Apr-25 with reviews incomplete; successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>3.3771</v>
+        <v>6.5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.75</v>
       </c>
       <c r="K34" t="n">
-        <v>2.5</v>
+        <v>-43</v>
       </c>
       <c r="L34" t="n">
-        <v>18.38</v>
+        <v>3.9</v>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="P34" t="n">
-        <v>34.7</v>
+        <v>94</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.6</v>
+        <v>-6.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-2.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>15.6</v>
+        <v>-0.1</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.9</v>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
@@ -2925,54 +2772,54 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>reports/oman-sovereign-credit.md</t>
+          <t>reports/mozambique-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>South Asia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="H35" t="n">
-        <v>10.2591</v>
+        <v>4.4106</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.4</v>
+        <v>-15.7</v>
       </c>
       <c r="L35" t="n">
-        <v>27.993</v>
+        <v>3.252</v>
       </c>
       <c r="M35" t="n">
-        <v>3.755</v>
+        <v>3.958</v>
       </c>
       <c r="P35" t="n">
-        <v>70.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.02</v>
+        <v>-6.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>22.8</v>
+        <v>-6.3</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.151</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.14</v>
+        <v>-1.86</v>
       </c>
       <c r="AB35" t="n">
-        <v>-2.3</v>
+        <v>0.8</v>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
@@ -2981,63 +2828,84 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>reports/pakistan-sovereign-credit.md</t>
+          <t>reports/namibia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>B3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="H36" t="n">
-        <v>4.0636</v>
+        <v>15.39</v>
       </c>
       <c r="I36" t="n">
-        <v>4.25</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>0.19</v>
+        <v>7.61</v>
       </c>
       <c r="K36" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="L36" t="n">
-        <v>95.26900000000001</v>
+        <v>54.98</v>
       </c>
       <c r="M36" t="n">
-        <v>10.423</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O36" t="n">
+        <v>14.4</v>
       </c>
       <c r="P36" t="n">
-        <v>30</v>
+        <v>32.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>-2</v>
+        <v>-4.4</v>
+      </c>
+      <c r="S36" t="n">
+        <v>55</v>
       </c>
       <c r="X36" t="n">
-        <v>1.8</v>
+        <v>-0.51</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>87.288</v>
+        <v>30.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>12.01</v>
+        <v>15.61</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>15.12</v>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
@@ -3046,63 +2914,80 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>reports/peru-sovereign-credit.md</t>
+          <t>reports/nigeria-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>Europe (Western Balkans)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BB+</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BB-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PLL concluded Nov-24</t>
+        </is>
+      </c>
       <c r="G37" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="H37" t="n">
-        <v>6.3629</v>
+        <v>2.5729</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.36</v>
+        <v>1.68</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.4</v>
+        <v>-5</v>
       </c>
       <c r="L37" t="n">
-        <v>103.316</v>
+        <v>5.51</v>
       </c>
       <c r="M37" t="n">
-        <v>7.306</v>
+        <v>4.2</v>
       </c>
       <c r="P37" t="n">
-        <v>60.2</v>
+        <v>55.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>-3.7</v>
+        <v>-4.2</v>
       </c>
       <c r="X37" t="n">
-        <v>-0.19</v>
+        <v>1.52</v>
       </c>
       <c r="Y37" t="n">
-        <v>-2</v>
+        <v>7.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>93.018</v>
+        <v>4.474</v>
       </c>
       <c r="AA37" t="n">
-        <v>-22.11</v>
+        <v>-0.99</v>
       </c>
       <c r="AB37" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.16</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -3111,63 +2996,67 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>reports/philippines-sovereign-credit.md</t>
+          <t>reports/north-macedonia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Central Europe</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>Middle East (GCC)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Baa3</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
       <c r="G38" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="H38" t="n">
-        <v>3.2123</v>
-      </c>
-      <c r="I38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.54</v>
+        <v>3.3771</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.1</v>
+        <v>2.5</v>
       </c>
       <c r="L38" t="n">
-        <v>304.971</v>
+        <v>18.38</v>
       </c>
       <c r="M38" t="n">
-        <v>5.861</v>
+        <v>5</v>
       </c>
       <c r="P38" t="n">
-        <v>65.7</v>
+        <v>34.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>277.21</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>-13.87</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB38" t="n">
-        <v>-1.1</v>
+        <v>15.6</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -3176,63 +3065,54 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>reports/poland-sovereign-credit.md</t>
+          <t>reports/oman-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="H39" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="I39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>-1.66</v>
+        <v>10.2591</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.8</v>
+        <v>-0.4</v>
       </c>
       <c r="L39" t="n">
-        <v>90.04300000000001</v>
+        <v>27.993</v>
       </c>
       <c r="M39" t="n">
-        <v>5.528</v>
+        <v>3.755</v>
       </c>
       <c r="P39" t="n">
-        <v>61.9</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Q39" t="n">
-        <v>-6.2</v>
+        <v>-3.2</v>
       </c>
       <c r="X39" t="n">
-        <v>1.95</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>72.172</v>
+        <v>22.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>-32.2</v>
+        <v>-0.14</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.5</v>
+        <v>-2.3</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -3241,85 +3121,63 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>reports/romania-sovereign-credit.md</t>
+          <t>reports/pakistan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>ECF (38-month, reported)</t>
-        </is>
-      </c>
+          <t>Latin America</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>9.699999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="H40" t="n">
-        <v>15.7</v>
+        <v>4.0636</v>
       </c>
       <c r="I40" t="n">
-        <v>8.75</v>
+        <v>4.25</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.95</v>
+        <v>0.19</v>
       </c>
       <c r="K40" t="n">
-        <v>-15</v>
+        <v>3.4</v>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>95.26900000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
-      </c>
-      <c r="O40" t="n">
-        <v>63</v>
+        <v>10.423</v>
       </c>
       <c r="P40" t="n">
-        <v>77.5</v>
+        <v>30</v>
       </c>
       <c r="Q40" t="n">
-        <v>-4.8</v>
+        <v>-2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>-16.4</v>
+        <v>16.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.795</v>
+        <v>87.288</v>
       </c>
       <c r="AA40" t="n">
-        <v>-1.98</v>
+        <v>12.01</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0.62</v>
+        <v>2.5</v>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
@@ -3328,62 +3186,63 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>reports/rwanda-sovereign-credit.md</t>
+          <t>reports/peru-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa (WAEMU)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Caa2</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Staff-level agreement on new arrangement replacing suspended $1.8B facility</t>
-        </is>
-      </c>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="H41" t="n">
-        <v>1.2</v>
+        <v>6.3629</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
-        <v>1.8</v>
+        <v>-1.36</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.2</v>
+        <v>-4.4</v>
+      </c>
+      <c r="L41" t="n">
+        <v>103.316</v>
+      </c>
+      <c r="M41" t="n">
+        <v>7.306</v>
       </c>
       <c r="P41" t="n">
-        <v>132</v>
+        <v>60.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>-6.7</v>
+        <v>-3.7</v>
+      </c>
+      <c r="X41" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>93.018</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-22.11</v>
       </c>
       <c r="AB41" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
@@ -3392,82 +3251,63 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>reports/senegal-sovereign-credit.md</t>
+          <t>reports/philippines-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Western Balkans / CEEMEA</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>BB+</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>BBB-</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Ba2</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Policy Coordination Instrument (36-month, non-financing, through late 2027)</t>
-        </is>
-      </c>
+          <t>Central Europe</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="H42" t="n">
-        <v>2.2</v>
+        <v>3.2123</v>
       </c>
       <c r="I42" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="J42" t="n">
-        <v>3.55</v>
+        <v>0.54</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.1</v>
+        <v>-1.1</v>
       </c>
       <c r="L42" t="n">
-        <v>35.71</v>
+        <v>304.971</v>
       </c>
       <c r="M42" t="n">
-        <v>6.2</v>
+        <v>5.861</v>
       </c>
       <c r="P42" t="n">
-        <v>43.3</v>
+        <v>65.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>-2.9</v>
+        <v>-6.7</v>
       </c>
       <c r="X42" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>7</v>
+        <v>16.9</v>
       </c>
       <c r="Z42" t="n">
-        <v>30.033</v>
+        <v>277.21</v>
       </c>
       <c r="AA42" t="n">
-        <v>-4.36</v>
+        <v>-13.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>-1.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
@@ -3476,138 +3316,99 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>reports/serbia-sovereign-credit.md</t>
+          <t>reports/poland-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>BB (foreign) / BB+ (local)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Ba2</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I43" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.9</v>
+        <v>-8.6</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.6</v>
+        <v>11</v>
       </c>
       <c r="L43" t="n">
-        <v>75.95999999999999</v>
+        <v>55.847</v>
       </c>
       <c r="M43" t="n">
-        <v>5.8</v>
+        <v>7.453</v>
       </c>
       <c r="P43" t="n">
-        <v>77.2</v>
+        <v>43.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="S43" t="n">
-        <v>20</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>74.307</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>-0.9</v>
+        <v>-3.4</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>reports/south-africa-sovereign-credit.md</t>
+          <t>reports/qatar-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Central Europe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="H44" t="n">
-        <v>4.0609</v>
+        <v>8.16</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-1.66</v>
       </c>
       <c r="K44" t="n">
-        <v>6.3</v>
+        <v>-6.8</v>
       </c>
       <c r="L44" t="n">
-        <v>6.395</v>
+        <v>90.04300000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>5.749</v>
+        <v>5.528</v>
       </c>
       <c r="P44" t="n">
-        <v>21.9</v>
+        <v>61.9</v>
       </c>
       <c r="Q44" t="n">
-        <v>-2.5</v>
+        <v>-6.2</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.95</v>
       </c>
       <c r="Y44" t="n">
-        <v>45.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>72.172</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.48</v>
+        <v>-32.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
@@ -3616,63 +3417,85 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>reports/tajikistan-sovereign-credit.md</t>
+          <t>reports/romania-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ECF (38-month, reported)</t>
+        </is>
+      </c>
       <c r="G45" t="n">
-        <v>1.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>2.5265</v>
+        <v>15.7</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>8.75</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.53</v>
+        <v>-6.95</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7</v>
+        <v>-15</v>
       </c>
       <c r="L45" t="n">
-        <v>283.137</v>
+        <v>2.2</v>
       </c>
       <c r="M45" t="n">
-        <v>8.051</v>
+        <v>4</v>
+      </c>
+      <c r="O45" t="n">
+        <v>63</v>
       </c>
       <c r="P45" t="n">
-        <v>66.8</v>
+        <v>77.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0.21</v>
+        <v>-4.8</v>
       </c>
       <c r="Y45" t="n">
-        <v>5.9</v>
+        <v>-16.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>302.852</v>
+        <v>1.795</v>
       </c>
       <c r="AA45" t="n">
-        <v>8.08</v>
+        <v>-1.98</v>
       </c>
       <c r="AB45" t="n">
-        <v>-3.9</v>
+        <v>-0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.62</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -3681,163 +3504,98 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>reports/thailand-sovereign-credit.md</t>
+          <t>reports/rwanda-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>MENA / North Africa</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>USD 1.9bn Extended Fund Facility, staff-level agreement Oct-22, never approved by the Executive Board; frozen</t>
-        </is>
-      </c>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H46" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I46" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.2</v>
+        <v>-1.6</v>
       </c>
       <c r="L46" t="n">
-        <v>9.079000000000001</v>
+        <v>505.164</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>15.595</v>
       </c>
       <c r="P46" t="n">
-        <v>82</v>
+        <v>32.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>-1.33</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0.15</v>
+        <v>-3.5</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>reports/tunisia-sovereign-credit.md</t>
+          <t>reports/saudi-arabia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CEEMEA</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>BB-</t>
+          <t>Sub-Saharan Africa (WAEMU)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ba3</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>Caa2</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Staff-level agreement on new arrangement replacing suspended $1.8B facility</t>
+        </is>
+      </c>
       <c r="G47" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="H47" t="n">
-        <v>29.73</v>
+        <v>1.2</v>
       </c>
       <c r="I47" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>12.5</v>
+        <v>1.8</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="L47" t="n">
-        <v>174.4</v>
-      </c>
-      <c r="M47" t="n">
-        <v>5.128</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O47" t="n">
-        <v>31.8</v>
+        <v>-6.2</v>
       </c>
       <c r="P47" t="n">
-        <v>29.5</v>
+        <v>132</v>
       </c>
       <c r="Q47" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>137.109</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>-38.89</v>
+        <v>-6.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>-1</v>
+        <v>-2.4</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.2</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
@@ -3846,82 +3604,82 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>reports/turkey-sovereign-credit.md</t>
+          <t>reports/senegal-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CEEMEA</t>
+          <t>Western Balkans / CEEMEA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CCC+</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ba2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
+          <t>Policy Coordination Instrument (36-month, non-financing, through late 2027)</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="H48" t="n">
-        <v>8.1</v>
+        <v>2.2</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>5.75</v>
       </c>
       <c r="J48" t="n">
-        <v>7.9</v>
+        <v>3.55</v>
       </c>
       <c r="K48" t="n">
-        <v>-18.9</v>
+        <v>-4.1</v>
       </c>
       <c r="L48" t="n">
-        <v>47.1</v>
+        <v>35.71</v>
       </c>
       <c r="M48" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="P48" t="n">
-        <v>98.40000000000001</v>
+        <v>43.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>-18.4</v>
+        <v>-2.9</v>
       </c>
       <c r="X48" t="n">
-        <v>-0.5</v>
+        <v>1.37</v>
       </c>
       <c r="Y48" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="Z48" t="n">
-        <v>38.646</v>
+        <v>30.033</v>
       </c>
       <c r="AA48" t="n">
-        <v>-24.81</v>
+        <v>-4.36</v>
       </c>
       <c r="AB48" t="n">
-        <v>-2.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
@@ -3930,19 +3688,19 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+          <t>reports/serbia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CIS / Central Asia</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3952,7 +3710,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BB (foreign) / BB+ (local)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3962,41 +3720,53 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>None active (annual Article IV surveillance and technical assistance only)</t>
+          <t>None (Article IV)</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="I49" t="n">
-        <v>14</v>
+        <v>7.25</v>
       </c>
       <c r="J49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L49" t="n">
+        <v>75.95999999999999</v>
+      </c>
+      <c r="M49" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P49" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Y49" t="n">
         <v>7.8</v>
       </c>
-      <c r="K49" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="L49" t="n">
-        <v>72.13</v>
-      </c>
-      <c r="M49" t="n">
-        <v>12</v>
-      </c>
-      <c r="P49" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>32</v>
+      <c r="Z49" t="n">
+        <v>74.307</v>
       </c>
       <c r="AA49" t="n">
-        <v>-11.23</v>
+        <v>-1.32</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>-0.9</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
@@ -4005,89 +3775,567 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>reports/uzbekistan-sovereign-credit.md</t>
+          <t>reports/south-africa-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Central Asia</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.0609</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L50" t="n">
+        <v>6.395</v>
+      </c>
+      <c r="M50" t="n">
+        <v>5.749</v>
+      </c>
+      <c r="P50" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>reports/tajikistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.5265</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L51" t="n">
+        <v>283.137</v>
+      </c>
+      <c r="M51" t="n">
+        <v>8.051</v>
+      </c>
+      <c r="P51" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>302.852</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>reports/thailand-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MENA / North Africa</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Caa1</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>USD 1.9bn Extended Fund Facility, staff-level agreement Oct-22, never approved by the Executive Board; frozen</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I52" t="n">
+        <v>7</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="L52" t="n">
+        <v>9.079000000000001</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>reports/tunisia-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CEEMEA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BB-</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BB-</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ba3</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H53" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="I53" t="n">
+        <v>37</v>
+      </c>
+      <c r="J53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L53" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="M53" t="n">
+        <v>5.128</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O53" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="P53" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>137.109</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-38.89</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>reports/turkey-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Uae</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L54" t="n">
+        <v>292.319</v>
+      </c>
+      <c r="M54" t="n">
+        <v>5.234</v>
+      </c>
+      <c r="P54" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>09-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>reports/uae-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CEEMEA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CCC+</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>16</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="L55" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P55" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="X55" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>38.646</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-24.81</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>reports/ukraine-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CIS / Central Asia</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>None active (annual Article IV surveillance and technical assistance only)</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>14</v>
+      </c>
+      <c r="J56" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="L56" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="M56" t="n">
+        <v>12</v>
+      </c>
+      <c r="P56" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-11.23</v>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>reports/uzbekistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>CCC+</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Caa2</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>38-month ECF concluded Jan-26 (sixth and final review); successor programme under negotiation</t>
         </is>
       </c>
-      <c r="G50" t="n">
+      <c r="G57" t="n">
         <v>4.3</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H57" t="n">
         <v>6.1</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I57" t="n">
         <v>10.75</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J57" t="n">
         <v>4.65</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K57" t="n">
         <v>0.9</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L57" t="n">
         <v>5.8</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M57" t="n">
         <v>4.2</v>
       </c>
-      <c r="P50" t="n">
+      <c r="P57" t="n">
         <v>91</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q57" t="n">
         <v>-4.9</v>
       </c>
-      <c r="S50" t="n">
+      <c r="S57" t="n">
         <v>35</v>
       </c>
-      <c r="X50" t="n">
+      <c r="X57" t="n">
         <v>2.27</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Y57" t="n">
         <v>25.6</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AA57" t="n">
         <v>-0.9</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AB57" t="n">
         <v>5.1</v>
       </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr">
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
         <is>
           <t>reports/zambia-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2130,11 +2130,20 @@
       <c r="G24" t="n">
         <v>3.5</v>
       </c>
+      <c r="H24" t="n">
+        <v>1.5355</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.71</v>
+      </c>
       <c r="K24" t="n">
         <v>1.9</v>
       </c>
       <c r="L24" t="n">
-        <v>229.487</v>
+        <v>241.633</v>
       </c>
       <c r="M24" t="n">
         <v>14.361</v>
@@ -2144,6 +2153,15 @@
       </c>
       <c r="Q24" t="n">
         <v>-5.9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-1.6</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
@@ -2253,11 +2271,14 @@
       <c r="G26" t="n">
         <v>4.6</v>
       </c>
+      <c r="H26" t="n">
+        <v>9.239800000000001</v>
+      </c>
       <c r="K26" t="n">
         <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>66.069</v>
+        <v>70.56699999999999</v>
       </c>
       <c r="M26" t="n">
         <v>7.386</v>
@@ -2267,6 +2288,12 @@
       </c>
       <c r="Q26" t="n">
         <v>-1.3</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>11.5</v>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
@@ -2363,11 +2390,20 @@
       <c r="G28" t="n">
         <v>-0.6</v>
       </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K28" t="n">
         <v>26</v>
       </c>
       <c r="L28" t="n">
-        <v>51.738</v>
+        <v>32.689</v>
       </c>
       <c r="M28" t="n">
         <v>8.406000000000001</v>
@@ -2377,6 +2413,12 @@
       </c>
       <c r="Q28" t="n">
         <v>27.6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>28.1</v>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
@@ -2399,11 +2441,14 @@
       <c r="G29" t="n">
         <v>4</v>
       </c>
+      <c r="H29" t="n">
+        <v>16.6565</v>
+      </c>
       <c r="K29" t="n">
         <v>-22.5</v>
       </c>
       <c r="L29" t="n">
-        <v>33.301</v>
+        <v>38.164</v>
       </c>
       <c r="M29" t="n">
         <v>13.603</v>
@@ -2413,6 +2458,12 @@
       </c>
       <c r="Q29" t="n">
         <v>3.3</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-4.6</v>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
@@ -3330,11 +3381,20 @@
       <c r="G43" t="n">
         <v>-8.6</v>
       </c>
+      <c r="H43" t="n">
+        <v>0.7338</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.62</v>
+      </c>
       <c r="K43" t="n">
         <v>11</v>
       </c>
       <c r="L43" t="n">
-        <v>55.847</v>
+        <v>61.098</v>
       </c>
       <c r="M43" t="n">
         <v>7.453</v>
@@ -3344,6 +3404,12 @@
       </c>
       <c r="Q43" t="n">
         <v>-3.4</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>14.7</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
@@ -3518,11 +3584,20 @@
       <c r="G46" t="n">
         <v>3.1</v>
       </c>
+      <c r="H46" t="n">
+        <v>1.8167</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.68</v>
+      </c>
       <c r="K46" t="n">
         <v>-1.6</v>
       </c>
       <c r="L46" t="n">
-        <v>505.164</v>
+        <v>488.684</v>
       </c>
       <c r="M46" t="n">
         <v>15.595</v>
@@ -3532,6 +3607,15 @@
       </c>
       <c r="Q46" t="n">
         <v>-3.5</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>15.9</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
@@ -4072,11 +4156,14 @@
       <c r="G54" t="n">
         <v>3.1</v>
       </c>
+      <c r="H54" t="n">
+        <v>2.0488</v>
+      </c>
       <c r="K54" t="n">
         <v>11.4</v>
       </c>
       <c r="L54" t="n">
-        <v>292.319</v>
+        <v>259.72</v>
       </c>
       <c r="M54" t="n">
         <v>5.234</v>
@@ -4086,6 +4173,15 @@
       </c>
       <c r="Q54" t="n">
         <v>4.9</v>
+      </c>
+      <c r="X54" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>13.2</v>
       </c>
       <c r="AF54" t="inlineStr">
         <is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2160,6 +2160,12 @@
       <c r="Y24" t="n">
         <v>4.9</v>
       </c>
+      <c r="Z24" t="n">
+        <v>232.204</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.53</v>
+      </c>
       <c r="AB24" t="n">
         <v>-1.6</v>
       </c>
@@ -2292,6 +2298,12 @@
       <c r="Y26" t="n">
         <v>29.9</v>
       </c>
+      <c r="Z26" t="n">
+        <v>59.792</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-13.41</v>
+      </c>
       <c r="AB26" t="n">
         <v>11.5</v>
       </c>
@@ -2417,6 +2429,9 @@
       <c r="Y28" t="n">
         <v>-23.4</v>
       </c>
+      <c r="AA28" t="n">
+        <v>32.54</v>
+      </c>
       <c r="AB28" t="n">
         <v>28.1</v>
       </c>
@@ -2462,6 +2477,9 @@
       <c r="Y29" t="n">
         <v>31.2</v>
       </c>
+      <c r="AA29" t="n">
+        <v>-9.16</v>
+      </c>
       <c r="AB29" t="n">
         <v>-4.6</v>
       </c>
@@ -3408,6 +3426,9 @@
       <c r="Y43" t="n">
         <v>10.4</v>
       </c>
+      <c r="AA43" t="n">
+        <v>28.52</v>
+      </c>
       <c r="AB43" t="n">
         <v>14.7</v>
       </c>
@@ -3613,6 +3634,12 @@
       </c>
       <c r="Y46" t="n">
         <v>10</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>482.147</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-25.78</v>
       </c>
       <c r="AB46" t="n">
         <v>15.9</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2126,6 +2126,11 @@
           <t>Israel</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Middle East (EMBI IG)</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>3.5</v>
@@ -2273,6 +2278,11 @@
           <t>Kazakhstan</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CIS / Central Asia (EMBI IG)</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>4.6</v>
@@ -2398,6 +2408,11 @@
           <t>Kuwait</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MENA / GCC (EMBI IG)</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>-0.6</v>
@@ -2452,6 +2467,11 @@
           <t>Lebanon</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Middle East (EMBI, in default since 2020)</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>4</v>
@@ -3395,6 +3415,11 @@
           <t>Qatar</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MENA / GCC (EMBI IG)</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>-8.6</v>
@@ -3601,6 +3626,11 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MENA / GCC (EMBI IG)</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
         <v>3.1</v>
@@ -4177,6 +4207,11 @@
       <c r="A54" t="inlineStr">
         <is>
           <t>Uae</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MENA / GCC (EMBI IG)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CEEMEA (Western Balkans)</t>
+          <t>Western Balkans (CEEMEA)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caucasus</t>
+          <t>Caucasus / CEEMEA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3-year precautionary Stand-By Arrangement</t>
+          <t>Stand-By Arrangement (3-year, precautionary)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CEEMEA (South Caucasus)</t>
+          <t>CEEMEA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BB+ (unsolicited)</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -876,7 +876,7 @@
         <v>15.36</v>
       </c>
       <c r="M6" t="n">
-        <v>4.954</v>
+        <v>50</v>
       </c>
       <c r="O6" t="n">
         <v>8.300000000000001</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CEEMEA (GCC)</t>
+          <t>MENA / Gulf (CEEMEA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -953,10 +953,10 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q7" t="n">
-        <v>-11</v>
+        <v>10.8</v>
       </c>
       <c r="S7" t="n">
         <v>27.5</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EFF/ECF/RSF (42-month blended) completed; final disbursement USD 118m</t>
+          <t>Blended EFF/ECF (USD 638m) and RSF (USD 200m), 42 months, completed; no active programme</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>None; ECF/EFF/RSF completed Jul-25, Post-Financing Assessment</t>
+          <t>ECF/EFF/RSF arrangements completed Jul-25; now Post-Financing Assessment, no active programme</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1338,60 +1338,56 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa (WAEMU)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Ba2</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>EFF/ECF (final sixth review completed) and RSF (fifth review completed)</t>
-        </is>
-      </c>
+          <t>Central Europe</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>1.922</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1</v>
+        <v>-1.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>184.565</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7.644</v>
       </c>
       <c r="P13" t="n">
-        <v>55.1</v>
+        <v>46.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.8</v>
+        <v>-2.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6</v>
+        <v>1.35</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>171.989</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.21</v>
       </c>
       <c r="AB13" t="n">
-        <v>-7.3</v>
+        <v>-1.8</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -1400,72 +1396,76 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>reports/cote-d-ivoire-sovereign-credit.md</t>
+          <t>reports/czech-republic-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Central Europe</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>Sub-Saharan Africa (WAEMU)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B), final reviews completed; no successor arrangement identified</t>
+        </is>
+      </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>1.922</v>
+        <v>1.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>184.565</v>
-      </c>
-      <c r="M14" t="n">
-        <v>7.644</v>
+        <v>-1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>46.4</v>
+        <v>55.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3</v>
+        <v>-3.8</v>
       </c>
       <c r="X14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>171.989</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.21</v>
+        <v>0.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.8</v>
+        <v>-7.3</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>reports/czech-republic-sovereign-credit.md</t>
+          <t>reports/cote-d-ivoire-sovereign-credit.md</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
         <v>-12.1</v>
       </c>
       <c r="R15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa (East Africa)</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CCC- (LTFC IDR); LTLC CC</t>
+          <t>CCC-</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>None (2021 EFF expired; Sep-26 staff mission was technical surveillance of the mid-2026 debt audit)</t>
+          <t>None (2021 Extended Fund Facility expired; Sep-26 staff mission ended without a staff-level agreement)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Policy Coordination Instrument (36-month, non-financing); follows the US$3.0B ECF closed 27-Jul-26</t>
+          <t>36-month non-financing Policy Coordination Instrument (PCI), following completion of the US$3.0B ECF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Middle East (CEEMEA)</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>None (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
+          <t>None (Article IV surveillance and Post-Financing Assessment only; last SBA expired 2018)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (4-year, SDR 926.37m) plus RSF; Fifth EFF Review completed Jun-26</t>
+          <t>Extended Fund Facility (4-year); Fifth Review completed Jun-26, plus RSF Second Review</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -2354,7 +2354,11 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>None; prior EFF/ECF/RSF expired uncompleted Apr-25, successor talks ongoing</t>
+        </is>
+      </c>
       <c r="G27" t="n">
         <v>4.5</v>
       </c>
@@ -2393,7 +2397,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -2688,7 +2692,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -2705,7 +2709,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>North Africa (MENA)</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2725,7 +2729,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Flexible Credit Line (2-year, precautionary)</t>
+          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review concluded Mar-26</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2775,7 +2779,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -2802,7 +2806,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CCC (LTFC) / SD (LC)</t>
+          <t>CCC (local currency SD)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2812,7 +2816,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2022 Extended Credit Facility (SDR 340.8m) lapsed Apr-25 with reviews incomplete; successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>None active; 2022 ECF (SDR 340.8m) lapsed Apr-25, successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2856,7 +2860,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -2912,7 +2916,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -2998,7 +3002,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -3015,7 +3019,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Europe (Western Balkans)</t>
+          <t>CEEMEA (Western Balkans)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3080,7 +3084,7 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
@@ -3149,7 +3153,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
@@ -3205,7 +3209,7 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
@@ -3561,7 +3565,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ECF (38-month, reported)</t>
+          <t>ECF, 38-month (reported by Gemini, unverified)</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -3611,7 +3615,7 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
@@ -3708,7 +3712,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Staff-level agreement on new arrangement replacing suspended $1.8B facility</t>
+          <t>New arrangement (staff-level agreement) replacing the suspended USD 1.8bn facility</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3740,7 +3744,7 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
@@ -3757,7 +3761,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Western Balkans / CEEMEA</t>
+          <t>CEEMEA - Southeast Europe</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3777,7 +3781,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Policy Coordination Instrument (36-month, non-financing, through late 2027)</t>
+          <t>36-month non-financing Policy Coordination Instrument (third review completed 15-Jun-26)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3824,7 +3828,7 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
@@ -3841,7 +3845,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3851,7 +3855,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BB (foreign) / BB+ (local)</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3911,7 +3915,7 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
@@ -3964,7 +3968,7 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
@@ -4046,7 +4050,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MENA / North Africa</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4061,7 +4065,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USD 1.9bn Extended Fund Facility, staff-level agreement Oct-22, never approved by the Executive Board; frozen</t>
+          <t>None active; USD 1.9bn EFF agreed at staff level Oct-22, never submitted to or approved by the Executive Board</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -4108,7 +4112,7 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
@@ -4194,7 +4198,7 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MENA / GCC (EMBI IG)</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3640,7 +3640,7 @@
         <v>3.1</v>
       </c>
       <c r="H46" t="n">
-        <v>1.8167</v>
+        <v>1.82</v>
       </c>
       <c r="I46" t="n">
         <v>4.5</v>
@@ -3655,7 +3655,7 @@
         <v>488.684</v>
       </c>
       <c r="M46" t="n">
-        <v>15.595</v>
+        <v>15.6</v>
       </c>
       <c r="P46" t="n">
         <v>32.1</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
+          <t>4-year EFF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CIS / Central Asia</t>
+          <t>CEEMEA (Central Asia / CIS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>38-month ECF concluded Jan-26 (sixth and final review); successor programme under negotiation</t>
+          <t>38-month Extended Credit Facility, completed (sixth and final review); successor programme under negotiation</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -4210,44 +4210,75 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Uae</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MENA / GCC (EMBI IG)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>CEEMEA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CCC+</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>4-year EFF</t>
+        </is>
+      </c>
       <c r="G54" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>2.0488</v>
+        <v>8.1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>16</v>
+      </c>
+      <c r="J54" t="n">
+        <v>7.9</v>
       </c>
       <c r="K54" t="n">
-        <v>11.4</v>
+        <v>-18.9</v>
       </c>
       <c r="L54" t="n">
-        <v>259.72</v>
+        <v>47.1</v>
       </c>
       <c r="M54" t="n">
-        <v>5.234</v>
+        <v>5.6</v>
       </c>
       <c r="P54" t="n">
-        <v>31.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.9</v>
+        <v>-18.4</v>
       </c>
       <c r="X54" t="n">
-        <v>-1.12</v>
+        <v>-0.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>-3.1</v>
+        <v>5.7</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>38.646</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-24.81</v>
       </c>
       <c r="AB54" t="n">
-        <v>13.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
@@ -4256,82 +4287,61 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>reports/uae-sovereign-credit.md</t>
+          <t>reports/ukraine-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CEEMEA</t>
+          <t>GCC / Middle East</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CCC+</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Ca</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>4-year EFF</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="H55" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>16</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7.9</v>
+        <v>2.05</v>
       </c>
       <c r="K55" t="n">
-        <v>-18.9</v>
+        <v>11.4</v>
       </c>
       <c r="L55" t="n">
-        <v>47.1</v>
+        <v>259.7</v>
       </c>
       <c r="M55" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="P55" t="n">
-        <v>98.40000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>-18.4</v>
+        <v>4.9</v>
       </c>
       <c r="X55" t="n">
-        <v>-0.5</v>
+        <v>-1.12</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>38.646</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>-24.81</v>
+        <v>-3.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>-2.3</v>
+        <v>13.2</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
@@ -4340,7 +4350,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+          <t>reports/uae-sovereign-credit.md</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -3421,7 +3421,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MENA / GCC (EMBI IG)</t>
+          <t>GCC / Middle East</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -3429,7 +3434,7 @@
         <v>-8.6</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7338</v>
+        <v>0.73</v>
       </c>
       <c r="I43" t="n">
         <v>4.35</v>
@@ -3441,10 +3446,10 @@
         <v>11</v>
       </c>
       <c r="L43" t="n">
-        <v>61.098</v>
+        <v>61.1</v>
       </c>
       <c r="M43" t="n">
-        <v>7.453</v>
+        <v>7.45</v>
       </c>
       <c r="P43" t="n">
         <v>43.3</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2414,7 +2414,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MENA / GCC (EMBI IG)</t>
+          <t>Middle East (GCC)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>A1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2431,19 +2446,19 @@
         <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>26</v>
+        <v>18.8</v>
       </c>
       <c r="L28" t="n">
         <v>32.689</v>
       </c>
       <c r="M28" t="n">
-        <v>8.406000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="P28" t="n">
-        <v>22.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>27.6</v>
+        <v>-18.5</v>
       </c>
       <c r="Y28" t="n">
         <v>-23.4</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2280,7 +2280,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CIS / Central Asia (EMBI IG)</t>
+          <t>Central Asia</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Baa1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2288,16 +2303,22 @@
         <v>4.6</v>
       </c>
       <c r="H26" t="n">
-        <v>9.239800000000001</v>
+        <v>9.24</v>
+      </c>
+      <c r="I26" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7.51</v>
       </c>
       <c r="K26" t="n">
         <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>70.56699999999999</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>7.386</v>
+        <v>7.39</v>
       </c>
       <c r="P26" t="n">
         <v>24.9</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Middle East (EMBI IG)</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2136,7 +2136,7 @@
         <v>3.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5355</v>
+        <v>1.54</v>
       </c>
       <c r="I24" t="n">
         <v>3.25</v>
@@ -2148,10 +2148,10 @@
         <v>1.9</v>
       </c>
       <c r="L24" t="n">
-        <v>241.633</v>
+        <v>241.63</v>
       </c>
       <c r="M24" t="n">
-        <v>14.361</v>
+        <v>14.36</v>
       </c>
       <c r="P24" t="n">
         <v>69.8</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Middle East (EMBI, in default since 2020)</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2517,16 +2517,16 @@
         <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>16.6565</v>
+        <v>16.7</v>
       </c>
       <c r="K29" t="n">
         <v>-22.5</v>
       </c>
       <c r="L29" t="n">
-        <v>38.164</v>
+        <v>38.16</v>
       </c>
       <c r="M29" t="n">
-        <v>13.603</v>
+        <v>13.6</v>
       </c>
       <c r="P29" t="n">
         <v>139.4</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Western Balkans (CEEMEA)</t>
+          <t>CEEMEA (Balkans)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -630,6 +630,9 @@
       <c r="M3" t="n">
         <v>7.2</v>
       </c>
+      <c r="N3" t="n">
+        <v>5.28</v>
+      </c>
       <c r="O3" t="n">
         <v>39.7</v>
       </c>
@@ -834,7 +837,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CEEMEA</t>
+          <t>CEEMEA (South Caucasus)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -918,7 +921,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MENA / Gulf (CEEMEA)</t>
+          <t>MENA / GCC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -953,10 +956,10 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.8</v>
+        <v>-11</v>
       </c>
       <c r="S7" t="n">
         <v>27.5</v>
@@ -1012,7 +1015,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blended EFF/ECF (USD 638m) and RSF (USD 200m), 42 months, completed; no active programme</t>
+          <t>Blended 42-month EFF/ECF and RSF arrangements, completed 25-Feb-26 (final tranche USD 118m)</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1149,7 +1152,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ECF/EFF/RSF arrangements completed Jul-25; now Post-Financing Assessment, no active programme</t>
+          <t>None; ECF/EFF/RSF completed Jul-25, now annual Post-Financing Assessment</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1428,7 +1431,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B), final reviews completed; no successor arrangement identified</t>
+          <t>EFF/ECF and RSF, completed (sixth and final EFF/ECF review and fifth RSF review, Jun-26); no successor arrangement identified</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1528,7 +1531,7 @@
         <v>-12.1</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -1657,7 +1660,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>None (2021 Extended Fund Facility expired; Sep-26 staff mission ended without a staff-level agreement)</t>
+          <t>None (2021 EFF expired); Sep-26 technical surveillance mission only</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1712,7 +1715,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Caucasus</t>
+          <t>Caucasus (CEEMEA)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1797,7 +1800,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36-month non-financing Policy Coordination Instrument (PCI), following completion of the US$3.0B ECF</t>
+          <t>Policy Coordination Instrument (36-month, non-financing), following the US$3.0B ECF completed 27-Jul-26</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2053,7 +2056,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2092,7 +2095,7 @@
         <v>9.6</v>
       </c>
       <c r="P23" t="n">
-        <v>57</v>
+        <v>53.9</v>
       </c>
       <c r="Q23" t="n">
         <v>-4.2</v>
@@ -2193,7 +2196,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2213,7 +2216,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (4-year); Fifth Review completed Jun-26, plus RSF Second Review</t>
+          <t>Extended Fund Facility (4-year) plus RSF; Fifth EFF review completed Jun-26</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2280,7 +2283,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>CEEMEA - Central Asia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2517,7 +2520,7 @@
         <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>16.7</v>
+        <v>16.66</v>
       </c>
       <c r="K29" t="n">
         <v>-22.5</v>
@@ -2692,7 +2695,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Western Balkans (CEEMEA)</t>
+          <t>CEEMEA - Western Balkans</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -2765,7 +2768,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review concluded Mar-26</t>
+          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review concluded Mar-26; also RSF (SDR 1.0bn, approved Sep-23)</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2842,7 +2845,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CCC (local currency SD)</t>
+          <t>CCC (LC: SD)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2852,7 +2855,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>None active; 2022 ECF (SDR 340.8m) lapsed Apr-25, successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>2022 ECF (SDR 340.8m) lapsed Apr-25 with fifth and sixth reviews uncompleted; successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3055,7 +3058,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CEEMEA (Western Balkans)</t>
+          <t>CEE / Western Balkans</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3137,7 +3140,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Middle East (GCC)</t>
+          <t>GCC / Middle East</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3457,7 +3460,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GCC / Middle East</t>
+          <t>Middle East (GCC)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3606,7 +3609,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ECF, 38-month (reported by Gemini, unverified)</t>
+          <t>38-month ECF (reported; first-review staff-level agreement 06-Oct-26 for SDR 26.43m)</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -3673,7 +3676,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Middle East (GCC)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3753,7 +3756,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New arrangement (staff-level agreement) replacing the suspended USD 1.8bn facility</t>
+          <t>Staff-level agreement on new arrangement replacing suspended facility; Board consideration 15-Dec-26</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3802,7 +3805,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CEEMEA - Southeast Europe</t>
+          <t>CEEMEA (Europe)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3822,7 +3825,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>36-month non-financing Policy Coordination Instrument (third review completed 15-Jun-26)</t>
+          <t>Policy Coordination Instrument (36-month, non-financing)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3850,7 +3853,7 @@
         <v>43.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>-2.9</v>
+        <v>-3.25</v>
       </c>
       <c r="X48" t="n">
         <v>1.37</v>
@@ -3886,7 +3889,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3896,7 +3899,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BB (foreign) / BB+ (local)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4106,7 +4109,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>None active; USD 1.9bn EFF agreed at staff level Oct-22, never submitted to or approved by the Executive Board</t>
+          <t>EFF (staff-level agreement Oct-22, never approved by Executive Board; frozen)</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -4276,7 +4279,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4-year EFF</t>
+          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -4340,7 +4343,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GCC / Middle East</t>
+          <t>GCC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4403,7 +4406,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CEEMEA (Central Asia / CIS)</t>
+          <t>CIS / Central Asia</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4423,7 +4426,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>None active (annual Article IV surveillance and technical assistance only)</t>
+          <t>None (annual Article IV surveillance only)</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -4498,7 +4501,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>38-month Extended Credit Facility, completed (sixth and final review); successor programme under negotiation</t>
+          <t>Extended Credit Facility (38-month) concluded Jan-26; successor programme under negotiation</t>
         </is>
       </c>
       <c r="G57" t="n">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caucasus / CEEMEA</t>
+          <t>Caucasus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stand-By Arrangement (3-year, precautionary)</t>
+          <t>3-year precautionary Stand-By Arrangement</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CEEMEA (South Caucasus)</t>
+          <t>CEEMEA - South Caucasus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>None (Article IV surveillance only)</t>
+          <t>None active (Article IV surveillance only)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MENA / GCC</t>
+          <t>Middle East (GCC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1015,11 +1015,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blended 42-month EFF/ECF and RSF arrangements, completed 25-Feb-26 (final tranche USD 118m)</t>
+          <t>EFF/ECF (42-month, blended) and RSF arrangements, completed</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>None; ECF/EFF/RSF completed Jul-25, now annual Post-Financing Assessment</t>
+          <t>None active; ECF/EFF/RSF completed Jul-25, now Post-Financing Assessment</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>EFF/ECF and RSF, completed (sixth and final EFF/ECF review and fifth RSF review, Jun-26); no successor arrangement identified</t>
+          <t>EFF/ECF (final sixth reviews completed) and RSF (fifth review completed), Jun-26</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Extended Credit Facility (48-month)</t>
+          <t>48-month Extended Credit Facility (ECF)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1658,11 +1658,7 @@
           <t>Caa2</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>None (2021 EFF expired); Sep-26 technical surveillance mission only</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>2.7</v>
       </c>
@@ -1715,7 +1711,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Caucasus (CEEMEA)</t>
+          <t>Caucasus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1800,7 +1796,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Policy Coordination Instrument (36-month, non-financing), following the US$3.0B ECF completed 27-Jul-26</t>
+          <t>36-month non-financing Policy Coordination Instrument (PCI), following completion of the US$3.0B ECF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2076,7 +2072,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>None (Article IV surveillance and Post-Financing Assessment only; last SBA expired 2018)</t>
+          <t>None active (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2095,7 +2091,7 @@
         <v>9.6</v>
       </c>
       <c r="P23" t="n">
-        <v>53.9</v>
+        <v>57</v>
       </c>
       <c r="Q23" t="n">
         <v>-4.2</v>
@@ -2196,7 +2192,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Middle East (CEEMEA)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2216,7 +2212,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (4-year) plus RSF; Fifth EFF review completed Jun-26</t>
+          <t>Extended Fund Facility (4-year, SDR 926.37m; Fifth Review completed Jun-26, with RSF)</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2283,7 +2279,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CEEMEA - Central Asia</t>
+          <t>CIS / Central Asia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2515,7 +2511,11 @@
           <t>MENA</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>None; mission of 15-18 Sep-26 ended without staff-level agreement</t>
+        </is>
+      </c>
       <c r="G29" t="n">
         <v>4</v>
       </c>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CEEMEA - Western Balkans</t>
+          <t>Western Balkans (CEEMEA)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review concluded Mar-26; also RSF (SDR 1.0bn, approved Sep-23)</t>
+          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review completed Mar-26; RSF SDR 1.0bn approved Sep-23</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2022 ECF (SDR 340.8m) lapsed Apr-25 with fifth and sixth reviews uncompleted; successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>None; 2022 ECF (SDR 340.8m) lapsed Apr-25; successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CEE / Western Balkans</t>
+          <t>CEEMEA - Western Balkans</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GCC / Middle East</t>
+          <t>Middle East (GCC)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Middle East (GCC)</t>
+          <t>GCC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>38-month ECF (reported; first-review staff-level agreement 06-Oct-26 for SDR 26.43m)</t>
+          <t>38-month ECF (reported)</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Middle East (GCC)</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Staff-level agreement on new arrangement replacing suspended facility; Board consideration 15-Dec-26</t>
+          <t>Staff-level agreement on new arrangement replacing suspended USD 1.8B facility; Board consideration 15-Dec-26</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CEEMEA (Europe)</t>
+          <t>CEEMEA - Western Balkans</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BB (foreign) / BB+ (local)</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3937,7 +3937,7 @@
         <v>77.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>-4.5</v>
+        <v>-3.8</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>EFF (staff-level agreement Oct-22, never approved by Executive Board; frozen)</t>
+          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board; frozen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GCC</t>
+          <t>MENA / GCC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CIS / Central Asia</t>
+          <t>Central Asia / CIS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>None (annual Article IV surveillance only)</t>
+          <t>None (Article IV surveillance only)</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Extended Credit Facility (38-month) concluded Jan-26; successor programme under negotiation</t>
+          <t>38-month ECF completed Jan-26 (sixth and final review); successor programme under negotiation</t>
         </is>
       </c>
       <c r="G57" t="n">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CEEMEA (Balkans)</t>
+          <t>CEEMEA - Southeast Europe (Western Balkans)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caucasus</t>
+          <t>CEEMEA - South Caucasus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3-year precautionary Stand-By Arrangement</t>
+          <t>3-year Stand-By Arrangement (precautionary)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1475,79 +1475,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EM sovereign issuance, index flows and positioning</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MENA</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>EFF (with RSF)</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="I15" t="n">
-        <v>19</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>53.559</v>
-      </c>
-      <c r="M15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-12.1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>17.224</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-16.76</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-0.7</v>
-      </c>
+          <t>EM cross-region (thematic, no single country)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
           <t>09-Oct-26</t>
@@ -1555,76 +1491,85 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>reports/egypt-sovereign-credit.md</t>
+          <t>reports/em-issuance-index-flows-and-positioning-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RD</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Caa3</t>
+          <t>Caa1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>48-month Extended Credit Facility (ECF)</t>
+          <t>EFF (with RSF)</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="H16" t="n">
-        <v>13.4</v>
+        <v>12.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>19</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.3</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.4</v>
+        <v>-4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>3.784</v>
+        <v>53.559</v>
       </c>
       <c r="M16" t="n">
-        <v>1.781</v>
+        <v>7.5</v>
       </c>
       <c r="P16" t="n">
-        <v>40.4</v>
+        <v>79.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>7</v>
+        <v>-12.1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
-        <v>86.59999999999999</v>
+        <v>14.7</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>17.224</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.79</v>
+        <v>-16.76</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1</v>
+        <v>-0.7</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -1633,64 +1578,76 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>reports/ethiopia-sovereign-credit.md</t>
+          <t>reports/egypt-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa (CEMAC)</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CCC-</t>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caa2</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>Caa3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>48-month Extended Credit Facility (ECF)</t>
+        </is>
+      </c>
       <c r="G17" t="n">
-        <v>2.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1.597</v>
+        <v>13.4</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.3</v>
+        <v>-2.4</v>
       </c>
       <c r="L17" t="n">
-        <v>0.673</v>
+        <v>3.784</v>
       </c>
       <c r="M17" t="n">
-        <v>4.247</v>
+        <v>1.781</v>
       </c>
       <c r="P17" t="n">
-        <v>70</v>
+        <v>40.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>-10</v>
-      </c>
-      <c r="U17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7</v>
       </c>
       <c r="Y17" t="n">
-        <v>-51.4</v>
+        <v>86.59999999999999</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-3.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>22.6</v>
+        <v>-2.8</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -1699,63 +1656,64 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>reports/gabon-sovereign-credit.md</t>
+          <t>reports/ethiopia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Caucasus</t>
+          <t>Sub-Saharan Africa (CEMAC)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CCC-</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="n">
-        <v>5.6478</v>
-      </c>
-      <c r="I18" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.6</v>
+        <v>1.597</v>
       </c>
       <c r="K18" t="n">
-        <v>-5</v>
+        <v>-4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>8.138999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="M18" t="n">
-        <v>3.017</v>
+        <v>4.247</v>
       </c>
       <c r="P18" t="n">
-        <v>35.1</v>
+        <v>70</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3</v>
+        <v>-10</v>
+      </c>
+      <c r="U18" t="n">
+        <v>17.5</v>
       </c>
       <c r="X18" t="n">
-        <v>1.22</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>7.255</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>-0.72</v>
+        <v>-51.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.5</v>
+        <v>22.6</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -1764,79 +1722,63 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>reports/georgia-sovereign-credit.md</t>
+          <t>reports/gabon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>36-month non-financing Policy Coordination Instrument (PCI), following completion of the US$3.0B ECF</t>
-        </is>
-      </c>
+          <t>Caucasus</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="H19" t="n">
-        <v>5.2</v>
+        <v>5.6478</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>8.25</v>
       </c>
       <c r="J19" t="n">
-        <v>8.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="K19" t="n">
-        <v>10.1</v>
+        <v>-5</v>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>8.138999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>5.2</v>
+        <v>3.017</v>
       </c>
       <c r="P19" t="n">
-        <v>53</v>
+        <v>35.1</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.3</v>
       </c>
       <c r="X19" t="n">
-        <v>1.86</v>
+        <v>1.22</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.9</v>
+        <v>56.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>7.255</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.06</v>
+        <v>-0.72</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.3</v>
+        <v>-2.5</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -1845,128 +1787,144 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>reports/ghana-sovereign-credit.md</t>
+          <t>reports/georgia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Central Europe</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Caa1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>36-month non-financing Policy Coordination Instrument (PCI), following completion of the US$3.0B ECF</t>
+        </is>
+      </c>
       <c r="G20" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2826</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>5.5</v>
+        <v>14</v>
       </c>
       <c r="J20" t="n">
-        <v>4.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4</v>
+        <v>10.1</v>
       </c>
       <c r="L20" t="n">
-        <v>73.621</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>3.495</v>
+        <v>5.2</v>
       </c>
       <c r="P20" t="n">
-        <v>77.90000000000001</v>
+        <v>53</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.5</v>
+        <v>-2.3</v>
       </c>
       <c r="X20" t="n">
-        <v>2.27</v>
+        <v>1.86</v>
       </c>
       <c r="Y20" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>66.95</v>
+        <v>11.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.37</v>
+        <v>10.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>-1.1</v>
+        <v>3.3</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>reports/hungary-sovereign-credit.md</t>
+          <t>reports/ghana-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Central Europe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4412</v>
+        <v>1.2826</v>
       </c>
       <c r="I21" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.22</v>
       </c>
       <c r="K21" t="n">
-        <v>-2</v>
+        <v>-0.4</v>
       </c>
       <c r="L21" t="n">
-        <v>751.764</v>
+        <v>73.621</v>
       </c>
       <c r="M21" t="n">
-        <v>7.851</v>
+        <v>3.495</v>
       </c>
       <c r="P21" t="n">
-        <v>83.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-7.4</v>
+        <v>-5.5</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.75</v>
+        <v>2.27</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.1</v>
+        <v>30.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>715.745</v>
+        <v>66.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>-28.25</v>
+        <v>2.37</v>
       </c>
       <c r="AB21" t="n">
-        <v>-2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -1975,14 +1933,14 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>reports/india-sovereign-credit.md</t>
+          <t>reports/hungary-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1992,47 +1950,47 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8821</v>
+        <v>4.4412</v>
       </c>
       <c r="I22" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="J22" t="n">
-        <v>2.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1</v>
+        <v>-2</v>
       </c>
       <c r="L22" t="n">
-        <v>146.492</v>
+        <v>751.764</v>
       </c>
       <c r="M22" t="n">
-        <v>5.514</v>
+        <v>7.851</v>
       </c>
       <c r="P22" t="n">
-        <v>41.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9</v>
+        <v>-7.4</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.03</v>
+        <v>-2.75</v>
       </c>
       <c r="Y22" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>715.745</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-28.25</v>
+      </c>
+      <c r="AB22" t="n">
         <v>-2.8</v>
       </c>
-      <c r="Z22" t="n">
-        <v>75.541</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>-14.36</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AF22" t="inlineStr">
         <is>
           <t>08-Oct-26</t>
@@ -2040,138 +1998,138 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>reports/indonesia-sovereign-credit.md</t>
+          <t>reports/india-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MENA</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>None active (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
-        </is>
-      </c>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>-6.8</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>3.0928</v>
+        <v>2.8821</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.87</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.3</v>
+        <v>-1.1</v>
       </c>
       <c r="L23" t="n">
-        <v>80.59999999999999</v>
+        <v>146.492</v>
       </c>
       <c r="M23" t="n">
-        <v>9.6</v>
+        <v>5.514</v>
       </c>
       <c r="P23" t="n">
-        <v>57</v>
+        <v>41.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.2</v>
+        <v>-2.9</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-3.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>-10.9</v>
+        <v>-2.8</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>75.541</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.92</v>
+        <v>-14.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.50625</v>
+        <v>0.4</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>reports/iraq-sovereign-credit.md</t>
+          <t>reports/indonesia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Middle East</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>MENA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Caa1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>None active (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
+        </is>
+      </c>
       <c r="G24" t="n">
-        <v>3.5</v>
+        <v>-6.8</v>
       </c>
       <c r="H24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.71</v>
+        <v>3.0928</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9</v>
+        <v>-5.3</v>
       </c>
       <c r="L24" t="n">
-        <v>241.63</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>14.36</v>
+        <v>9.6</v>
       </c>
       <c r="P24" t="n">
-        <v>69.8</v>
+        <v>57</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.67</v>
+        <v>-4.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>232.204</v>
+        <v>-10.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.53</v>
+        <v>4.92</v>
       </c>
       <c r="AB24" t="n">
-        <v>-1.6</v>
+        <v>16.7</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.50625</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
@@ -2180,85 +2138,63 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>reports/israel-sovereign-credit.md</t>
+          <t>reports/iraq-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Middle East (CEEMEA)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Ba3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Extended Fund Facility (4-year, SDR 926.37m; Fifth Review completed Jun-26, with RSF)</t>
-        </is>
-      </c>
+          <t>Middle East</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="H25" t="n">
-        <v>2.7011</v>
+        <v>1.54</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>1.71</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.2</v>
+        <v>1.9</v>
       </c>
       <c r="L25" t="n">
-        <v>28.5</v>
+        <v>241.63</v>
       </c>
       <c r="M25" t="n">
-        <v>9.199999999999999</v>
+        <v>14.36</v>
       </c>
       <c r="P25" t="n">
-        <v>83.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>-2.8</v>
+        <v>-5.9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.67</v>
       </c>
       <c r="Y25" t="n">
-        <v>23</v>
+        <v>4.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.01</v>
+        <v>232.204</v>
       </c>
       <c r="AA25" t="n">
-        <v>-3.11</v>
+        <v>4.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.95</v>
+        <v>-1.6</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
@@ -2267,75 +2203,85 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>reports/jordan-sovereign-credit.md</t>
+          <t>reports/israel-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CIS / Central Asia</t>
+          <t>Middle East (CEEMEA)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Baa1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>Ba3</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Extended Fund Facility (4-year, SDR 926.37m; Fifth Review completed Jun-26, with RSF)</t>
+        </is>
+      </c>
       <c r="G26" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="H26" t="n">
-        <v>9.24</v>
+        <v>2.7011</v>
       </c>
       <c r="I26" t="n">
-        <v>16.75</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>7.51</v>
+        <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>-1</v>
+        <v>-6.2</v>
       </c>
       <c r="L26" t="n">
-        <v>70.56999999999999</v>
+        <v>28.5</v>
       </c>
       <c r="M26" t="n">
-        <v>7.39</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>24.9</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.3</v>
+        <v>-5.2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-2.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>29.9</v>
+        <v>23</v>
       </c>
       <c r="Z26" t="n">
-        <v>59.792</v>
+        <v>21.01</v>
       </c>
       <c r="AA26" t="n">
-        <v>-13.41</v>
+        <v>-3.11</v>
       </c>
       <c r="AB26" t="n">
-        <v>11.5</v>
+        <v>-6.1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.95</v>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
@@ -2344,76 +2290,75 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>reports/kazakhstan-sovereign-credit.md</t>
+          <t>reports/jordan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>CIS / Central Asia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>None; prior EFF/ECF/RSF expired uncompleted Apr-25, successor talks ongoing</t>
-        </is>
-      </c>
+          <t>Baa1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H27" t="n">
-        <v>6.76</v>
+        <v>9.24</v>
       </c>
       <c r="I27" t="n">
-        <v>8.75</v>
+        <v>16.75</v>
       </c>
       <c r="J27" t="n">
-        <v>1.99</v>
+        <v>7.51</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.1</v>
+        <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>14.702</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>4.632</v>
+        <v>7.39</v>
       </c>
       <c r="P27" t="n">
-        <v>68.5</v>
+        <v>24.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>33</v>
+        <v>-1.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>34.7</v>
+        <v>29.9</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>59.792</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-13.41</v>
       </c>
       <c r="AB27" t="n">
-        <v>-2.9</v>
+        <v>11.5</v>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
@@ -2422,72 +2367,76 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>reports/kenya-sovereign-credit.md</t>
+          <t>reports/kazakhstan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Middle East (GCC)</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>None; prior EFF/ECF/RSF expired uncompleted Apr-25, successor talks ongoing</t>
+        </is>
+      </c>
       <c r="G28" t="n">
-        <v>-0.6</v>
+        <v>4.5</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>8.75</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="K28" t="n">
-        <v>18.8</v>
+        <v>-4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>32.689</v>
+        <v>14.702</v>
       </c>
       <c r="M28" t="n">
-        <v>8.4</v>
+        <v>4.632</v>
       </c>
       <c r="P28" t="n">
-        <v>2.9</v>
+        <v>68.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>-18.5</v>
+        <v>-6.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>33</v>
       </c>
       <c r="Y28" t="n">
-        <v>-23.4</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>32.54</v>
+        <v>34.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>28.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
@@ -2496,55 +2445,72 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>reports/kuwait-sovereign-credit.md</t>
+          <t>reports/kenya-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MENA</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>None; mission of 15-18 Sep-26 ended without staff-level agreement</t>
-        </is>
-      </c>
+          <t>Middle East (GCC)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>-0.6</v>
       </c>
       <c r="H29" t="n">
-        <v>16.66</v>
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.5</v>
       </c>
       <c r="K29" t="n">
-        <v>-22.5</v>
+        <v>18.8</v>
       </c>
       <c r="L29" t="n">
-        <v>38.16</v>
+        <v>32.689</v>
       </c>
       <c r="M29" t="n">
-        <v>13.6</v>
+        <v>8.4</v>
       </c>
       <c r="P29" t="n">
-        <v>139.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>-18.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>31.2</v>
+        <v>-23.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>-9.16</v>
+        <v>32.54</v>
       </c>
       <c r="AB29" t="n">
-        <v>-4.6</v>
+        <v>28.1</v>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
@@ -2553,128 +2519,120 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>reports/lebanon-sovereign-credit.md</t>
+          <t>reports/kuwait-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>MENA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>None; mission of 15-18 Sep-26 ended without staff-level agreement</t>
+        </is>
+      </c>
       <c r="G30" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>1.7817</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.97</v>
+        <v>16.66</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4</v>
+        <v>-22.5</v>
       </c>
       <c r="L30" t="n">
-        <v>131.981</v>
+        <v>38.16</v>
       </c>
       <c r="M30" t="n">
-        <v>4.276</v>
+        <v>13.6</v>
       </c>
       <c r="P30" t="n">
-        <v>69.5</v>
+        <v>139.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>97.798</v>
+        <v>31.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>10.37</v>
+        <v>-9.16</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>-4.6</v>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>reports/malaysia-sovereign-credit.md</t>
+          <t>reports/lebanon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2619</v>
+        <v>1.7817</v>
       </c>
       <c r="I31" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="J31" t="n">
-        <v>3.24</v>
+        <v>0.97</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.4</v>
+        <v>1.4</v>
       </c>
       <c r="L31" t="n">
-        <v>265.969</v>
+        <v>131.981</v>
       </c>
       <c r="M31" t="n">
-        <v>3.73</v>
+        <v>4.276</v>
       </c>
       <c r="P31" t="n">
-        <v>62.7</v>
+        <v>69.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>-4.4</v>
+        <v>-3.3</v>
       </c>
       <c r="X31" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>250.968</v>
+        <v>97.798</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.7</v>
+        <v>10.37</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
@@ -2683,138 +2641,116 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>reports/mexico-sovereign-credit.md</t>
+          <t>reports/malaysia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Western Balkans (CEEMEA)</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H32" t="n">
-        <v>3.6043</v>
+        <v>3.2619</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.24</v>
       </c>
       <c r="K32" t="n">
-        <v>-19.4</v>
+        <v>-0.4</v>
       </c>
       <c r="L32" t="n">
-        <v>2.196</v>
+        <v>265.969</v>
       </c>
       <c r="M32" t="n">
-        <v>3.947</v>
+        <v>3.73</v>
       </c>
       <c r="P32" t="n">
-        <v>63.5</v>
+        <v>62.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>-4</v>
+        <v>-4.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>26.1</v>
+        <v>6.8</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>250.968</v>
       </c>
       <c r="AA32" t="n">
-        <v>-2.07</v>
+        <v>-0.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>-1.6</v>
+        <v>0.3</v>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>reports/montenegro-sovereign-credit.md</t>
+          <t>reports/mexico-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>BB+</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>BBB-</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Ba1</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review completed Mar-26; RSF SDR 1.0bn approved Sep-23</t>
-        </is>
-      </c>
+          <t>Western Balkans (CEEMEA)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3333</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.58</v>
+        <v>3.6043</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.1</v>
+        <v>-19.4</v>
       </c>
       <c r="L33" t="n">
-        <v>55.65</v>
+        <v>2.196</v>
       </c>
       <c r="M33" t="n">
-        <v>5.5</v>
+        <v>3.947</v>
       </c>
       <c r="P33" t="n">
-        <v>67.2</v>
+        <v>63.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="X33" t="n">
-        <v>-2.1</v>
+        <v>-4</v>
       </c>
       <c r="Y33" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>50.756</v>
+        <v>26.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>-5.83</v>
+        <v>-2.07</v>
       </c>
       <c r="AB33" t="n">
-        <v>-3.2</v>
+        <v>-1.6</v>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
@@ -2823,79 +2759,85 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>reports/morocco-sovereign-credit.md</t>
+          <t>reports/montenegro-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CCC (LC: SD)</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Caa3</t>
+          <t>Ba1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>None; 2022 ECF (SDR 340.8m) lapsed Apr-25; successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review completed Mar-26; RSF SDR 1.0bn approved Sep-23</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="H34" t="n">
-        <v>6.5</v>
+        <v>-0.3333</v>
       </c>
       <c r="I34" t="n">
-        <v>9.25</v>
+        <v>2.25</v>
       </c>
       <c r="J34" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="K34" t="n">
-        <v>-43</v>
+        <v>-3.1</v>
       </c>
       <c r="L34" t="n">
-        <v>3.9</v>
+        <v>55.65</v>
       </c>
       <c r="M34" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="P34" t="n">
-        <v>94</v>
+        <v>67.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>-6.5</v>
+        <v>-3.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-2.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>4.9</v>
+        <v>18</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>50.756</v>
       </c>
       <c r="AA34" t="n">
-        <v>-2.95</v>
+        <v>-5.83</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.9</v>
+        <v>-3.2</v>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
@@ -2904,14 +2846,14 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>reports/mozambique-sovereign-credit.md</t>
+          <t>reports/morocco-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2919,39 +2861,64 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CCC (LC: SD)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Caa3</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>None; 2022 ECF (SDR 340.8m) lapsed Apr-25; successor arrangement under discussion after Sep-26 staff mission</t>
+        </is>
+      </c>
       <c r="G35" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="H35" t="n">
-        <v>4.4106</v>
+        <v>6.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.75</v>
       </c>
       <c r="K35" t="n">
-        <v>-15.7</v>
+        <v>-43</v>
       </c>
       <c r="L35" t="n">
-        <v>3.252</v>
+        <v>3.9</v>
       </c>
       <c r="M35" t="n">
-        <v>3.958</v>
+        <v>6.5</v>
       </c>
       <c r="P35" t="n">
-        <v>70.5</v>
+        <v>94</v>
       </c>
       <c r="Q35" t="n">
-        <v>-6.1</v>
+        <v>-6.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.151</v>
+        <v>4.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>-1.86</v>
+        <v>-2.95</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.9</v>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
@@ -2960,84 +2927,54 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>reports/namibia-sovereign-credit.md</t>
+          <t>reports/mozambique-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>B3</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="H36" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="I36" t="n">
-        <v>23</v>
-      </c>
-      <c r="J36" t="n">
-        <v>7.61</v>
+        <v>4.4106</v>
       </c>
       <c r="K36" t="n">
-        <v>5.8</v>
+        <v>-15.7</v>
       </c>
       <c r="L36" t="n">
-        <v>54.98</v>
+        <v>3.252</v>
       </c>
       <c r="M36" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O36" t="n">
-        <v>14.4</v>
+        <v>3.958</v>
       </c>
       <c r="P36" t="n">
-        <v>32.3</v>
+        <v>70.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="S36" t="n">
-        <v>55</v>
-      </c>
-      <c r="X36" t="n">
-        <v>-0.51</v>
+        <v>-6.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>30.8</v>
+        <v>-6.3</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.151</v>
       </c>
       <c r="AA36" t="n">
-        <v>15.61</v>
+        <v>-1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>15.12</v>
+        <v>0.8</v>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
@@ -3046,80 +2983,84 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>reports/nigeria-sovereign-credit.md</t>
+          <t>reports/namibia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CEEMEA - Western Balkans</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>PLL concluded Nov-24</t>
-        </is>
-      </c>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="H37" t="n">
-        <v>2.5729</v>
+        <v>15.39</v>
       </c>
       <c r="I37" t="n">
-        <v>4.25</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>1.68</v>
+        <v>7.61</v>
       </c>
       <c r="K37" t="n">
-        <v>-5</v>
+        <v>5.8</v>
       </c>
       <c r="L37" t="n">
-        <v>5.51</v>
+        <v>54.98</v>
       </c>
       <c r="M37" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O37" t="n">
+        <v>14.4</v>
       </c>
       <c r="P37" t="n">
-        <v>55.2</v>
+        <v>32.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>-4.2</v>
+        <v>-4.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>55</v>
       </c>
       <c r="X37" t="n">
-        <v>1.52</v>
+        <v>-0.51</v>
       </c>
       <c r="Y37" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.474</v>
+        <v>30.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>-0.99</v>
+        <v>15.61</v>
       </c>
       <c r="AB37" t="n">
-        <v>-2.6</v>
+        <v>4.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.16</v>
+        <v>15.12</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -3128,67 +3069,80 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>reports/north-macedonia-sovereign-credit.md</t>
+          <t>reports/nigeria-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Middle East (GCC)</t>
+          <t>CEEMEA - Western Balkans</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BBB-</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Baa3</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>PLL concluded Nov-24</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="H38" t="n">
-        <v>3.3771</v>
+        <v>2.5729</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.68</v>
       </c>
       <c r="K38" t="n">
-        <v>2.5</v>
+        <v>-5</v>
       </c>
       <c r="L38" t="n">
-        <v>18.38</v>
+        <v>5.51</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="P38" t="n">
-        <v>34.7</v>
+        <v>55.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.6</v>
+        <v>-4.2</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.52</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.474</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-0.99</v>
       </c>
       <c r="AB38" t="n">
-        <v>15.6</v>
+        <v>-2.6</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.16</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -3197,54 +3151,67 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>reports/oman-sovereign-credit.md</t>
+          <t>reports/north-macedonia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>South Asia</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>Middle East (GCC)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Baa3</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
       <c r="G39" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="H39" t="n">
-        <v>10.2591</v>
+        <v>3.3771</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.4</v>
+        <v>2.5</v>
       </c>
       <c r="L39" t="n">
-        <v>27.993</v>
+        <v>18.38</v>
       </c>
       <c r="M39" t="n">
-        <v>3.755</v>
+        <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>70.09999999999999</v>
+        <v>34.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.02</v>
+        <v>0.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>-0.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB39" t="n">
-        <v>-2.3</v>
+        <v>15.6</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -3253,128 +3220,119 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>reports/pakistan-sovereign-credit.md</t>
+          <t>reports/oman-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="H40" t="n">
-        <v>4.0636</v>
-      </c>
-      <c r="I40" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.19</v>
+        <v>10.2591</v>
       </c>
       <c r="K40" t="n">
-        <v>3.4</v>
+        <v>-0.4</v>
       </c>
       <c r="L40" t="n">
-        <v>95.26900000000001</v>
+        <v>27.993</v>
       </c>
       <c r="M40" t="n">
-        <v>10.423</v>
+        <v>3.755</v>
       </c>
       <c r="P40" t="n">
-        <v>30</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Q40" t="n">
-        <v>-2</v>
+        <v>-3.2</v>
       </c>
       <c r="X40" t="n">
-        <v>1.8</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>87.288</v>
+        <v>22.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>12.01</v>
+        <v>-0.14</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.5</v>
+        <v>-2.3</v>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>reports/peru-sovereign-credit.md</t>
+          <t>reports/pakistan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="H41" t="n">
-        <v>6.3629</v>
+        <v>4.0636</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.36</v>
+        <v>0.19</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.4</v>
+        <v>3.4</v>
       </c>
       <c r="L41" t="n">
-        <v>103.316</v>
+        <v>95.26900000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>7.306</v>
+        <v>10.423</v>
       </c>
       <c r="P41" t="n">
-        <v>60.2</v>
+        <v>30</v>
       </c>
       <c r="Q41" t="n">
-        <v>-3.7</v>
+        <v>-2</v>
       </c>
       <c r="X41" t="n">
-        <v>-0.19</v>
+        <v>1.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>-2</v>
+        <v>16.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>93.018</v>
+        <v>87.288</v>
       </c>
       <c r="AA41" t="n">
-        <v>-22.11</v>
+        <v>12.01</v>
       </c>
       <c r="AB41" t="n">
-        <v>-1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
@@ -3383,63 +3341,63 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>reports/philippines-sovereign-credit.md</t>
+          <t>reports/peru-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="H42" t="n">
-        <v>3.2123</v>
+        <v>6.3629</v>
       </c>
       <c r="I42" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
-        <v>0.54</v>
+        <v>-1.36</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.1</v>
+        <v>-4.4</v>
       </c>
       <c r="L42" t="n">
-        <v>304.971</v>
+        <v>103.316</v>
       </c>
       <c r="M42" t="n">
-        <v>5.861</v>
+        <v>7.306</v>
       </c>
       <c r="P42" t="n">
-        <v>65.7</v>
+        <v>60.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>-6.7</v>
+        <v>-3.7</v>
       </c>
       <c r="X42" t="n">
-        <v>1.5</v>
+        <v>-0.19</v>
       </c>
       <c r="Y42" t="n">
-        <v>16.9</v>
+        <v>-2</v>
       </c>
       <c r="Z42" t="n">
-        <v>277.21</v>
+        <v>93.018</v>
       </c>
       <c r="AA42" t="n">
-        <v>-13.87</v>
+        <v>-22.11</v>
       </c>
       <c r="AB42" t="n">
-        <v>-1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
@@ -3448,279 +3406,279 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>reports/poland-sovereign-credit.md</t>
+          <t>reports/philippines-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GCC</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AA</t>
+          <t>Central Europe</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>-8.6</v>
+        <v>3.3</v>
       </c>
       <c r="H43" t="n">
-        <v>0.73</v>
+        <v>3.2123</v>
       </c>
       <c r="I43" t="n">
-        <v>4.35</v>
+        <v>3.75</v>
       </c>
       <c r="J43" t="n">
-        <v>3.62</v>
+        <v>0.54</v>
       </c>
       <c r="K43" t="n">
-        <v>11</v>
+        <v>-1.1</v>
       </c>
       <c r="L43" t="n">
-        <v>61.1</v>
+        <v>304.971</v>
       </c>
       <c r="M43" t="n">
-        <v>7.45</v>
+        <v>5.861</v>
       </c>
       <c r="P43" t="n">
-        <v>43.3</v>
+        <v>65.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>-3.4</v>
+        <v>-6.7</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>10.4</v>
+        <v>16.9</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>277.21</v>
       </c>
       <c r="AA43" t="n">
-        <v>28.52</v>
+        <v>-13.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>14.7</v>
+        <v>-1.1</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>reports/qatar-sovereign-credit.md</t>
+          <t>reports/poland-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>GCC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>0.7</v>
+        <v>-8.6</v>
       </c>
       <c r="H44" t="n">
-        <v>8.16</v>
+        <v>0.73</v>
       </c>
       <c r="I44" t="n">
-        <v>6.5</v>
+        <v>4.35</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.66</v>
+        <v>3.62</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.8</v>
+        <v>11</v>
       </c>
       <c r="L44" t="n">
-        <v>90.04300000000001</v>
+        <v>61.1</v>
       </c>
       <c r="M44" t="n">
-        <v>5.528</v>
+        <v>7.45</v>
       </c>
       <c r="P44" t="n">
-        <v>61.9</v>
+        <v>43.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.95</v>
+        <v>-3.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>72.172</v>
+        <v>10.4</v>
       </c>
       <c r="AA44" t="n">
-        <v>-32.2</v>
+        <v>28.52</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.5</v>
+        <v>14.7</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>reports/romania-sovereign-credit.md</t>
+          <t>reports/qatar-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>38-month ECF (reported)</t>
-        </is>
-      </c>
+          <t>Central Europe</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>9.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H45" t="n">
-        <v>15.7</v>
+        <v>8.16</v>
       </c>
       <c r="I45" t="n">
-        <v>8.75</v>
+        <v>6.5</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.95</v>
+        <v>-1.66</v>
       </c>
       <c r="K45" t="n">
-        <v>-15</v>
+        <v>-6.8</v>
       </c>
       <c r="L45" t="n">
-        <v>2.2</v>
+        <v>90.04300000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
-      </c>
-      <c r="O45" t="n">
-        <v>63</v>
+        <v>5.528</v>
       </c>
       <c r="P45" t="n">
-        <v>77.5</v>
+        <v>61.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>-4.8</v>
+        <v>-6.2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.95</v>
       </c>
       <c r="Y45" t="n">
-        <v>-16.4</v>
+        <v>2.9</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.795</v>
+        <v>72.172</v>
       </c>
       <c r="AA45" t="n">
-        <v>-1.98</v>
+        <v>-32.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0.62</v>
+        <v>-0.5</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>reports/rwanda-sovereign-credit.md</t>
+          <t>reports/romania-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Middle East</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>38-month ECF (reported)</t>
+        </is>
+      </c>
       <c r="G46" t="n">
-        <v>3.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>1.82</v>
+        <v>15.7</v>
       </c>
       <c r="I46" t="n">
-        <v>4.5</v>
+        <v>8.75</v>
       </c>
       <c r="J46" t="n">
-        <v>2.68</v>
+        <v>-6.95</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.6</v>
+        <v>-15</v>
       </c>
       <c r="L46" t="n">
-        <v>488.684</v>
+        <v>2.2</v>
       </c>
       <c r="M46" t="n">
-        <v>15.6</v>
+        <v>4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>63</v>
       </c>
       <c r="P46" t="n">
-        <v>32.1</v>
+        <v>77.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="X46" t="n">
-        <v>-0.31</v>
+        <v>-4.8</v>
       </c>
       <c r="Y46" t="n">
-        <v>10</v>
+        <v>-16.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>482.147</v>
+        <v>1.795</v>
       </c>
       <c r="AA46" t="n">
-        <v>-25.78</v>
+        <v>-1.98</v>
       </c>
       <c r="AB46" t="n">
-        <v>15.9</v>
+        <v>-0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.62</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
@@ -3729,62 +3687,63 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>reports/saudi-arabia-sovereign-credit.md</t>
+          <t>reports/rwanda-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa (WAEMU)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Caa2</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Staff-level agreement on new arrangement replacing suspended USD 1.8B facility; Board consideration 15-Dec-26</t>
-        </is>
-      </c>
+          <t>Middle East</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="H47" t="n">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J47" t="n">
-        <v>1.8</v>
+        <v>2.68</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.2</v>
+        <v>-1.6</v>
+      </c>
+      <c r="L47" t="n">
+        <v>488.684</v>
+      </c>
+      <c r="M47" t="n">
+        <v>15.6</v>
       </c>
       <c r="P47" t="n">
-        <v>132</v>
+        <v>32.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>-6.7</v>
+        <v>-3.5</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>482.147</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-25.78</v>
       </c>
       <c r="AB47" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
@@ -3793,82 +3752,62 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>reports/senegal-sovereign-credit.md</t>
+          <t>reports/saudi-arabia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CEEMEA - Western Balkans</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>BB+</t>
+          <t>Sub-Saharan Africa (WAEMU)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Policy Coordination Instrument (36-month, non-financing)</t>
+          <t>Staff-level agreement on new arrangement replacing suspended USD 1.8B facility; Board consideration 15-Dec-26</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="H48" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="I48" t="n">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="M48" t="n">
-        <v>6.2</v>
+        <v>-6.2</v>
       </c>
       <c r="P48" t="n">
-        <v>43.3</v>
+        <v>132</v>
       </c>
       <c r="Q48" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>30.033</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>-4.36</v>
+        <v>-6.7</v>
       </c>
       <c r="AB48" t="n">
-        <v>-1.4</v>
+        <v>-2.4</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.2</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
@@ -3877,29 +3816,29 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>reports/serbia-sovereign-credit.md</t>
+          <t>reports/senegal-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>CEEMEA - Western Balkans</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3909,53 +3848,50 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>Policy Coordination Instrument (36-month, non-financing)</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="H49" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="I49" t="n">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="J49" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.6</v>
+        <v>-4.1</v>
       </c>
       <c r="L49" t="n">
-        <v>75.95999999999999</v>
+        <v>35.71</v>
       </c>
       <c r="M49" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="P49" t="n">
-        <v>77.2</v>
+        <v>43.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="S49" t="n">
-        <v>20</v>
+        <v>-3.25</v>
       </c>
       <c r="X49" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="Y49" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Z49" t="n">
-        <v>74.307</v>
+        <v>30.033</v>
       </c>
       <c r="AA49" t="n">
-        <v>-1.32</v>
+        <v>-4.36</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.9</v>
+        <v>-1.4</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
@@ -3964,51 +3900,85 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>reports/south-africa-sovereign-credit.md</t>
+          <t>reports/serbia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Central Asia</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>4.0609</v>
+        <v>4.4</v>
+      </c>
+      <c r="I50" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.9</v>
       </c>
       <c r="K50" t="n">
-        <v>6.3</v>
+        <v>-1.6</v>
       </c>
       <c r="L50" t="n">
-        <v>6.395</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>5.749</v>
+        <v>5.8</v>
       </c>
       <c r="P50" t="n">
-        <v>21.9</v>
+        <v>77.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>-2.5</v>
+        <v>-3.8</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.23</v>
       </c>
       <c r="Y50" t="n">
-        <v>45.9</v>
+        <v>7.8</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>74.307</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.48</v>
+        <v>-1.32</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
@@ -4017,228 +3987,195 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>reports/tajikistan-sovereign-credit.md</t>
+          <t>reports/south-africa-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="H51" t="n">
-        <v>2.5265</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>-1.53</v>
+        <v>4.0609</v>
       </c>
       <c r="K51" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="L51" t="n">
-        <v>283.137</v>
+        <v>6.395</v>
       </c>
       <c r="M51" t="n">
-        <v>8.051</v>
+        <v>5.749</v>
       </c>
       <c r="P51" t="n">
-        <v>66.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q51" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0.21</v>
+        <v>-2.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>302.852</v>
+        <v>45.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>8.08</v>
+        <v>3.48</v>
       </c>
       <c r="AB51" t="n">
-        <v>-3.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>reports/thailand-sovereign-credit.md</t>
+          <t>reports/tajikistan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board; frozen</t>
-        </is>
-      </c>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="H52" t="n">
-        <v>5.6</v>
+        <v>2.5265</v>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>1.4</v>
+        <v>-1.53</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.2</v>
+        <v>0.7</v>
       </c>
       <c r="L52" t="n">
-        <v>9.079000000000001</v>
+        <v>283.137</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>8.051</v>
       </c>
       <c r="P52" t="n">
-        <v>82</v>
+        <v>66.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>-5.2</v>
+        <v>-2.2</v>
       </c>
       <c r="X52" t="n">
-        <v>1.63</v>
+        <v>0.21</v>
       </c>
       <c r="Y52" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>302.852</v>
       </c>
       <c r="AA52" t="n">
-        <v>-1.33</v>
+        <v>8.08</v>
       </c>
       <c r="AB52" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0.15</v>
+        <v>-3.9</v>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>reports/tunisia-sovereign-credit.md</t>
+          <t>reports/thailand-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CEEMEA</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ba3</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>Caa1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board; frozen</t>
+        </is>
+      </c>
       <c r="G53" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="H53" t="n">
-        <v>29.73</v>
+        <v>5.6</v>
       </c>
       <c r="I53" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="J53" t="n">
-        <v>12.5</v>
+        <v>1.4</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.7</v>
+        <v>-4.2</v>
       </c>
       <c r="L53" t="n">
-        <v>174.4</v>
+        <v>9.079000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>5.128</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O53" t="n">
-        <v>31.8</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>29.5</v>
+        <v>82</v>
       </c>
       <c r="Q53" t="n">
         <v>-5.2</v>
       </c>
       <c r="X53" t="n">
-        <v>0.31</v>
+        <v>1.63</v>
       </c>
       <c r="Y53" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>137.109</v>
+        <v>6.8</v>
       </c>
       <c r="AA53" t="n">
-        <v>-38.89</v>
+        <v>-1.33</v>
       </c>
       <c r="AB53" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0.15</v>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
@@ -4247,14 +4184,14 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>reports/turkey-sovereign-credit.md</t>
+          <t>reports/tunisia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4264,65 +4201,67 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CCC+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ca</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
-        </is>
-      </c>
+          <t>Ba3</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="H54" t="n">
-        <v>8.1</v>
+        <v>29.73</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J54" t="n">
-        <v>7.9</v>
+        <v>12.5</v>
       </c>
       <c r="K54" t="n">
-        <v>-18.9</v>
+        <v>-2.7</v>
       </c>
       <c r="L54" t="n">
-        <v>47.1</v>
+        <v>174.4</v>
       </c>
       <c r="M54" t="n">
-        <v>5.6</v>
+        <v>5.128</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O54" t="n">
+        <v>31.8</v>
       </c>
       <c r="P54" t="n">
-        <v>98.40000000000001</v>
+        <v>29.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>-18.4</v>
+        <v>-5.2</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.5</v>
+        <v>0.31</v>
       </c>
       <c r="Y54" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="Z54" t="n">
-        <v>38.646</v>
+        <v>137.109</v>
       </c>
       <c r="AA54" t="n">
-        <v>-24.81</v>
+        <v>-38.89</v>
       </c>
       <c r="AB54" t="n">
-        <v>-2.3</v>
+        <v>-1</v>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
@@ -4331,61 +4270,82 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+          <t>reports/turkey-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MENA / GCC</t>
+          <t>CEEMEA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>CCC+</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
+        </is>
+      </c>
       <c r="G55" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="H55" t="n">
-        <v>2.05</v>
+        <v>8.1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>16</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7.9</v>
       </c>
       <c r="K55" t="n">
-        <v>11.4</v>
+        <v>-18.9</v>
       </c>
       <c r="L55" t="n">
-        <v>259.7</v>
+        <v>47.1</v>
       </c>
       <c r="M55" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="P55" t="n">
-        <v>31.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.9</v>
+        <v>-18.4</v>
       </c>
       <c r="X55" t="n">
-        <v>-1.12</v>
+        <v>-0.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>-3.1</v>
+        <v>5.7</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>38.646</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-24.81</v>
       </c>
       <c r="AB55" t="n">
-        <v>13.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
@@ -4394,73 +4354,61 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>reports/uae-sovereign-credit.md</t>
+          <t>reports/ukraine-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Central Asia / CIS</t>
+          <t>MENA / GCC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Ba2</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>None (Article IV surveillance only)</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>8.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="H56" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I56" t="n">
-        <v>14</v>
-      </c>
-      <c r="J56" t="n">
-        <v>7.8</v>
+        <v>2.05</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.3</v>
+        <v>11.4</v>
       </c>
       <c r="L56" t="n">
-        <v>72.13</v>
+        <v>259.7</v>
       </c>
       <c r="M56" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="P56" t="n">
-        <v>27</v>
+        <v>31.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>-2.1</v>
+        <v>4.9</v>
+      </c>
+      <c r="X56" t="n">
+        <v>-1.12</v>
       </c>
       <c r="Y56" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>-11.23</v>
+        <v>-3.1</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>13.2</v>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
@@ -4469,89 +4417,164 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>reports/uzbekistan-sovereign-credit.md</t>
+          <t>reports/uae-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Central Asia / CIS</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>None (Article IV surveillance only)</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H57" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>14</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="L57" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="M57" t="n">
+        <v>12</v>
+      </c>
+      <c r="P57" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-11.23</v>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>09-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>reports/uzbekistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>CCC+</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Caa2</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>38-month ECF completed Jan-26 (sixth and final review); successor programme under negotiation</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="G58" t="n">
         <v>4.3</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H58" t="n">
         <v>6.1</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I58" t="n">
         <v>10.75</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J58" t="n">
         <v>4.65</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K58" t="n">
         <v>0.9</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L58" t="n">
         <v>5.8</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M58" t="n">
         <v>4.2</v>
       </c>
-      <c r="P57" t="n">
+      <c r="P58" t="n">
         <v>91</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="Q58" t="n">
         <v>-4.9</v>
       </c>
-      <c r="S57" t="n">
+      <c r="S58" t="n">
         <v>35</v>
       </c>
-      <c r="X57" t="n">
+      <c r="X58" t="n">
         <v>2.27</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Y58" t="n">
         <v>25.6</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AA58" t="n">
         <v>-0.9</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AB58" t="n">
         <v>5.1</v>
       </c>
-      <c r="AF57" t="inlineStr">
+      <c r="AF58" t="inlineStr">
         <is>
           <t>09-Oct-26</t>
         </is>
       </c>
-      <c r="AG57" t="inlineStr">
+      <c r="AG58" t="inlineStr">
         <is>
           <t>reports/zambia-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1875,121 +1875,79 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Gulf support and anchors for EM sovereigns</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>Thematic: Gulf (GCC) support for EM sovereigns (Pakistan, Egypt, Bahrain)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.2826</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>73.621</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.495</v>
-      </c>
-      <c r="P21" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>66.95</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-1.1</v>
-      </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>reports/hungary-sovereign-credit.md</t>
+          <t>reports/gulf-support-and-anchors-for-em-s-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Central Europe</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4412</v>
+        <v>1.2826</v>
       </c>
       <c r="I22" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.22</v>
       </c>
       <c r="K22" t="n">
-        <v>-2</v>
+        <v>-0.4</v>
       </c>
       <c r="L22" t="n">
-        <v>751.764</v>
+        <v>73.621</v>
       </c>
       <c r="M22" t="n">
-        <v>7.851</v>
+        <v>3.495</v>
       </c>
       <c r="P22" t="n">
-        <v>83.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-7.4</v>
+        <v>-5.5</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.75</v>
+        <v>2.27</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.1</v>
+        <v>30.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>715.745</v>
+        <v>66.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>-28.25</v>
+        <v>2.37</v>
       </c>
       <c r="AB22" t="n">
-        <v>-2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
@@ -1998,14 +1956,14 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>reports/india-sovereign-credit.md</t>
+          <t>reports/hungary-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2015,47 +1973,47 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8821</v>
+        <v>4.4412</v>
       </c>
       <c r="I23" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="J23" t="n">
-        <v>2.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1</v>
+        <v>-2</v>
       </c>
       <c r="L23" t="n">
-        <v>146.492</v>
+        <v>751.764</v>
       </c>
       <c r="M23" t="n">
-        <v>5.514</v>
+        <v>7.851</v>
       </c>
       <c r="P23" t="n">
-        <v>41.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9</v>
+        <v>-7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.03</v>
+        <v>-2.75</v>
       </c>
       <c r="Y23" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>715.745</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-28.25</v>
+      </c>
+      <c r="AB23" t="n">
         <v>-2.8</v>
       </c>
-      <c r="Z23" t="n">
-        <v>75.541</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-14.36</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AF23" t="inlineStr">
         <is>
           <t>08-Oct-26</t>
@@ -2063,138 +2021,138 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>reports/indonesia-sovereign-credit.md</t>
+          <t>reports/india-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MENA</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>None active (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
-        </is>
-      </c>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>-6.8</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>3.0928</v>
+        <v>2.8821</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.87</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.3</v>
+        <v>-1.1</v>
       </c>
       <c r="L24" t="n">
-        <v>80.59999999999999</v>
+        <v>146.492</v>
       </c>
       <c r="M24" t="n">
-        <v>9.6</v>
+        <v>5.514</v>
       </c>
       <c r="P24" t="n">
-        <v>57</v>
+        <v>41.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.2</v>
+        <v>-2.9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-3.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>-10.9</v>
+        <v>-2.8</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>75.541</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.92</v>
+        <v>-14.36</v>
       </c>
       <c r="AB24" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0.50625</v>
+        <v>0.4</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>reports/iraq-sovereign-credit.md</t>
+          <t>reports/indonesia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Middle East</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>MENA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Caa1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>None active (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
+        </is>
+      </c>
       <c r="G25" t="n">
-        <v>3.5</v>
+        <v>-6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.71</v>
+        <v>3.0928</v>
       </c>
       <c r="K25" t="n">
-        <v>1.9</v>
+        <v>-5.3</v>
       </c>
       <c r="L25" t="n">
-        <v>241.63</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>14.36</v>
+        <v>9.6</v>
       </c>
       <c r="P25" t="n">
-        <v>69.8</v>
+        <v>57</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.67</v>
+        <v>-4.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>232.204</v>
+        <v>-10.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.53</v>
+        <v>4.92</v>
       </c>
       <c r="AB25" t="n">
-        <v>-1.6</v>
+        <v>16.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.50625</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
@@ -2203,85 +2161,63 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>reports/israel-sovereign-credit.md</t>
+          <t>reports/iraq-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Middle East (CEEMEA)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Ba3</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Extended Fund Facility (4-year, SDR 926.37m; Fifth Review completed Jun-26, with RSF)</t>
-        </is>
-      </c>
+          <t>Middle East</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="H26" t="n">
-        <v>2.7011</v>
+        <v>1.54</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="J26" t="n">
-        <v>3.3</v>
+        <v>1.71</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.2</v>
+        <v>1.9</v>
       </c>
       <c r="L26" t="n">
-        <v>28.5</v>
+        <v>241.63</v>
       </c>
       <c r="M26" t="n">
-        <v>9.199999999999999</v>
+        <v>14.36</v>
       </c>
       <c r="P26" t="n">
-        <v>83.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>-2.8</v>
+        <v>-5.9</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.67</v>
       </c>
       <c r="Y26" t="n">
-        <v>23</v>
+        <v>4.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.01</v>
+        <v>232.204</v>
       </c>
       <c r="AA26" t="n">
-        <v>-3.11</v>
+        <v>4.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.95</v>
+        <v>-1.6</v>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
@@ -2290,75 +2226,85 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>reports/jordan-sovereign-credit.md</t>
+          <t>reports/israel-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CIS / Central Asia</t>
+          <t>Middle East (CEEMEA)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Baa1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>Ba3</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Extended Fund Facility (4-year, SDR 926.37m; Fifth Review completed Jun-26, with RSF)</t>
+        </is>
+      </c>
       <c r="G27" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="H27" t="n">
-        <v>9.24</v>
+        <v>2.7011</v>
       </c>
       <c r="I27" t="n">
-        <v>16.75</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>7.51</v>
+        <v>3.3</v>
       </c>
       <c r="K27" t="n">
-        <v>-1</v>
+        <v>-6.2</v>
       </c>
       <c r="L27" t="n">
-        <v>70.56999999999999</v>
+        <v>28.5</v>
       </c>
       <c r="M27" t="n">
-        <v>7.39</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>24.9</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.3</v>
+        <v>-5.2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-2.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>29.9</v>
+        <v>23</v>
       </c>
       <c r="Z27" t="n">
-        <v>59.792</v>
+        <v>21.01</v>
       </c>
       <c r="AA27" t="n">
-        <v>-13.41</v>
+        <v>-3.11</v>
       </c>
       <c r="AB27" t="n">
-        <v>11.5</v>
+        <v>-6.1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.95</v>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
@@ -2367,76 +2313,75 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>reports/kazakhstan-sovereign-credit.md</t>
+          <t>reports/jordan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>CIS / Central Asia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>None; prior EFF/ECF/RSF expired uncompleted Apr-25, successor talks ongoing</t>
-        </is>
-      </c>
+          <t>Baa1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H28" t="n">
-        <v>6.76</v>
+        <v>9.24</v>
       </c>
       <c r="I28" t="n">
-        <v>8.75</v>
+        <v>16.75</v>
       </c>
       <c r="J28" t="n">
-        <v>1.99</v>
+        <v>7.51</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.1</v>
+        <v>-1</v>
       </c>
       <c r="L28" t="n">
-        <v>14.702</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>4.632</v>
+        <v>7.39</v>
       </c>
       <c r="P28" t="n">
-        <v>68.5</v>
+        <v>24.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>33</v>
+        <v>-1.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>34.7</v>
+        <v>29.9</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>59.792</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-13.41</v>
       </c>
       <c r="AB28" t="n">
-        <v>-2.9</v>
+        <v>11.5</v>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
@@ -2445,72 +2390,76 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>reports/kenya-sovereign-credit.md</t>
+          <t>reports/kazakhstan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Middle East (GCC)</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>None; prior EFF/ECF/RSF expired uncompleted Apr-25, successor talks ongoing</t>
+        </is>
+      </c>
       <c r="G29" t="n">
-        <v>-0.6</v>
+        <v>4.5</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="I29" t="n">
-        <v>3.5</v>
+        <v>8.75</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="K29" t="n">
-        <v>18.8</v>
+        <v>-4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>32.689</v>
+        <v>14.702</v>
       </c>
       <c r="M29" t="n">
-        <v>8.4</v>
+        <v>4.632</v>
       </c>
       <c r="P29" t="n">
-        <v>2.9</v>
+        <v>68.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>-18.5</v>
+        <v>-6.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>33</v>
       </c>
       <c r="Y29" t="n">
-        <v>-23.4</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>32.54</v>
+        <v>34.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>28.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
@@ -2519,55 +2468,72 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>reports/kuwait-sovereign-credit.md</t>
+          <t>reports/kenya-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MENA</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>None; mission of 15-18 Sep-26 ended without staff-level agreement</t>
-        </is>
-      </c>
+          <t>Middle East (GCC)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>-0.6</v>
       </c>
       <c r="H30" t="n">
-        <v>16.66</v>
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>-22.5</v>
+        <v>18.8</v>
       </c>
       <c r="L30" t="n">
-        <v>38.16</v>
+        <v>32.689</v>
       </c>
       <c r="M30" t="n">
-        <v>13.6</v>
+        <v>8.4</v>
       </c>
       <c r="P30" t="n">
-        <v>139.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>-18.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>31.2</v>
+        <v>-23.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>-9.16</v>
+        <v>32.54</v>
       </c>
       <c r="AB30" t="n">
-        <v>-4.6</v>
+        <v>28.1</v>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
@@ -2576,128 +2542,120 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>reports/lebanon-sovereign-credit.md</t>
+          <t>reports/kuwait-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>MENA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>None; mission of 15-18 Sep-26 ended without staff-level agreement</t>
+        </is>
+      </c>
       <c r="G31" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>1.7817</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.97</v>
+        <v>16.66</v>
       </c>
       <c r="K31" t="n">
-        <v>1.4</v>
+        <v>-22.5</v>
       </c>
       <c r="L31" t="n">
-        <v>131.981</v>
+        <v>38.16</v>
       </c>
       <c r="M31" t="n">
-        <v>4.276</v>
+        <v>13.6</v>
       </c>
       <c r="P31" t="n">
-        <v>69.5</v>
+        <v>139.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>97.798</v>
+        <v>31.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>10.37</v>
+        <v>-9.16</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>-4.6</v>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>reports/malaysia-sovereign-credit.md</t>
+          <t>reports/lebanon-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="H32" t="n">
-        <v>3.2619</v>
+        <v>1.7817</v>
       </c>
       <c r="I32" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="J32" t="n">
-        <v>3.24</v>
+        <v>0.97</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.4</v>
+        <v>1.4</v>
       </c>
       <c r="L32" t="n">
-        <v>265.969</v>
+        <v>131.981</v>
       </c>
       <c r="M32" t="n">
-        <v>3.73</v>
+        <v>4.276</v>
       </c>
       <c r="P32" t="n">
-        <v>62.7</v>
+        <v>69.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>-4.4</v>
+        <v>-3.3</v>
       </c>
       <c r="X32" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>250.968</v>
+        <v>97.798</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.7</v>
+        <v>10.37</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
@@ -2706,138 +2664,116 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>reports/mexico-sovereign-credit.md</t>
+          <t>reports/malaysia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Western Balkans (CEEMEA)</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H33" t="n">
-        <v>3.6043</v>
+        <v>3.2619</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.24</v>
       </c>
       <c r="K33" t="n">
-        <v>-19.4</v>
+        <v>-0.4</v>
       </c>
       <c r="L33" t="n">
-        <v>2.196</v>
+        <v>265.969</v>
       </c>
       <c r="M33" t="n">
-        <v>3.947</v>
+        <v>3.73</v>
       </c>
       <c r="P33" t="n">
-        <v>63.5</v>
+        <v>62.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>-4</v>
+        <v>-4.4</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>26.1</v>
+        <v>6.8</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>250.968</v>
       </c>
       <c r="AA33" t="n">
-        <v>-2.07</v>
+        <v>-0.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>-1.6</v>
+        <v>0.3</v>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>reports/montenegro-sovereign-credit.md</t>
+          <t>reports/mexico-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>BB+</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>BBB-</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Ba1</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review completed Mar-26; RSF SDR 1.0bn approved Sep-23</t>
-        </is>
-      </c>
+          <t>Western Balkans (CEEMEA)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3333</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.58</v>
+        <v>3.6043</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.1</v>
+        <v>-19.4</v>
       </c>
       <c r="L34" t="n">
-        <v>55.65</v>
+        <v>2.196</v>
       </c>
       <c r="M34" t="n">
-        <v>5.5</v>
+        <v>3.947</v>
       </c>
       <c r="P34" t="n">
-        <v>67.2</v>
+        <v>63.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="X34" t="n">
-        <v>-2.1</v>
+        <v>-4</v>
       </c>
       <c r="Y34" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>50.756</v>
+        <v>26.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>-5.83</v>
+        <v>-2.07</v>
       </c>
       <c r="AB34" t="n">
-        <v>-3.2</v>
+        <v>-1.6</v>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
@@ -2846,79 +2782,85 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>reports/morocco-sovereign-credit.md</t>
+          <t>reports/montenegro-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CCC (LC: SD)</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Caa3</t>
+          <t>Ba1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>None; 2022 ECF (SDR 340.8m) lapsed Apr-25; successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review completed Mar-26; RSF SDR 1.0bn approved Sep-23</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="H35" t="n">
-        <v>6.5</v>
+        <v>-0.3333</v>
       </c>
       <c r="I35" t="n">
-        <v>9.25</v>
+        <v>2.25</v>
       </c>
       <c r="J35" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="K35" t="n">
-        <v>-43</v>
+        <v>-3.1</v>
       </c>
       <c r="L35" t="n">
-        <v>3.9</v>
+        <v>55.65</v>
       </c>
       <c r="M35" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="P35" t="n">
-        <v>94</v>
+        <v>67.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>-6.5</v>
+        <v>-3.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>-2.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>4.9</v>
+        <v>18</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>50.756</v>
       </c>
       <c r="AA35" t="n">
-        <v>-2.95</v>
+        <v>-5.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.9</v>
+        <v>-3.2</v>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
@@ -2927,14 +2869,14 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>reports/mozambique-sovereign-credit.md</t>
+          <t>reports/morocco-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2942,39 +2884,64 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CCC (LC: SD)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Caa3</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>None; 2022 ECF (SDR 340.8m) lapsed Apr-25; successor arrangement under discussion after Sep-26 staff mission</t>
+        </is>
+      </c>
       <c r="G36" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="H36" t="n">
-        <v>4.4106</v>
+        <v>6.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.75</v>
       </c>
       <c r="K36" t="n">
-        <v>-15.7</v>
+        <v>-43</v>
       </c>
       <c r="L36" t="n">
-        <v>3.252</v>
+        <v>3.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.958</v>
+        <v>6.5</v>
       </c>
       <c r="P36" t="n">
-        <v>70.5</v>
+        <v>94</v>
       </c>
       <c r="Q36" t="n">
-        <v>-6.1</v>
+        <v>-6.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.151</v>
+        <v>4.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>-1.86</v>
+        <v>-2.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.9</v>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
@@ -2983,84 +2950,54 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>reports/namibia-sovereign-credit.md</t>
+          <t>reports/mozambique-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>B3</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="H37" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="I37" t="n">
-        <v>23</v>
-      </c>
-      <c r="J37" t="n">
-        <v>7.61</v>
+        <v>4.4106</v>
       </c>
       <c r="K37" t="n">
-        <v>5.8</v>
+        <v>-15.7</v>
       </c>
       <c r="L37" t="n">
-        <v>54.98</v>
+        <v>3.252</v>
       </c>
       <c r="M37" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O37" t="n">
-        <v>14.4</v>
+        <v>3.958</v>
       </c>
       <c r="P37" t="n">
-        <v>32.3</v>
+        <v>70.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="S37" t="n">
-        <v>55</v>
-      </c>
-      <c r="X37" t="n">
-        <v>-0.51</v>
+        <v>-6.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>30.8</v>
+        <v>-6.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.151</v>
       </c>
       <c r="AA37" t="n">
-        <v>15.61</v>
+        <v>-1.86</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>15.12</v>
+        <v>0.8</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -3069,80 +3006,84 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>reports/nigeria-sovereign-credit.md</t>
+          <t>reports/namibia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CEEMEA - Western Balkans</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>PLL concluded Nov-24</t>
-        </is>
-      </c>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="H38" t="n">
-        <v>2.5729</v>
+        <v>15.39</v>
       </c>
       <c r="I38" t="n">
-        <v>4.25</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>1.68</v>
+        <v>7.61</v>
       </c>
       <c r="K38" t="n">
-        <v>-5</v>
+        <v>5.8</v>
       </c>
       <c r="L38" t="n">
-        <v>5.51</v>
+        <v>54.98</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O38" t="n">
+        <v>14.4</v>
       </c>
       <c r="P38" t="n">
-        <v>55.2</v>
+        <v>32.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>-4.2</v>
+        <v>-4.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>55</v>
       </c>
       <c r="X38" t="n">
-        <v>1.52</v>
+        <v>-0.51</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.474</v>
+        <v>30.8</v>
       </c>
       <c r="AA38" t="n">
-        <v>-0.99</v>
+        <v>15.61</v>
       </c>
       <c r="AB38" t="n">
-        <v>-2.6</v>
+        <v>4.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.16</v>
+        <v>15.12</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -3151,67 +3092,80 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>reports/north-macedonia-sovereign-credit.md</t>
+          <t>reports/nigeria-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Middle East (GCC)</t>
+          <t>CEEMEA - Western Balkans</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BBB-</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Baa3</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>PLL concluded Nov-24</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="H39" t="n">
-        <v>3.3771</v>
+        <v>2.5729</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.68</v>
       </c>
       <c r="K39" t="n">
-        <v>2.5</v>
+        <v>-5</v>
       </c>
       <c r="L39" t="n">
-        <v>18.38</v>
+        <v>5.51</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="P39" t="n">
-        <v>34.7</v>
+        <v>55.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.6</v>
+        <v>-4.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.52</v>
       </c>
       <c r="Y39" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>4.474</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-0.99</v>
       </c>
       <c r="AB39" t="n">
-        <v>15.6</v>
+        <v>-2.6</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.16</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -3220,54 +3174,67 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>reports/oman-sovereign-credit.md</t>
+          <t>reports/north-macedonia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>South Asia</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>Middle East (GCC)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Baa3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
       <c r="G40" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="H40" t="n">
-        <v>10.2591</v>
+        <v>3.3771</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.4</v>
+        <v>2.5</v>
       </c>
       <c r="L40" t="n">
-        <v>27.993</v>
+        <v>18.38</v>
       </c>
       <c r="M40" t="n">
-        <v>3.755</v>
+        <v>5</v>
       </c>
       <c r="P40" t="n">
-        <v>70.09999999999999</v>
+        <v>34.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.02</v>
+        <v>0.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>-0.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB40" t="n">
-        <v>-2.3</v>
+        <v>15.6</v>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
@@ -3276,128 +3243,119 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>reports/pakistan-sovereign-credit.md</t>
+          <t>reports/oman-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="H41" t="n">
-        <v>4.0636</v>
-      </c>
-      <c r="I41" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.19</v>
+        <v>10.2591</v>
       </c>
       <c r="K41" t="n">
-        <v>3.4</v>
+        <v>-0.4</v>
       </c>
       <c r="L41" t="n">
-        <v>95.26900000000001</v>
+        <v>27.993</v>
       </c>
       <c r="M41" t="n">
-        <v>10.423</v>
+        <v>3.755</v>
       </c>
       <c r="P41" t="n">
-        <v>30</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>-2</v>
+        <v>-3.2</v>
       </c>
       <c r="X41" t="n">
-        <v>1.8</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>87.288</v>
+        <v>22.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>12.01</v>
+        <v>-0.14</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.5</v>
+        <v>-2.3</v>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>reports/peru-sovereign-credit.md</t>
+          <t>reports/pakistan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="H42" t="n">
-        <v>6.3629</v>
+        <v>4.0636</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.36</v>
+        <v>0.19</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.4</v>
+        <v>3.4</v>
       </c>
       <c r="L42" t="n">
-        <v>103.316</v>
+        <v>95.26900000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>7.306</v>
+        <v>10.423</v>
       </c>
       <c r="P42" t="n">
-        <v>60.2</v>
+        <v>30</v>
       </c>
       <c r="Q42" t="n">
-        <v>-3.7</v>
+        <v>-2</v>
       </c>
       <c r="X42" t="n">
-        <v>-0.19</v>
+        <v>1.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>-2</v>
+        <v>16.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>93.018</v>
+        <v>87.288</v>
       </c>
       <c r="AA42" t="n">
-        <v>-22.11</v>
+        <v>12.01</v>
       </c>
       <c r="AB42" t="n">
-        <v>-1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
@@ -3406,63 +3364,63 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>reports/philippines-sovereign-credit.md</t>
+          <t>reports/peru-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2123</v>
+        <v>6.3629</v>
       </c>
       <c r="I43" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
-        <v>0.54</v>
+        <v>-1.36</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.1</v>
+        <v>-4.4</v>
       </c>
       <c r="L43" t="n">
-        <v>304.971</v>
+        <v>103.316</v>
       </c>
       <c r="M43" t="n">
-        <v>5.861</v>
+        <v>7.306</v>
       </c>
       <c r="P43" t="n">
-        <v>65.7</v>
+        <v>60.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>-6.7</v>
+        <v>-3.7</v>
       </c>
       <c r="X43" t="n">
-        <v>1.5</v>
+        <v>-0.19</v>
       </c>
       <c r="Y43" t="n">
-        <v>16.9</v>
+        <v>-2</v>
       </c>
       <c r="Z43" t="n">
-        <v>277.21</v>
+        <v>93.018</v>
       </c>
       <c r="AA43" t="n">
-        <v>-13.87</v>
+        <v>-22.11</v>
       </c>
       <c r="AB43" t="n">
-        <v>-1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
@@ -3471,279 +3429,279 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>reports/poland-sovereign-credit.md</t>
+          <t>reports/philippines-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GCC</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AA</t>
+          <t>Central Europe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>-8.6</v>
+        <v>3.3</v>
       </c>
       <c r="H44" t="n">
-        <v>0.73</v>
+        <v>3.2123</v>
       </c>
       <c r="I44" t="n">
-        <v>4.35</v>
+        <v>3.75</v>
       </c>
       <c r="J44" t="n">
-        <v>3.62</v>
+        <v>0.54</v>
       </c>
       <c r="K44" t="n">
-        <v>11</v>
+        <v>-1.1</v>
       </c>
       <c r="L44" t="n">
-        <v>61.1</v>
+        <v>304.971</v>
       </c>
       <c r="M44" t="n">
-        <v>7.45</v>
+        <v>5.861</v>
       </c>
       <c r="P44" t="n">
-        <v>43.3</v>
+        <v>65.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>-3.4</v>
+        <v>-6.7</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>10.4</v>
+        <v>16.9</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>277.21</v>
       </c>
       <c r="AA44" t="n">
-        <v>28.52</v>
+        <v>-13.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>14.7</v>
+        <v>-1.1</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>reports/qatar-sovereign-credit.md</t>
+          <t>reports/poland-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>GCC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>0.7</v>
+        <v>-8.6</v>
       </c>
       <c r="H45" t="n">
-        <v>8.16</v>
+        <v>0.73</v>
       </c>
       <c r="I45" t="n">
-        <v>6.5</v>
+        <v>4.35</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.66</v>
+        <v>3.62</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.8</v>
+        <v>11</v>
       </c>
       <c r="L45" t="n">
-        <v>90.04300000000001</v>
+        <v>61.1</v>
       </c>
       <c r="M45" t="n">
-        <v>5.528</v>
+        <v>7.45</v>
       </c>
       <c r="P45" t="n">
-        <v>61.9</v>
+        <v>43.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.95</v>
+        <v>-3.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>72.172</v>
+        <v>10.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>-32.2</v>
+        <v>28.52</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.5</v>
+        <v>14.7</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>reports/romania-sovereign-credit.md</t>
+          <t>reports/qatar-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>38-month ECF (reported)</t>
-        </is>
-      </c>
+          <t>Central Europe</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>9.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H46" t="n">
-        <v>15.7</v>
+        <v>8.16</v>
       </c>
       <c r="I46" t="n">
-        <v>8.75</v>
+        <v>6.5</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.95</v>
+        <v>-1.66</v>
       </c>
       <c r="K46" t="n">
-        <v>-15</v>
+        <v>-6.8</v>
       </c>
       <c r="L46" t="n">
-        <v>2.2</v>
+        <v>90.04300000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
-      </c>
-      <c r="O46" t="n">
-        <v>63</v>
+        <v>5.528</v>
       </c>
       <c r="P46" t="n">
-        <v>77.5</v>
+        <v>61.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>-4.8</v>
+        <v>-6.2</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.95</v>
       </c>
       <c r="Y46" t="n">
-        <v>-16.4</v>
+        <v>2.9</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.795</v>
+        <v>72.172</v>
       </c>
       <c r="AA46" t="n">
-        <v>-1.98</v>
+        <v>-32.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0.62</v>
+        <v>-0.5</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>reports/rwanda-sovereign-credit.md</t>
+          <t>reports/romania-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Middle East</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>38-month ECF (reported)</t>
+        </is>
+      </c>
       <c r="G47" t="n">
-        <v>3.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>1.82</v>
+        <v>15.7</v>
       </c>
       <c r="I47" t="n">
-        <v>4.5</v>
+        <v>8.75</v>
       </c>
       <c r="J47" t="n">
-        <v>2.68</v>
+        <v>-6.95</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.6</v>
+        <v>-15</v>
       </c>
       <c r="L47" t="n">
-        <v>488.684</v>
+        <v>2.2</v>
       </c>
       <c r="M47" t="n">
-        <v>15.6</v>
+        <v>4</v>
+      </c>
+      <c r="O47" t="n">
+        <v>63</v>
       </c>
       <c r="P47" t="n">
-        <v>32.1</v>
+        <v>77.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="X47" t="n">
-        <v>-0.31</v>
+        <v>-4.8</v>
       </c>
       <c r="Y47" t="n">
-        <v>10</v>
+        <v>-16.4</v>
       </c>
       <c r="Z47" t="n">
-        <v>482.147</v>
+        <v>1.795</v>
       </c>
       <c r="AA47" t="n">
-        <v>-25.78</v>
+        <v>-1.98</v>
       </c>
       <c r="AB47" t="n">
-        <v>15.9</v>
+        <v>-0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0.62</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
@@ -3752,62 +3710,63 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>reports/saudi-arabia-sovereign-credit.md</t>
+          <t>reports/rwanda-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa (WAEMU)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Caa2</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Staff-level agreement on new arrangement replacing suspended USD 1.8B facility; Board consideration 15-Dec-26</t>
-        </is>
-      </c>
+          <t>Middle East</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="H48" t="n">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
-        <v>1.8</v>
+        <v>2.68</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.2</v>
+        <v>-1.6</v>
+      </c>
+      <c r="L48" t="n">
+        <v>488.684</v>
+      </c>
+      <c r="M48" t="n">
+        <v>15.6</v>
       </c>
       <c r="P48" t="n">
-        <v>132</v>
+        <v>32.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>-6.7</v>
+        <v>-3.5</v>
+      </c>
+      <c r="X48" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>482.147</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-25.78</v>
       </c>
       <c r="AB48" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
@@ -3816,82 +3775,62 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>reports/senegal-sovereign-credit.md</t>
+          <t>reports/saudi-arabia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CEEMEA - Western Balkans</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>BB+</t>
+          <t>Sub-Saharan Africa (WAEMU)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ba2</t>
+          <t>Caa2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Policy Coordination Instrument (36-month, non-financing)</t>
+          <t>Staff-level agreement on new arrangement replacing suspended USD 1.8B facility; Board consideration 15-Dec-26</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="H49" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="I49" t="n">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="M49" t="n">
-        <v>6.2</v>
+        <v>-6.2</v>
       </c>
       <c r="P49" t="n">
-        <v>43.3</v>
+        <v>132</v>
       </c>
       <c r="Q49" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>30.033</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>-4.36</v>
+        <v>-6.7</v>
       </c>
       <c r="AB49" t="n">
-        <v>-1.4</v>
+        <v>-2.4</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.2</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
@@ -3900,29 +3839,29 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>reports/serbia-sovereign-credit.md</t>
+          <t>reports/senegal-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>CEEMEA - Western Balkans</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3932,53 +3871,50 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>Policy Coordination Instrument (36-month, non-financing)</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="H50" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="I50" t="n">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="J50" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.6</v>
+        <v>-4.1</v>
       </c>
       <c r="L50" t="n">
-        <v>75.95999999999999</v>
+        <v>35.71</v>
       </c>
       <c r="M50" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="P50" t="n">
-        <v>77.2</v>
+        <v>43.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="S50" t="n">
-        <v>20</v>
+        <v>-3.25</v>
       </c>
       <c r="X50" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="Y50" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Z50" t="n">
-        <v>74.307</v>
+        <v>30.033</v>
       </c>
       <c r="AA50" t="n">
-        <v>-1.32</v>
+        <v>-4.36</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.9</v>
+        <v>-1.4</v>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
@@ -3987,51 +3923,85 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>reports/south-africa-sovereign-credit.md</t>
+          <t>reports/serbia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Central Asia</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>None (Article IV)</t>
+        </is>
+      </c>
       <c r="G51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>4.0609</v>
+        <v>4.4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.9</v>
       </c>
       <c r="K51" t="n">
-        <v>6.3</v>
+        <v>-1.6</v>
       </c>
       <c r="L51" t="n">
-        <v>6.395</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>5.749</v>
+        <v>5.8</v>
       </c>
       <c r="P51" t="n">
-        <v>21.9</v>
+        <v>77.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>-2.5</v>
+        <v>-3.8</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.23</v>
       </c>
       <c r="Y51" t="n">
-        <v>45.9</v>
+        <v>7.8</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>74.307</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.48</v>
+        <v>-1.32</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
@@ -4040,228 +4010,195 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>reports/tajikistan-sovereign-credit.md</t>
+          <t>reports/south-africa-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>2.5265</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" t="n">
-        <v>-1.53</v>
+        <v>4.0609</v>
       </c>
       <c r="K52" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="L52" t="n">
-        <v>283.137</v>
+        <v>6.395</v>
       </c>
       <c r="M52" t="n">
-        <v>8.051</v>
+        <v>5.749</v>
       </c>
       <c r="P52" t="n">
-        <v>66.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q52" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0.21</v>
+        <v>-2.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>302.852</v>
+        <v>45.9</v>
       </c>
       <c r="AA52" t="n">
-        <v>8.08</v>
+        <v>3.48</v>
       </c>
       <c r="AB52" t="n">
-        <v>-3.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>reports/thailand-sovereign-credit.md</t>
+          <t>reports/tajikistan-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Caa1</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board; frozen</t>
-        </is>
-      </c>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="H53" t="n">
-        <v>5.6</v>
+        <v>2.5265</v>
       </c>
       <c r="I53" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1.4</v>
+        <v>-1.53</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.2</v>
+        <v>0.7</v>
       </c>
       <c r="L53" t="n">
-        <v>9.079000000000001</v>
+        <v>283.137</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>8.051</v>
       </c>
       <c r="P53" t="n">
-        <v>82</v>
+        <v>66.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>-5.2</v>
+        <v>-2.2</v>
       </c>
       <c r="X53" t="n">
-        <v>1.63</v>
+        <v>0.21</v>
       </c>
       <c r="Y53" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>302.852</v>
       </c>
       <c r="AA53" t="n">
-        <v>-1.33</v>
+        <v>8.08</v>
       </c>
       <c r="AB53" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0.15</v>
+        <v>-3.9</v>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>reports/tunisia-sovereign-credit.md</t>
+          <t>reports/thailand-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CEEMEA</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BB-</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BB-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ba3</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>Caa1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board; frozen</t>
+        </is>
+      </c>
       <c r="G54" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="H54" t="n">
-        <v>29.73</v>
+        <v>5.6</v>
       </c>
       <c r="I54" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="J54" t="n">
-        <v>12.5</v>
+        <v>1.4</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.7</v>
+        <v>-4.2</v>
       </c>
       <c r="L54" t="n">
-        <v>174.4</v>
+        <v>9.079000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>5.128</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O54" t="n">
-        <v>31.8</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
-        <v>29.5</v>
+        <v>82</v>
       </c>
       <c r="Q54" t="n">
         <v>-5.2</v>
       </c>
       <c r="X54" t="n">
-        <v>0.31</v>
+        <v>1.63</v>
       </c>
       <c r="Y54" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>137.109</v>
+        <v>6.8</v>
       </c>
       <c r="AA54" t="n">
-        <v>-38.89</v>
+        <v>-1.33</v>
       </c>
       <c r="AB54" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0.15</v>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
@@ -4270,14 +4207,14 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>reports/turkey-sovereign-credit.md</t>
+          <t>reports/tunisia-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4287,65 +4224,67 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CCC+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ca</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
-        </is>
-      </c>
+          <t>Ba3</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="H55" t="n">
-        <v>8.1</v>
+        <v>29.73</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J55" t="n">
-        <v>7.9</v>
+        <v>12.5</v>
       </c>
       <c r="K55" t="n">
-        <v>-18.9</v>
+        <v>-2.7</v>
       </c>
       <c r="L55" t="n">
-        <v>47.1</v>
+        <v>174.4</v>
       </c>
       <c r="M55" t="n">
-        <v>5.6</v>
+        <v>5.128</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O55" t="n">
+        <v>31.8</v>
       </c>
       <c r="P55" t="n">
-        <v>98.40000000000001</v>
+        <v>29.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>-18.4</v>
+        <v>-5.2</v>
       </c>
       <c r="X55" t="n">
-        <v>-0.5</v>
+        <v>0.31</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="Z55" t="n">
-        <v>38.646</v>
+        <v>137.109</v>
       </c>
       <c r="AA55" t="n">
-        <v>-24.81</v>
+        <v>-38.89</v>
       </c>
       <c r="AB55" t="n">
-        <v>-2.3</v>
+        <v>-1</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
@@ -4354,61 +4293,82 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>reports/ukraine-sovereign-credit.md</t>
+          <t>reports/turkey-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MENA / GCC</t>
+          <t>CEEMEA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>CCC+</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
+        </is>
+      </c>
       <c r="G56" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>2.05</v>
+        <v>8.1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>16</v>
+      </c>
+      <c r="J56" t="n">
+        <v>7.9</v>
       </c>
       <c r="K56" t="n">
-        <v>11.4</v>
+        <v>-18.9</v>
       </c>
       <c r="L56" t="n">
-        <v>259.7</v>
+        <v>47.1</v>
       </c>
       <c r="M56" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="P56" t="n">
-        <v>31.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.9</v>
+        <v>-18.4</v>
       </c>
       <c r="X56" t="n">
-        <v>-1.12</v>
+        <v>-0.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>-3.1</v>
+        <v>5.7</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>38.646</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-24.81</v>
       </c>
       <c r="AB56" t="n">
-        <v>13.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
@@ -4417,73 +4377,61 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>reports/uae-sovereign-credit.md</t>
+          <t>reports/ukraine-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Central Asia / CIS</t>
+          <t>MENA / GCC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Ba2</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>None (Article IV surveillance only)</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>8.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="H57" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>14</v>
-      </c>
-      <c r="J57" t="n">
-        <v>7.8</v>
+        <v>2.05</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.3</v>
+        <v>11.4</v>
       </c>
       <c r="L57" t="n">
-        <v>72.13</v>
+        <v>259.7</v>
       </c>
       <c r="M57" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="P57" t="n">
-        <v>27</v>
+        <v>31.4</v>
       </c>
       <c r="Q57" t="n">
-        <v>-2.1</v>
+        <v>4.9</v>
+      </c>
+      <c r="X57" t="n">
+        <v>-1.12</v>
       </c>
       <c r="Y57" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>-11.23</v>
+        <v>-3.1</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>13.2</v>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
@@ -4492,89 +4440,164 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>reports/uzbekistan-sovereign-credit.md</t>
+          <t>reports/uae-sovereign-credit.md</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Central Asia / CIS</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ba2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>None (Article IV surveillance only)</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H58" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>14</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="L58" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="M58" t="n">
+        <v>12</v>
+      </c>
+      <c r="P58" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-11.23</v>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>09-Oct-26</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>reports/uzbekistan-sovereign-credit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>CCC+</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Caa2</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>38-month ECF completed Jan-26 (sixth and final review); successor programme under negotiation</t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="G59" t="n">
         <v>4.3</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H59" t="n">
         <v>6.1</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I59" t="n">
         <v>10.75</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J59" t="n">
         <v>4.65</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K59" t="n">
         <v>0.9</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L59" t="n">
         <v>5.8</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M59" t="n">
         <v>4.2</v>
       </c>
-      <c r="P58" t="n">
+      <c r="P59" t="n">
         <v>91</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="Q59" t="n">
         <v>-4.9</v>
       </c>
-      <c r="S58" t="n">
+      <c r="S59" t="n">
         <v>35</v>
       </c>
-      <c r="X58" t="n">
+      <c r="X59" t="n">
         <v>2.27</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Y59" t="n">
         <v>25.6</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AA59" t="n">
         <v>-0.9</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AB59" t="n">
         <v>5.1</v>
       </c>
-      <c r="AF58" t="inlineStr">
+      <c r="AF59" t="inlineStr">
         <is>
           <t>09-Oct-26</t>
         </is>
       </c>
-      <c r="AG58" t="inlineStr">
+      <c r="AG59" t="inlineStr">
         <is>
           <t>reports/zambia-sovereign-credit.md</t>
         </is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CEEMEA - Southeast Europe (Western Balkans)</t>
+          <t>CEEMEA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CEEMEA - South Caucasus</t>
+          <t>Caucasus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3-year Stand-By Arrangement (precautionary)</t>
+          <t>3-year precautionary Stand-By Arrangement</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CEEMEA - South Caucasus</t>
+          <t>CEEMEA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>None active (Article IV surveillance only)</t>
+          <t>None (Article IV surveillance only)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Middle East (GCC)</t>
+          <t>CEEMEA - GCC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa (WAEMU)</t>
+          <t>Sub-Saharan Africa (West Africa, WAEMU)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EFF/ECF (42-month, blended) and RSF arrangements, completed</t>
+          <t>42-month blended EFF/ECF and RSF arrangements, completed (final review)</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa (CEMAC)</t>
+          <t>Central Africa (CEMAC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>EFF/ECF (final sixth reviews completed) and RSF (fifth review completed), Jun-26</t>
+          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B); final reviews completed</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EFF (with RSF)</t>
+          <t>Extended Fund Facility (EFF)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>48-month Extended Credit Facility (ECF)</t>
+          <t>Extended Credit Facility (48-month)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CCC-</t>
+          <t>CCC- (LTFC IDR); LTLC CC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1681,7 +1681,11 @@
           <t>Caa2</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>None (2021 Extended Fund Facility expired; Sep-26 staff mission ended without Staff-Level Agreement)</t>
+        </is>
+      </c>
       <c r="G18" t="n">
         <v>2.7</v>
       </c>
@@ -2116,11 +2120,7 @@
           <t>Caa1</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>None active (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>-6.8</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>9.6</v>
       </c>
       <c r="P25" t="n">
-        <v>57</v>
+        <v>53.9</v>
       </c>
       <c r="Q25" t="n">
         <v>-4.2</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Middle East (CEEMEA)</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (4-year, SDR 926.37m; Fifth Review completed Jun-26, with RSF)</t>
+          <t>Extended Fund Facility (4-year), with RSF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CIS / Central Asia</t>
+          <t>CEEMEA (Central Asia)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>None; prior EFF/ECF/RSF expired uncompleted Apr-25, successor talks ongoing</t>
+          <t>None; prior EFF/ECF/RSF expired uncompleted Apr-25; successor talks ongoing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>None; mission of 15-18 Sep-26 ended without staff-level agreement</t>
+          <t>None; staff mission 15-18 Sep-26 ended without a staff-level agreement</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2572,7 +2572,7 @@
         <v>-22.5</v>
       </c>
       <c r="L31" t="n">
-        <v>38.16</v>
+        <v>38.164</v>
       </c>
       <c r="M31" t="n">
         <v>13.6</v>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review completed Mar-26; RSF SDR 1.0bn approved Sep-23</t>
+          <t>Flexible Credit Line (2-year, precautionary)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>None; 2022 ECF (SDR 340.8m) lapsed Apr-25; successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>2022 Extended Credit Facility (36-month; lapsed Apr-25 with fifth and sixth reviews uncompleted); successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CEEMEA - Western Balkans</t>
+          <t>Western Balkans (CEEMEA)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GCC</t>
+          <t>GCC / Middle East</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>38-month ECF (reported)</t>
+          <t>ECF, 38-month (reported, unverified); first-review staff-level agreement 06-Oct-26, SDR 26.43m</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Middle East (GCC)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Staff-level agreement on new arrangement replacing suspended USD 1.8B facility; Board consideration 15-Dec-26</t>
+          <t>Staff-level agreement on new arrangement replacing the suspended USD 1.8bn facility</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CEEMEA - Western Balkans</t>
+          <t>CEEMEA - Southeast Europe</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BB (foreign) / BB+ (local)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3983,7 +3983,7 @@
         <v>77.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>-3.8</v>
+        <v>-4.5</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>MENA / North Africa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board; frozen</t>
+          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board (frozen)</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
+          <t>4-year EFF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MENA / GCC</t>
+          <t>GCC / Middle East</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Central Asia / CIS</t>
+          <t>CIS / Central Asia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>None (Article IV surveillance only)</t>
+          <t>None active (Article IV surveillance and technical assistance only)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>38-month ECF completed Jan-26 (sixth and final review); successor programme under negotiation</t>
+          <t>38-month ECF, completed (sixth and final review, US$190m final disbursement); successor programme under negotiation</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CEEMEA</t>
+          <t>Europe (Western Balkans)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caucasus</t>
+          <t>Caucasus (CEEMEA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CEEMEA</t>
+          <t>CEEMEA (Caucasus)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CEEMEA - GCC</t>
+          <t>Middle East (GCC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -959,7 +959,7 @@
         <v>134</v>
       </c>
       <c r="Q7" t="n">
-        <v>-11</v>
+        <v>-10.8</v>
       </c>
       <c r="S7" t="n">
         <v>27.5</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa (West Africa, WAEMU)</t>
+          <t>Sub-Saharan Africa (WAEMU)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1015,11 +1015,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42-month blended EFF/ECF and RSF arrangements, completed (final review)</t>
+          <t>Blended EFF/ECF and RSF arrangements (42 months), completed with final review</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Central Africa (CEMAC)</t>
+          <t>Sub-Saharan Africa (CEMAC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>None active; ECF/EFF/RSF completed Jul-25, now Post-Financing Assessment</t>
+          <t>Post-Financing Assessment (ECF/EFF/RSF arrangements completed Jul-25)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B); final reviews completed</t>
+          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B), final reviews completed; no successor arrangement identified</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (EFF)</t>
+          <t>EFF (with RSF)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1554,7 +1554,7 @@
         <v>-12.1</v>
       </c>
       <c r="R16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Extended Credit Facility (48-month)</t>
+          <t>Extended Credit Facility (48 months)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CCC- (LTFC IDR); LTLC CC</t>
+          <t>CCC-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>None (2021 Extended Fund Facility expired; Sep-26 staff mission ended without Staff-Level Agreement)</t>
+          <t>None (2021 Extended Fund Facility expired; Sep-26 staff mission was surveillance only)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Caucasus</t>
+          <t>Caucasus / CEEMEA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36-month non-financing Policy Coordination Instrument (PCI), following completion of the US$3.0B ECF</t>
+          <t>Policy Coordination Instrument (36-month, non-financing), following the completed US$3.0B ECF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2120,7 +2120,11 @@
           <t>Caa1</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>None active (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
+        </is>
+      </c>
       <c r="G25" t="n">
         <v>-6.8</v>
       </c>
@@ -2258,7 +2262,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (4-year), with RSF</t>
+          <t>Extended Fund Facility (4-year, plus RSF)</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2325,7 +2329,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CEEMEA (Central Asia)</t>
+          <t>CEEMEA - Central Asia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2557,22 +2561,18 @@
           <t>MENA</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>None; staff mission 15-18 Sep-26 ended without a staff-level agreement</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>16.66</v>
+        <v>16.7</v>
       </c>
       <c r="K31" t="n">
         <v>-22.5</v>
       </c>
       <c r="L31" t="n">
-        <v>38.164</v>
+        <v>38.16</v>
       </c>
       <c r="M31" t="n">
         <v>13.6</v>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Western Balkans (CEEMEA)</t>
+          <t>Western Balkans</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>MENA / North Africa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2022 Extended Credit Facility (36-month; lapsed Apr-25 with fifth and sixth reviews uncompleted); successor arrangement under discussion after Sep-26 staff mission</t>
+          <t>None current; 2022 ECF (SDR 340.8m) lapsed Apr-25 with 5th and 6th reviews uncompleted; successor arrangement under discussion after Sep-26 staff mission</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Western Balkans (CEEMEA)</t>
+          <t>CEEMEA (Western Balkans)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GCC / Middle East</t>
+          <t>Middle East (GCC)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ECF, 38-month (reported, unverified); first-review staff-level agreement 06-Oct-26, SDR 26.43m</t>
+          <t>ECF, 38-month (reported, unverified)</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Staff-level agreement on new arrangement replacing the suspended USD 1.8bn facility</t>
+          <t>USD 2.2bn arrangement, staff-level agreement Sep-26, replacing suspended USD 1.8bn facility</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CEEMEA - Southeast Europe</t>
+          <t>CEEMEA - Europe (Western Balkans)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BB (foreign) / BB+ (local)</t>
+          <t>BB (foreign currency) / BB+ (local currency)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3983,7 +3983,7 @@
         <v>77.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>-4.5</v>
+        <v>-3.8</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>$1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board (frozen)</t>
+          <t>USD 1.9bn Extended Fund Facility agreed at staff level Oct-22; never approved by the Executive Board; frozen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>4-year EFF</t>
+          <t>4-year EFF (first review completed 20-Jul-26; SDR 503M, about $690M disbursed)</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GCC / Middle East</t>
+          <t>Middle East (GCC)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>38-month ECF, completed (sixth and final review, US$190m final disbursement); successor programme under negotiation</t>
+          <t>Successor programme under negotiation; 38-month US$1.3bn ECF completed Jan-26</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 09-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 12-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 12-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 15-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -1530,13 +1530,13 @@
         <v>4.2</v>
       </c>
       <c r="H16" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="I16" t="n">
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="K16" t="n">
         <v>-4.2</v>
@@ -1554,10 +1554,10 @@
         <v>-12.1</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="Y16" t="n">
         <v>14.7</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>15-Oct-26</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -1818,16 +1818,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Policy Coordination Instrument (36-month, non-financing), following the completed US$3.0B ECF</t>
+          <t>36-month non-financing Policy Coordination Instrument (PCI), following completion of the 39-month US$3bn ECF on 27-Jul-26</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
         <v>5.2</v>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>15-Oct-26</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2426,7 +2426,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>None; prior EFF/ECF/RSF expired uncompleted Apr-25; successor talks ongoing</t>
+          <t>None (previous EFF/ECF/RSF expired uncompleted Apr-25; new request Mar-25, no staff-level agreement; Article IV mission expected early Dec-26)</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2448,7 +2448,7 @@
         <v>14.702</v>
       </c>
       <c r="M29" t="n">
-        <v>4.632</v>
+        <v>4.63</v>
       </c>
       <c r="P29" t="n">
         <v>68.5</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>15-Oct-26</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 15-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 16-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
         <v>5.8</v>
       </c>
       <c r="L38" t="n">
-        <v>54.98</v>
+        <v>55.07</v>
       </c>
       <c r="M38" t="n">
         <v>9.199999999999999</v>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>16-Oct-26</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BB (foreign currency) / BB+ (local currency)</t>
+          <t>BB (FC) / BB+ (LC)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3953,11 +3953,7 @@
           <t>Ba2</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>None (Article IV)</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>1</v>
       </c>
@@ -3980,10 +3976,13 @@
         <v>5.8</v>
       </c>
       <c r="P51" t="n">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="Q51" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.6</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -4005,7 +4004,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>16-Oct-26</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 16-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 19-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -625,13 +625,13 @@
         <v>-2.8</v>
       </c>
       <c r="L3" t="n">
-        <v>8.6</v>
+        <v>9.347</v>
       </c>
       <c r="M3" t="n">
         <v>7.2</v>
       </c>
       <c r="N3" t="n">
-        <v>5.28</v>
+        <v>5.73</v>
       </c>
       <c r="O3" t="n">
         <v>39.7</v>
@@ -807,13 +807,13 @@
         <v>1.37</v>
       </c>
       <c r="Y5" t="n">
-        <v>53.9</v>
+        <v>55.3</v>
       </c>
       <c r="Z5" t="n">
         <v>3.708</v>
       </c>
       <c r="AA5" t="n">
-        <v>-2.52</v>
+        <v>-2.74</v>
       </c>
       <c r="AB5" t="n">
         <v>-1.1</v>
@@ -1075,19 +1075,19 @@
         <v>1.9</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2234</v>
+        <v>4.5761</v>
       </c>
       <c r="I9" t="n">
         <v>13.75</v>
       </c>
       <c r="J9" t="n">
-        <v>9.529999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="K9" t="n">
         <v>-2.7</v>
       </c>
       <c r="L9" t="n">
-        <v>372.615</v>
+        <v>362.979</v>
       </c>
       <c r="M9" t="n">
         <v>8.420999999999999</v>
@@ -1102,10 +1102,10 @@
         <v>-0.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>373.651</v>
+        <v>365.807</v>
       </c>
       <c r="AA9" t="n">
         <v>-59.09</v>
@@ -1224,13 +1224,13 @@
         <v>2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1322</v>
+        <v>4.0773</v>
       </c>
       <c r="I11" t="n">
         <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="K11" t="n">
         <v>-0.8</v>
@@ -1257,7 +1257,7 @@
         <v>47.964</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.16</v>
+        <v>0.91</v>
       </c>
       <c r="AB11" t="n">
         <v>2.4</v>
@@ -1289,13 +1289,13 @@
         <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>6.2417</v>
+        <v>6.2898</v>
       </c>
       <c r="I12" t="n">
         <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>5.76</v>
+        <v>5.71</v>
       </c>
       <c r="K12" t="n">
         <v>-2.5</v>
@@ -1746,19 +1746,19 @@
         <v>5.3</v>
       </c>
       <c r="H19" t="n">
-        <v>5.6478</v>
+        <v>5.5683</v>
       </c>
       <c r="I19" t="n">
         <v>8.25</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="K19" t="n">
         <v>-5</v>
       </c>
       <c r="L19" t="n">
-        <v>8.138999999999999</v>
+        <v>8.167999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>3.017</v>
@@ -1773,10 +1773,10 @@
         <v>1.22</v>
       </c>
       <c r="Y19" t="n">
-        <v>56.4</v>
+        <v>50.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.255</v>
+        <v>7.294</v>
       </c>
       <c r="AA19" t="n">
         <v>-0.72</v>
@@ -1915,19 +1915,19 @@
         <v>1.7</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2826</v>
+        <v>1.5398</v>
       </c>
       <c r="I22" t="n">
         <v>5.5</v>
       </c>
       <c r="J22" t="n">
-        <v>4.22</v>
+        <v>3.96</v>
       </c>
       <c r="K22" t="n">
         <v>-0.4</v>
       </c>
       <c r="L22" t="n">
-        <v>73.621</v>
+        <v>70.504</v>
       </c>
       <c r="M22" t="n">
         <v>3.495</v>
@@ -1942,7 +1942,7 @@
         <v>2.27</v>
       </c>
       <c r="Y22" t="n">
-        <v>30.3</v>
+        <v>25.8</v>
       </c>
       <c r="Z22" t="n">
         <v>66.95</v>
@@ -2045,13 +2045,13 @@
         <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8821</v>
+        <v>3.2831</v>
       </c>
       <c r="I24" t="n">
         <v>5.75</v>
       </c>
       <c r="J24" t="n">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
       <c r="K24" t="n">
         <v>-1.1</v>
@@ -2129,7 +2129,7 @@
         <v>-6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>3.0928</v>
+        <v>1.5009</v>
       </c>
       <c r="K25" t="n">
         <v>-5.3</v>
@@ -2212,10 +2212,10 @@
         <v>2.67</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>232.204</v>
+        <v>227.558</v>
       </c>
       <c r="AA26" t="n">
         <v>4.53</v>
@@ -2299,7 +2299,7 @@
         <v>23</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.01</v>
+        <v>23.003</v>
       </c>
       <c r="AA27" t="n">
         <v>-3.11</v>
@@ -2376,13 +2376,13 @@
         <v>-1.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>29.9</v>
+        <v>15.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>59.792</v>
+        <v>66.181</v>
       </c>
       <c r="AA28" t="n">
-        <v>-13.41</v>
+        <v>-7.12</v>
       </c>
       <c r="AB28" t="n">
         <v>11.5</v>
@@ -2631,7 +2631,7 @@
         <v>1.4</v>
       </c>
       <c r="L32" t="n">
-        <v>131.981</v>
+        <v>131.851</v>
       </c>
       <c r="M32" t="n">
         <v>4.276</v>
@@ -2646,7 +2646,7 @@
         <v>1.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="Z32" t="n">
         <v>97.798</v>
@@ -2684,19 +2684,19 @@
         <v>1.6</v>
       </c>
       <c r="H33" t="n">
-        <v>3.2619</v>
+        <v>3.4547</v>
       </c>
       <c r="I33" t="n">
         <v>6.5</v>
       </c>
       <c r="J33" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
         <v>-0.4</v>
       </c>
       <c r="L33" t="n">
-        <v>265.969</v>
+        <v>265.474</v>
       </c>
       <c r="M33" t="n">
         <v>3.73</v>
@@ -2711,10 +2711,10 @@
         <v>1.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>250.968</v>
+        <v>251.696</v>
       </c>
       <c r="AA33" t="n">
         <v>-0.7</v>
@@ -3156,7 +3156,7 @@
         <v>7.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.474</v>
+        <v>4.723</v>
       </c>
       <c r="AA39" t="n">
         <v>-0.99</v>
@@ -3352,7 +3352,7 @@
         <v>87.288</v>
       </c>
       <c r="AA42" t="n">
-        <v>12.01</v>
+        <v>16.79</v>
       </c>
       <c r="AB42" t="n">
         <v>2.5</v>
@@ -3384,13 +3384,13 @@
         <v>4.1</v>
       </c>
       <c r="H43" t="n">
-        <v>6.3629</v>
+        <v>7.1595</v>
       </c>
       <c r="I43" t="n">
         <v>5</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.36</v>
+        <v>-2.16</v>
       </c>
       <c r="K43" t="n">
         <v>-4.4</v>
@@ -3461,7 +3461,7 @@
         <v>-1.1</v>
       </c>
       <c r="L44" t="n">
-        <v>304.971</v>
+        <v>295.482</v>
       </c>
       <c r="M44" t="n">
         <v>5.861</v>
@@ -3476,7 +3476,7 @@
         <v>1.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>16.9</v>
+        <v>12.6</v>
       </c>
       <c r="Z44" t="n">
         <v>277.21</v>
@@ -3590,7 +3590,7 @@
         <v>-6.8</v>
       </c>
       <c r="L46" t="n">
-        <v>90.04300000000001</v>
+        <v>82.188</v>
       </c>
       <c r="M46" t="n">
         <v>5.528</v>
@@ -3605,7 +3605,7 @@
         <v>1.95</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.9</v>
+        <v>-7.7</v>
       </c>
       <c r="Z46" t="n">
         <v>72.172</v>
@@ -3760,10 +3760,10 @@
         <v>10</v>
       </c>
       <c r="Z48" t="n">
-        <v>482.147</v>
+        <v>480.825</v>
       </c>
       <c r="AA48" t="n">
-        <v>-25.78</v>
+        <v>-21.82</v>
       </c>
       <c r="AB48" t="n">
         <v>15.9</v>
@@ -3911,7 +3911,7 @@
         <v>30.033</v>
       </c>
       <c r="AA50" t="n">
-        <v>-4.36</v>
+        <v>-4.15</v>
       </c>
       <c r="AB50" t="n">
         <v>-1.4</v>
@@ -4050,7 +4050,7 @@
         <v>45.9</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.48</v>
+        <v>2.86</v>
       </c>
       <c r="AB52" t="n">
         <v>-0.8</v>
@@ -4094,7 +4094,7 @@
         <v>0.7</v>
       </c>
       <c r="L53" t="n">
-        <v>283.137</v>
+        <v>276.186</v>
       </c>
       <c r="M53" t="n">
         <v>8.051</v>
@@ -4109,7 +4109,7 @@
         <v>0.21</v>
       </c>
       <c r="Y53" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="Z53" t="n">
         <v>302.852</v>
@@ -4274,7 +4274,7 @@
         <v>0.31</v>
       </c>
       <c r="Y55" t="n">
-        <v>4.7</v>
+        <v>-7.8</v>
       </c>
       <c r="Z55" t="n">
         <v>137.109</v>
@@ -4427,7 +4427,7 @@
         <v>-1.12</v>
       </c>
       <c r="Y57" t="n">
-        <v>-3.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AB57" t="n">
         <v>13.2</v>
@@ -4505,7 +4505,7 @@
         <v>32</v>
       </c>
       <c r="AA58" t="n">
-        <v>-11.23</v>
+        <v>-12.01</v>
       </c>
       <c r="AF58" t="inlineStr">
         <is>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -4238,7 +4238,7 @@
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="H55" t="n">
         <v>29.73</v>
@@ -4253,13 +4253,13 @@
         <v>-2.7</v>
       </c>
       <c r="L55" t="n">
-        <v>174.4</v>
+        <v>167.4</v>
       </c>
       <c r="M55" t="n">
         <v>5.128</v>
       </c>
       <c r="N55" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="O55" t="n">
         <v>31.8</v>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -4324,7 +4324,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>4-year EFF (first review completed 20-Jul-26; SDR 503M, about $690M disbursed)</t>
+          <t>4-year EFF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 19-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 20-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -1480,13 +1480,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EM cross-region (thematic, no single country)</t>
+          <t>Emerging markets (cross-country theme)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>20-Oct-26</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 20-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 21-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -1884,13 +1884,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Thematic: Gulf (GCC) support for EM sovereigns (Pakistan, Egypt, Bahrain)</t>
+          <t>Thematic (Gulf donors; EM recipients Pakistan, Egypt, Bahrain)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>21-Oct-26</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 21-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 23-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Caa1</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1548,7 +1548,7 @@
         <v>7.5</v>
       </c>
       <c r="P16" t="n">
-        <v>79.7</v>
+        <v>81.8</v>
       </c>
       <c r="Q16" t="n">
         <v>-12.1</v>
@@ -1557,7 +1557,7 @@
         <v>4.9</v>
       </c>
       <c r="S16" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="Y16" t="n">
         <v>14.7</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>15-Oct-26</t>
+          <t>23-Oct-26</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36-month non-financing Policy Coordination Instrument (PCI), following completion of the 39-month US$3bn ECF on 27-Jul-26</t>
+          <t>36-month non-financing Policy Coordination Instrument (PCI), following the US$3bn 39-month ECF completed 27-Jul-26</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1842,16 +1842,19 @@
         <v>10.1</v>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3</v>
+        <v>-0.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>17.2</v>
       </c>
       <c r="X20" t="n">
         <v>1.86</v>
@@ -1867,7 +1870,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>15-Oct-26</t>
+          <t>23-Oct-26</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Sub-Saharan Africa (East Africa)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2429,11 +2429,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>None (previous EFF/ECF/RSF expired uncompleted Apr-25; new request Mar-25, no staff-level agreement; Article IV mission expected early Dec-26)</t>
+          <t>None; previous EFF/ECF/RSF expired uncompleted in Apr-25; new programme requested Mar-25, no staff-level agreement; Article IV mission expected early Dec-26</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="H29" t="n">
         <v>6.76</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>15-Oct-26</t>
+          <t>23-Oct-26</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 23-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 26-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -625,13 +625,13 @@
         <v>-2.8</v>
       </c>
       <c r="L3" t="n">
-        <v>9.347</v>
+        <v>9.756</v>
       </c>
       <c r="M3" t="n">
         <v>7.2</v>
       </c>
       <c r="N3" t="n">
-        <v>5.73</v>
+        <v>5.99</v>
       </c>
       <c r="O3" t="n">
         <v>39.7</v>
@@ -643,7 +643,7 @@
         <v>-2</v>
       </c>
       <c r="Y3" t="n">
-        <v>19.3</v>
+        <v>17.9</v>
       </c>
       <c r="Z3" t="n">
         <v>8.401999999999999</v>
@@ -950,7 +950,7 @@
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>6.671</v>
+        <v>3.079</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
@@ -968,7 +968,7 @@
         <v>-1.58</v>
       </c>
       <c r="Y7" t="n">
-        <v>86.40000000000001</v>
+        <v>-29.4</v>
       </c>
       <c r="AA7" t="n">
         <v>2.28</v>
@@ -1099,7 +1099,7 @@
         <v>-7.7</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Y9" t="n">
         <v>1.8</v>
@@ -1248,13 +1248,13 @@
         <v>-2.5</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.54</v>
+        <v>-1.05</v>
       </c>
       <c r="Y11" t="n">
         <v>11.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>47.964</v>
+        <v>47.62</v>
       </c>
       <c r="AA11" t="n">
         <v>0.91</v>
@@ -1313,7 +1313,7 @@
         <v>-5.2</v>
       </c>
       <c r="X12" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="Y12" t="n">
         <v>6.6</v>
@@ -1354,19 +1354,19 @@
         <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.922</v>
+        <v>2.5127</v>
       </c>
       <c r="I13" t="n">
         <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="K13" t="n">
         <v>-1.5</v>
       </c>
       <c r="L13" t="n">
-        <v>184.565</v>
+        <v>180.104</v>
       </c>
       <c r="M13" t="n">
         <v>7.644</v>
@@ -1378,10 +1378,10 @@
         <v>-2.3</v>
       </c>
       <c r="X13" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="Z13" t="n">
         <v>171.989</v>
@@ -1560,7 +1560,7 @@
         <v>59</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.7</v>
+        <v>16.2</v>
       </c>
       <c r="Z16" t="n">
         <v>17.224</v>
@@ -1779,7 +1779,7 @@
         <v>7.294</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.72</v>
+        <v>-0.62</v>
       </c>
       <c r="AB19" t="n">
         <v>-2.5</v>
@@ -1942,7 +1942,7 @@
         <v>-5.5</v>
       </c>
       <c r="X22" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="Y22" t="n">
         <v>25.8</v>
@@ -2007,7 +2007,7 @@
         <v>-7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.75</v>
+        <v>-2.63</v>
       </c>
       <c r="Y23" t="n">
         <v>8.1</v>
@@ -2072,7 +2072,7 @@
         <v>-2.9</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.03</v>
+        <v>-2.89</v>
       </c>
       <c r="Y24" t="n">
         <v>-2.8</v>
@@ -2132,7 +2132,7 @@
         <v>-6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5009</v>
+        <v>3.2588</v>
       </c>
       <c r="K25" t="n">
         <v>-5.3</v>
@@ -2150,7 +2150,7 @@
         <v>-4.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>-10.9</v>
+        <v>-14.6</v>
       </c>
       <c r="AA25" t="n">
         <v>4.92</v>
@@ -2212,7 +2212,7 @@
         <v>-5.9</v>
       </c>
       <c r="X26" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="Y26" t="n">
         <v>2.2</v>
@@ -2299,7 +2299,7 @@
         <v>-2.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>23</v>
+        <v>17.8</v>
       </c>
       <c r="Z27" t="n">
         <v>23.003</v>
@@ -2463,7 +2463,7 @@
         <v>33</v>
       </c>
       <c r="Y29" t="n">
-        <v>34.7</v>
+        <v>28.3</v>
       </c>
       <c r="AB29" t="n">
         <v>-2.9</v>
@@ -2646,7 +2646,7 @@
         <v>-3.3</v>
       </c>
       <c r="X32" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
         <v>6.7</v>
@@ -2711,7 +2711,7 @@
         <v>-4.4</v>
       </c>
       <c r="X33" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Y33" t="n">
         <v>2.3</v>
@@ -2752,7 +2752,7 @@
         <v>2.8</v>
       </c>
       <c r="H34" t="n">
-        <v>3.6043</v>
+        <v>5.1904</v>
       </c>
       <c r="K34" t="n">
         <v>-19.4</v>
@@ -2824,13 +2824,13 @@
         <v>4.9</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3333</v>
+        <v>0.4992</v>
       </c>
       <c r="I35" t="n">
         <v>2.25</v>
       </c>
       <c r="J35" t="n">
-        <v>2.58</v>
+        <v>1.75</v>
       </c>
       <c r="K35" t="n">
         <v>-3.1</v>
@@ -2851,7 +2851,7 @@
         <v>11.5</v>
       </c>
       <c r="X35" t="n">
-        <v>-2.1</v>
+        <v>-2.86</v>
       </c>
       <c r="Y35" t="n">
         <v>18</v>
@@ -3153,10 +3153,10 @@
         <v>-4.2</v>
       </c>
       <c r="X39" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="Y39" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="Z39" t="n">
         <v>4.723</v>
@@ -3272,7 +3272,7 @@
         <v>-0.4</v>
       </c>
       <c r="L41" t="n">
-        <v>27.993</v>
+        <v>31.584</v>
       </c>
       <c r="M41" t="n">
         <v>3.755</v>
@@ -3287,7 +3287,7 @@
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>22.8</v>
+        <v>34.7</v>
       </c>
       <c r="AA41" t="n">
         <v>-0.14</v>
@@ -3346,7 +3346,7 @@
         <v>-2</v>
       </c>
       <c r="X42" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="Y42" t="n">
         <v>16.3</v>
@@ -3411,7 +3411,7 @@
         <v>-3.7</v>
       </c>
       <c r="X43" t="n">
-        <v>-0.19</v>
+        <v>-0.57</v>
       </c>
       <c r="Y43" t="n">
         <v>-2</v>
@@ -3476,13 +3476,13 @@
         <v>-6.7</v>
       </c>
       <c r="X44" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="Y44" t="n">
         <v>12.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>277.21</v>
+        <v>267.391</v>
       </c>
       <c r="AA44" t="n">
         <v>-13.87</v>
@@ -3581,13 +3581,13 @@
         <v>0.7</v>
       </c>
       <c r="H46" t="n">
-        <v>8.16</v>
+        <v>6.1713</v>
       </c>
       <c r="I46" t="n">
         <v>6.5</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.66</v>
+        <v>0.33</v>
       </c>
       <c r="K46" t="n">
         <v>-6.8</v>
@@ -3605,7 +3605,7 @@
         <v>-6.2</v>
       </c>
       <c r="X46" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="Y46" t="n">
         <v>-7.7</v>
@@ -3757,10 +3757,10 @@
         <v>-3.5</v>
       </c>
       <c r="X48" t="n">
-        <v>-0.31</v>
+        <v>-0.68</v>
       </c>
       <c r="Y48" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="Z48" t="n">
         <v>480.825</v>
@@ -3893,7 +3893,7 @@
         <v>-4.1</v>
       </c>
       <c r="L50" t="n">
-        <v>35.71</v>
+        <v>33.849</v>
       </c>
       <c r="M50" t="n">
         <v>6.2</v>
@@ -3905,10 +3905,10 @@
         <v>-3.25</v>
       </c>
       <c r="X50" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="Y50" t="n">
-        <v>7</v>
+        <v>-0.7</v>
       </c>
       <c r="Z50" t="n">
         <v>30.033</v>
@@ -3991,10 +3991,10 @@
         <v>20</v>
       </c>
       <c r="X51" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="Y51" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z51" t="n">
         <v>74.307</v>
@@ -4053,7 +4053,7 @@
         <v>45.9</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="AB52" t="n">
         <v>-0.8</v>
@@ -4109,7 +4109,7 @@
         <v>-2.2</v>
       </c>
       <c r="X53" t="n">
-        <v>0.21</v>
+        <v>-0.11</v>
       </c>
       <c r="Y53" t="n">
         <v>1.1</v>
@@ -4274,7 +4274,7 @@
         <v>-5.2</v>
       </c>
       <c r="X55" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="Y55" t="n">
         <v>-7.8</v>
@@ -4361,10 +4361,10 @@
         <v>-0.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="Z56" t="n">
-        <v>38.646</v>
+        <v>36.955</v>
       </c>
       <c r="AA56" t="n">
         <v>-24.81</v>
@@ -4427,7 +4427,7 @@
         <v>4.9</v>
       </c>
       <c r="X57" t="n">
-        <v>-1.12</v>
+        <v>0.1</v>
       </c>
       <c r="Y57" t="n">
         <v>-0.8</v>

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -3044,22 +3044,22 @@
         <v>4.1</v>
       </c>
       <c r="H38" t="n">
-        <v>15.39</v>
+        <v>14.63</v>
       </c>
       <c r="I38" t="n">
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>7.61</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="L38" t="n">
         <v>55.07</v>
       </c>
       <c r="M38" t="n">
-        <v>9.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="O38" t="n">
         <v>14.4</v>
@@ -3071,7 +3071,7 @@
         <v>-4.4</v>
       </c>
       <c r="S38" t="n">
-        <v>55</v>
+        <v>53.7</v>
       </c>
       <c r="X38" t="n">
         <v>-0.51</v>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>16-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -3958,10 +3958,10 @@
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H51" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I51" t="n">
         <v>7.25</v>
@@ -3973,22 +3973,22 @@
         <v>-1.6</v>
       </c>
       <c r="L51" t="n">
-        <v>75.95999999999999</v>
+        <v>75.48</v>
       </c>
       <c r="M51" t="n">
         <v>5.8</v>
       </c>
       <c r="P51" t="n">
-        <v>77</v>
+        <v>78.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>-4</v>
+        <v>-3.9</v>
       </c>
       <c r="R51" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X51" t="n">
         <v>1.04</v>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>16-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 26-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 27-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -4247,22 +4247,22 @@
         <v>29.73</v>
       </c>
       <c r="I55" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J55" t="n">
-        <v>12.5</v>
+        <v>12.11</v>
       </c>
       <c r="K55" t="n">
         <v>-2.7</v>
       </c>
       <c r="L55" t="n">
-        <v>167.4</v>
+        <v>171.6</v>
       </c>
       <c r="M55" t="n">
         <v>5.128</v>
       </c>
       <c r="N55" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="O55" t="n">
         <v>31.8</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>27-Oct-26</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 27-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 28-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -4334,13 +4334,13 @@
         <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="I56" t="n">
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="K56" t="n">
         <v>-18.9</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>28-Oct-26</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sovereign comp sheet, built 28-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
+          <t>Sovereign comp sheet, built 29-Oct-26 from database/sovereigns/*.json; derived columns are formulas on the Data sheet</t>
         </is>
       </c>
     </row>
@@ -1480,13 +1480,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Emerging markets (cross-country theme)</t>
+          <t>Emerging markets (cross-market topic, no single sovereign)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>20-Oct-26</t>
+          <t>29-Oct-26</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">

--- a/models/sovereigns/Sovereign_Comp_Sheet.xlsx
+++ b/models/sovereigns/Sovereign_Comp_Sheet.xlsx
@@ -1887,13 +1887,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Thematic (Gulf donors; EM recipients Pakistan, Egypt, Bahrain)</t>
+          <t>Multi-country (Gulf creditors; EM recipients Egypt, Pakistan, Bahrain)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>21-Oct-26</t>
+          <t>29-Oct-26</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
